--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25684,7 +25684,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26466,7 +26466,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26558,7 +26558,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26696,7 +26696,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26788,7 +26788,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27340,7 +27340,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27938,7 +27938,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28076,7 +28076,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28260,7 +28260,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30744,7 +30744,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32032,7 +32032,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33044,7 +33044,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33412,7 +33412,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33550,7 +33550,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33826,7 +33826,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34102,7 +34102,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34424,7 +34424,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34516,7 +34516,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34746,7 +34746,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35022,7 +35022,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35206,7 +35206,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35390,7 +35390,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35482,7 +35482,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35528,7 +35528,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35804,7 +35804,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35942,7 +35942,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36080,7 +36080,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36126,7 +36126,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36356,7 +36356,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36402,7 +36402,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36770,7 +36770,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36908,7 +36908,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -37000,7 +37000,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37046,7 +37046,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37184,7 +37184,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37322,7 +37322,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37368,7 +37368,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37460,7 +37460,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37552,7 +37552,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37782,7 +37782,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,16 +80,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -25604,32 +25597,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -25665,26 +25658,26 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>43.19</v>
+        <v>43.56</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>42.39</v>
+        <v>45.09</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>43.09</v>
+        <v>46.98</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>43.67</v>
+        <v>48.42</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>38.77</v>
+        <v>47.61</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>47.63</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25711,26 +25704,26 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>60.62</v>
+        <v>61.36</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>61.8</v>
+        <v>61.44</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>61.99</v>
+        <v>60.23</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>60.86</v>
+        <v>59.55</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>60.18</v>
+        <v>58.64</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>58.93</v>
+        <v>57.17</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25757,26 +25750,26 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>57.11</v>
+        <v>55.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>57.42</v>
+        <v>56.44</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>59.73</v>
+        <v>56.99</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>61.63</v>
+        <v>54.9</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>60.18</v>
+        <v>53.28</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>59.34</v>
+        <v>51.58</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25803,26 +25796,26 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>69.91</v>
+        <v>67.67</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>71.83</v>
+        <v>67.09</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>73.18000000000001</v>
+        <v>64.39</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>73.25</v>
+        <v>60.95</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>73.59</v>
+        <v>56.71</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>72.05</v>
+        <v>54.76</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25849,26 +25842,26 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>44.06</v>
+        <v>44.42</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>44.01</v>
+        <v>45.56</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>44.71</v>
+        <v>46.69</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>45.26</v>
+        <v>46.39</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>38.98</v>
+        <v>43.7</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>42.08</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25895,26 +25888,26 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>51.38</v>
+        <v>52.49</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>52.52</v>
+        <v>53.58</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>53.65</v>
+        <v>52.78</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>52.88</v>
+        <v>49.14</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>49.69</v>
+        <v>46.05</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>47.17</v>
+        <v>43.85</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25941,26 +25934,26 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>59.62</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>60.33</v>
+        <v>59.24</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>60.94</v>
+        <v>58.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>61.17</v>
+        <v>57.45</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>60.83</v>
+        <v>56.48</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>62.01</v>
+        <v>57.33</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25987,26 +25980,26 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46.68</v>
+        <v>45.78</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>45.55</v>
+        <v>44.72</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44.25</v>
+        <v>44.79</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>43.97</v>
+        <v>46.62</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>45.09</v>
+        <v>49.91</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>48.21</v>
+        <v>54.05</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26033,26 +26026,26 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>49.88</v>
+        <v>51.91</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>52.14</v>
+        <v>53.61</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>53.9</v>
+        <v>54.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>54.53</v>
+        <v>53.38</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>53.74</v>
+        <v>55.03</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>56.14</v>
+        <v>54.97</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26079,26 +26072,26 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>52.99</v>
+        <v>52.95</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>53.67</v>
+        <v>52.4</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>53.42</v>
+        <v>51.52</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>52.94</v>
+        <v>51.87</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>53.8</v>
+        <v>52.91</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>56.65</v>
+        <v>55.01</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26125,26 +26118,26 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>51.47</v>
+        <v>51.83</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>52.52</v>
+        <v>51.67</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>52.69</v>
+        <v>52.13</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>53.38</v>
+        <v>52.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>53.98</v>
+        <v>53.21</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>54.91</v>
+        <v>56.44</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26171,26 +26164,26 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>53.08</v>
+        <v>51.58</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>52.23</v>
+        <v>48.9</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>49.89</v>
+        <v>45.77</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>47.28</v>
+        <v>44.14</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46.42</v>
+        <v>44.46</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>48.59</v>
+        <v>47.4</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26217,26 +26210,26 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>45.32</v>
+        <v>45.47</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>45.98</v>
+        <v>45.72</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45.79</v>
+        <v>45.7</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>44.49</v>
+        <v>45.54</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>42.33</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>38.86</v>
+        <v>43.48</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>42.96</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26263,26 +26256,26 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>48.16</v>
+        <v>48.68</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>50.17</v>
+        <v>50.44</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>52.28</v>
+        <v>51.19</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>52.96</v>
+        <v>50.41</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>51.72</v>
+        <v>48.35</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>48.36</v>
+        <v>48.02</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26309,26 +26302,26 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>41.09</v>
+        <v>42.34</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>38.98</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>36.93</v>
+        <v>37.64</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>34.58</v>
+        <v>36.84</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>32.15</v>
+        <v>35.39</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>29.33</v>
+        <v>32.93</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26355,26 +26348,26 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>43.85</v>
+        <v>42.91</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>41.17</v>
+        <v>40.6</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>37.7</v>
+        <v>39.18</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>34.65</v>
+        <v>38.93</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>31.9</v>
+        <v>38.13</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>30.61</v>
+        <v>34.24</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26401,26 +26394,26 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>47.83</v>
+        <v>48.83</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>49.45</v>
+        <v>49.21</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>49.73</v>
+        <v>48.28</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>48.56</v>
+        <v>49.28</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>49.16</v>
+        <v>51.78</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>51.21</v>
+        <v>52.65</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26447,26 +26440,26 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>26.84</v>
+        <v>25.24</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>24.59</v>
+        <v>24.74</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>23.99</v>
+        <v>26.27</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>25.42</v>
+        <v>28.12</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>27.23</v>
+        <v>30.71</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>29.39</v>
+        <v>30.44</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26493,26 +26486,26 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>45.35</v>
+        <v>43.85</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>42.28</v>
+        <v>41.73</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>39.17</v>
+        <v>39.78</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>35.79</v>
+        <v>38.16</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>32.17</v>
+        <v>37.61</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>31.9</v>
+        <v>35.71</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26539,26 +26532,26 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>39.68</v>
+        <v>37.87</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>37.37</v>
+        <v>35.91</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>35.13</v>
+        <v>36.46</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>35.35</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>36.15</v>
+        <v>37.81</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>40.4</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>38.68</v>
+        <v>39.78</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26585,26 +26578,26 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>59.96</v>
+        <v>61.25</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>59.58</v>
+        <v>60.14</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>57.75</v>
+        <v>57.58</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>54.15</v>
+        <v>54.88</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>50.3</v>
+        <v>52.14</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>46.86</v>
+        <v>50.71</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26631,26 +26624,26 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>59.93</v>
+        <v>59.42</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>57.48</v>
+        <v>57.91</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>55.16</v>
+        <v>55.59</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>51.45</v>
+        <v>54.68</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>49.25</v>
+        <v>52.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>46.18</v>
+        <v>53.08</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26677,26 +26670,26 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>62.59</v>
+        <v>63.25</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>61.26</v>
+        <v>61.58</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>58.73</v>
+        <v>58.58</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>54.25</v>
+        <v>58.61</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>52.18</v>
+        <v>57.17</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>48.9</v>
+        <v>56.5</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26723,26 +26716,26 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>66.76000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>64.95</v>
+        <v>62.73</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>63.29</v>
+        <v>61.55</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>62.43</v>
+        <v>59.95</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>61.16</v>
+        <v>58.11</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>59.6</v>
+        <v>59.3</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26769,26 +26762,26 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>50.1</v>
+        <v>50.41</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>50.88</v>
+        <v>51.13</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>51.82</v>
+        <v>52.54</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>53.52</v>
+        <v>54.74</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>55.69</v>
+        <v>55.87</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>55.75</v>
+        <v>54.11</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26815,26 +26808,26 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>54.09</v>
+        <v>56.76</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>55.8</v>
+        <v>58.42</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>56.76</v>
+        <v>59.52</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>56.68</v>
+        <v>63.52</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>59.27</v>
+        <v>66.13</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>61.55</v>
+        <v>65.11</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26861,26 +26854,26 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46.98</v>
+        <v>50.56</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>49.79</v>
+        <v>53.84</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>52.59</v>
+        <v>57.38</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>55.37</v>
+        <v>61.27</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>57.96</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>60.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26907,26 +26900,26 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>70.75</v>
+        <v>70.03</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>70.29000000000001</v>
+        <v>71.28</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>71.79000000000001</v>
+        <v>72.28</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>73.01000000000001</v>
+        <v>73.19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>74.11</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>75.02</v>
+        <v>74.3</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26953,26 +26946,26 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>72.38</v>
+        <v>72.81</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>73.06</v>
+        <v>71.39</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>71.69</v>
+        <v>68.42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>68.84999999999999</v>
+        <v>66.14</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>66.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>66.64</v>
+        <v>63.45</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -26999,26 +26992,26 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>52.44</v>
+        <v>52.57</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>52.36</v>
+        <v>53.05</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>52.8</v>
+        <v>52.48</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>52.26</v>
+        <v>51.61</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>51.5</v>
+        <v>49.64</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>48.66</v>
+        <v>45.94</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27045,26 +27038,26 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>56.97</v>
+        <v>58.16</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>59.55</v>
+        <v>59.88</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>61.84</v>
+        <v>61.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>63.89</v>
+        <v>62.24</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>64.83</v>
+        <v>61.24</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>62.76</v>
+        <v>59.53</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27091,26 +27084,26 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>51.09</v>
+        <v>51.47</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>50.95</v>
+        <v>51.52</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>50.52</v>
+        <v>52.42</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>50.8</v>
+        <v>53.67</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>51.26</v>
+        <v>53.73</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>50.27</v>
+        <v>54.32</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27137,26 +27130,26 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>51.85</v>
+        <v>51.99</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>50.97</v>
+        <v>51.13</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>49.8</v>
+        <v>50.13</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>48.28</v>
+        <v>48.42</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>45.96</v>
+        <v>47.21</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>45.21</v>
+        <v>50.35</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27183,26 +27176,26 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>52.4</v>
+        <v>53.08</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>51.69</v>
+        <v>52.5</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>50.45</v>
+        <v>51.85</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>48.97</v>
+        <v>52.62</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>48.27</v>
+        <v>52.62</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>48.17</v>
+        <v>54.09</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27229,26 +27222,26 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>55.6</v>
+        <v>54.57</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>54.3</v>
+        <v>52.23</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>51.7</v>
+        <v>48.84</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>48.09</v>
+        <v>46.84</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>45.75</v>
+        <v>45.12</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>44.61</v>
+        <v>45.07</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27275,26 +27268,26 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>52.63</v>
+        <v>53.49</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>53.61</v>
+        <v>53.7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>53.89</v>
+        <v>54.43</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>54.65</v>
+        <v>54.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>54.91</v>
+        <v>55.59</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>56.84</v>
+        <v>58.19</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27321,26 +27314,26 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>50.78</v>
+        <v>50.75</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>50.98</v>
+        <v>50.82</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>51.06</v>
+        <v>49.86</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>50.15</v>
+        <v>49.16</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>49.64</v>
+        <v>48.35</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27367,26 +27360,26 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>64.05</v>
+        <v>65.03</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>65.55</v>
+        <v>65.64</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>66.06999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>65.95</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>65.8</v>
+        <v>65.23</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>66.65000000000001</v>
+        <v>65.16</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27413,26 +27406,26 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>52.33</v>
+        <v>51.98</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>51.15</v>
+        <v>49.95</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>48.97</v>
+        <v>49.95</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>48.65</v>
+        <v>48.52</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>46.72</v>
+        <v>48.14</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>47.25</v>
+        <v>52.66</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27459,26 +27452,26 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>32.42</v>
+        <v>32.99</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>31.73</v>
+        <v>33.92</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>31.9</v>
+        <v>34.4</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>31.16</v>
+        <v>35.9</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>30.66</v>
+        <v>37.53</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>30.42</v>
+        <v>35.22</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27505,26 +27498,26 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>50.34</v>
+        <v>50.55</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>49.86</v>
+        <v>50.47</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>49.48</v>
+        <v>50.51</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>49</v>
+        <v>50.68</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>48.22</v>
+        <v>50.71</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>46.18</v>
+        <v>48.14</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27551,26 +27544,26 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>50.98</v>
+        <v>49.87</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>49.23</v>
+        <v>48.9</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>48</v>
+        <v>45.82</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>44.52</v>
+        <v>44.87</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>42.66</v>
+        <v>44.03</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>40.5</v>
+        <v>41.48</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27597,26 +27590,26 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>38.54</v>
+        <v>39.05</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>38.19</v>
+        <v>38.58</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>37.28</v>
+        <v>38.53</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>36.57</v>
+        <v>38.96</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>35.97</v>
+        <v>38.23</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>33.48</v>
+        <v>35.4</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27643,26 +27636,26 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>60.34</v>
+        <v>61.34</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>59.73</v>
+        <v>59.99</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>57.69</v>
+        <v>57.25</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>53.96</v>
+        <v>54.42</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>50.05</v>
+        <v>51.6</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>46.59</v>
+        <v>50.22</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27689,26 +27682,26 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>58.22</v>
+        <v>56.46</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>58.64</v>
+        <v>57.35</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>61.06</v>
+        <v>57.66</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>62.93</v>
+        <v>55.24</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>61.58</v>
+        <v>53.45</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>60.91</v>
+        <v>51.98</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27735,26 +27728,26 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>69.16</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>71.52</v>
+        <v>72.3</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>74.02</v>
+        <v>74.13</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>76.61</v>
+        <v>73.88</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>77.34999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>76.97</v>
+        <v>74.23</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27781,26 +27774,26 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>45.33</v>
+        <v>46.68</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>46.46</v>
+        <v>47.76</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>47.6</v>
+        <v>48.7</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>48.59</v>
+        <v>48.42</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>48.29</v>
+        <v>47.77</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>46.99</v>
+        <v>46.83</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27827,26 +27820,26 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>52.84</v>
+        <v>52.6</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>53.86</v>
+        <v>53.44</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>55.68</v>
+        <v>54.36</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>58.05</v>
+        <v>53.12</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>58.46</v>
+        <v>52.01</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>58.41</v>
+        <v>51.61</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27873,26 +27866,26 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>76.02</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>78.31999999999999</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>80.27</v>
+        <v>81.03</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>82.23999999999999</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>83.72</v>
+        <v>82.59</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>83.25</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27919,26 +27912,26 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>69.91</v>
+        <v>67.64</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>71.87</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>73.27</v>
+        <v>64.47</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>73.45</v>
+        <v>61.1</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>73.84</v>
+        <v>56.89</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>72.27</v>
+        <v>55.02</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27965,26 +27958,26 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>50.1</v>
+        <v>50.42</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>50.89</v>
+        <v>51.15</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>51.85</v>
+        <v>52.57</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>53.55</v>
+        <v>54.78</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>55.72</v>
+        <v>55.91</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>55.78</v>
+        <v>54.15</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28011,26 +28004,26 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>54.07</v>
+        <v>56.72</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>55.77</v>
+        <v>58.35</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>56.69</v>
+        <v>59.38</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>56.54</v>
+        <v>63.34</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>59.11</v>
+        <v>65.95</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>61.4</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28057,26 +28050,26 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>47.1</v>
+        <v>50.65</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>49.89</v>
+        <v>53.91</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>52.68</v>
+        <v>57.38</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>55.41</v>
+        <v>61.26</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>57.98</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>60.35</v>
+        <v>64.87</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28103,26 +28096,26 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>67.45</v>
+        <v>66.67</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>66.88</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>68.25</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>69.25</v>
+        <v>69.67</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>70.45999999999999</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>71.59</v>
+        <v>71.3</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28149,26 +28142,26 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>72.05</v>
+        <v>72.45</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>72.69</v>
+        <v>70.95</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>71.23</v>
+        <v>67.91</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>68.3</v>
+        <v>65.67</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>66.22</v>
+        <v>64.36</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>66.2</v>
+        <v>63.14</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28195,26 +28188,26 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>52.39</v>
+        <v>52.54</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>52.33</v>
+        <v>53.01</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>52.77</v>
+        <v>52.42</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>52.22</v>
+        <v>51.5</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>51.42</v>
+        <v>49.48</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>48.55</v>
+        <v>45.74</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28241,26 +28234,26 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>38.99</v>
+        <v>39.04</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>37.71</v>
+        <v>38.33</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>36.07</v>
+        <v>37.23</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>33.66</v>
+        <v>36.83</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>31.34</v>
+        <v>36.6</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>29.22</v>
+        <v>38.2</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28287,26 +28280,26 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>48.11</v>
+        <v>47.26</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>45.73</v>
+        <v>44.55</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>42.06</v>
+        <v>40.8</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>37.02</v>
+        <v>37.74</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>32.25</v>
+        <v>35.58</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>30.34</v>
+        <v>34.2</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28333,26 +28326,26 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>49.91</v>
+        <v>46.31</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>47.56</v>
+        <v>44.7</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>46.3</v>
+        <v>43.05</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>45.28</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>43.72</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>41.31</v>
+        <v>40.52</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>34.98</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28379,26 +28372,26 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>45.79</v>
+        <v>46.76</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>45.08</v>
+        <v>46.03</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>38.86</v>
+        <v>43.38</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>40.66</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>33.82</v>
+        <v>38.87</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>31.04</v>
+        <v>39.64</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28425,26 +28418,26 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>64.88</v>
+        <v>65.86</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>64.03</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>62.18</v>
+        <v>62.61</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>57.85</v>
+        <v>59.1</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>52.1</v>
+        <v>52.48</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>45.73</v>
+        <v>45.23</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28471,26 +28464,26 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>69.83</v>
+        <v>73.31</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>72.05</v>
+        <v>75.75</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>76.56</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>73.33</v>
+        <v>74.19</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>69.08</v>
+        <v>68.45</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>64.52</v>
+        <v>59.7</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28517,26 +28510,26 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>54.54</v>
+        <v>55.62</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>54.91</v>
+        <v>55.82</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>54.49</v>
+        <v>55.02</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>52.87</v>
+        <v>53.03</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>45.57</v>
+        <v>47.41</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>39.8</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28563,26 +28556,26 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>66.03</v>
+        <v>65.91</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>64.09</v>
+        <v>65.22</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>62.16</v>
+        <v>63.59</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>58.74</v>
+        <v>60.82</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>53.52</v>
+        <v>56.85</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>50.17</v>
+        <v>50.76</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28609,26 +28602,26 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>44.85</v>
+        <v>49.08</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>48.45</v>
+        <v>52.49</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>51.32</v>
+        <v>54.56</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>52.68</v>
+        <v>54.78</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>51.87</v>
+        <v>50.29</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>48.65</v>
+        <v>42.88</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28655,26 +28648,26 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>60.64</v>
+        <v>61.53</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>62.07</v>
+        <v>62.65</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>63.23</v>
+        <v>63.89</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>64.54000000000001</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>66.48999999999999</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>69.09</v>
+        <v>69.64</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28701,26 +28694,26 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>50.69</v>
+        <v>50.15</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>49.72</v>
+        <v>48.52</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>47.92</v>
+        <v>46.46</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>45.75</v>
+        <v>46.52</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>45.52</v>
+        <v>47.41</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>46.22</v>
+        <v>49.01</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28747,26 +28740,26 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>52.14</v>
+        <v>52.42</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>51.35</v>
+        <v>51.64</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>50.24</v>
+        <v>50.62</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>48.67</v>
+        <v>48.86</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>46.25</v>
+        <v>47.59</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>45.44</v>
+        <v>50.69</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28793,26 +28786,26 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>52.39</v>
+        <v>53.07</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>51.68</v>
+        <v>52.49</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>50.45</v>
+        <v>51.85</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>48.97</v>
+        <v>52.61</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>48.28</v>
+        <v>52.6</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>48.17</v>
+        <v>54.07</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28839,26 +28832,26 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>55.62</v>
+        <v>54.58</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>54.31</v>
+        <v>52.24</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>51.71</v>
+        <v>48.85</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>48.1</v>
+        <v>46.85</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>45.76</v>
+        <v>45.12</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>44.62</v>
+        <v>45.07</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28885,26 +28878,26 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>52.63</v>
+        <v>53.5</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>53.59</v>
+        <v>53.69</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>53.84</v>
+        <v>54.38</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>54.54</v>
+        <v>54.63</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>54.73</v>
+        <v>55.46</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>56.59</v>
+        <v>58.01</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28931,26 +28924,26 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>50.78</v>
+        <v>50.75</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>50.98</v>
+        <v>50.82</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>51.06</v>
+        <v>49.87</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>50.16</v>
+        <v>49.17</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>49.65</v>
+        <v>48.37</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>48.72</v>
+        <v>48.51</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28977,26 +28970,26 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>63.99</v>
+        <v>64.95</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>65.48</v>
+        <v>65.56</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>65.98999999999999</v>
+        <v>65.42</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>65.87</v>
+        <v>65.19</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>65.73</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>66.56</v>
+        <v>65.06</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29023,26 +29016,26 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>52.4</v>
+        <v>52.16</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>51.29</v>
+        <v>50.21</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>49.16</v>
+        <v>50.24</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>48.81</v>
+        <v>48.93</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>46.9</v>
+        <v>48.65</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>47.44</v>
+        <v>53.18</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29069,26 +29062,26 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>48.93</v>
+        <v>48.38</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>46.54</v>
+        <v>46.77</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>44.22</v>
+        <v>47.02</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>43.04</v>
+        <v>48.24</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>42.11</v>
+        <v>49.58</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>43.58</v>
+        <v>52.33</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29115,26 +29108,26 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>33.24</v>
+        <v>33.82</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>32.59</v>
+        <v>34.72</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>32.75</v>
+        <v>35.14</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>31.97</v>
+        <v>36.44</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>31.32</v>
+        <v>37.8</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>30.87</v>
+        <v>35.41</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29161,26 +29154,26 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>43.08</v>
+        <v>42.1</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>41.58</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>39.76</v>
+        <v>40.67</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>40.11</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>38.57</v>
+        <v>39.11</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>36.54</v>
+        <v>37.95</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>34.57</v>
+        <v>34.75</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29207,26 +29200,26 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>50.24</v>
+        <v>50.48</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>49.81</v>
+        <v>50.44</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>49.47</v>
+        <v>50.49</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>49.02</v>
+        <v>50.67</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>48.27</v>
+        <v>50.7</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>46.23</v>
+        <v>48.11</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29253,26 +29246,26 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>51.28</v>
+        <v>50.05</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>49.44</v>
+        <v>48.97</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>48.1</v>
+        <v>45.82</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>44.55</v>
+        <v>44.81</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>42.66</v>
+        <v>43.9</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>40.46</v>
+        <v>41.37</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29299,26 +29292,26 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>38.63</v>
+        <v>39.11</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>38.25</v>
+        <v>38.62</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>37.32</v>
+        <v>38.55</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>36.6</v>
+        <v>38.97</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>35.98</v>
+        <v>38.23</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>33.48</v>
+        <v>35.4</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29345,26 +29338,26 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>49.19</v>
+        <v>48.95</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>48.5</v>
+        <v>47.68</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>46.96</v>
+        <v>46.55</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>45.42</v>
+        <v>46.32</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>44.42</v>
+        <v>46.75</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>44.33</v>
+        <v>49.06</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29391,26 +29384,26 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>29.87</v>
+        <v>28.67</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>28.44</v>
+        <v>28.15</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>27.7</v>
+        <v>28.99</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>28.13</v>
+        <v>30.29</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>28.83</v>
+        <v>32.12</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>30.57</v>
+        <v>33.45</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29437,26 +29430,26 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>43.92</v>
+        <v>42.77</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>40.92</v>
+        <v>40.14</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>37.05</v>
+        <v>38.23</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>33.43</v>
+        <v>37.53</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>30.15</v>
+        <v>36.55</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>28.68</v>
+        <v>32.83</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29483,26 +29476,26 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>46.4</v>
+        <v>45.63</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>43.87</v>
+        <v>42.69</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>40.02</v>
-      </c>
-      <c r="H85" s="4" t="n">
-        <v>36.67</v>
-      </c>
-      <c r="I85" s="4" t="n">
-        <v>33.97</v>
-      </c>
-      <c r="J85" s="4" t="n">
-        <v>33.64</v>
+        <v>40.72</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>42.26</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29529,26 +29522,26 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>47.51</v>
+        <v>46.17</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>44.62</v>
+        <v>43.91</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>41.45</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v>38.62</v>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>35.62</v>
+        <v>42.4</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>41.59</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>35.93</v>
+        <v>39.85</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29575,26 +29568,26 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>38.22</v>
+        <v>36.24</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>36.64</v>
+        <v>34.83</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>35.32</v>
+        <v>33.61</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>34.29</v>
+        <v>34.65</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>35.57</v>
+        <v>37.05</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>37.57</v>
+        <v>39.71</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29621,26 +29614,26 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>52.39</v>
+        <v>51.68</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>51.61</v>
+        <v>51.11</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>50.94</v>
+        <v>50.76</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>50.45</v>
+        <v>51.44</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>50.9</v>
+        <v>53.21</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>52.99</v>
+        <v>55.55</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29667,26 +29660,26 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>60.38</v>
+        <v>61.59</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>59.97</v>
+        <v>60.43</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>58.11</v>
+        <v>57.82</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>54.5</v>
+        <v>55.07</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>50.63</v>
+        <v>52.24</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>47.14</v>
+        <v>50.8</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29713,26 +29706,26 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>59.79</v>
+        <v>59.22</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>57.22</v>
+        <v>57.67</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>54.83</v>
+        <v>55.32</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>51.06</v>
+        <v>54.44</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>48.86</v>
+        <v>52.74</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>45.81</v>
+        <v>52.89</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29759,26 +29752,26 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>62.69</v>
+        <v>63.35</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>61.38</v>
+        <v>61.69</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>58.86</v>
+        <v>58.68</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>54.38</v>
+        <v>58.68</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>52.3</v>
+        <v>57.24</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>49.05</v>
+        <v>56.55</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29805,26 +29798,26 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>45.83</v>
+        <v>47.33</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>47.02</v>
+        <v>48.32</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>48.02</v>
+        <v>49.53</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>49.17</v>
+        <v>49.73</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>49.21</v>
+        <v>49.95</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>48.47</v>
+        <v>49.61</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29851,26 +29844,26 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>64.48</v>
+        <v>63.87</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>62.37</v>
+        <v>62.2</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>59.55</v>
+        <v>58.35</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>54.29</v>
+        <v>53.33</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>47.63</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>40.49</v>
+        <v>46.12</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v>39.04</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29897,26 +29890,26 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>65.53</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>64.72</v>
+        <v>66.87</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>64.92</v>
+        <v>68.38</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>63.1</v>
+        <v>63.57</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>54.6</v>
+        <v>58.54</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29943,26 +29936,26 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>70.36</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>66.92</v>
+        <v>63.87</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>63.24</v>
+        <v>59.64</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>58.77</v>
+        <v>53.68</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>52.77</v>
+        <v>48.58</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>47.44</v>
+        <v>44.22</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -29989,26 +29982,26 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>59.99</v>
+        <v>59.75</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>57.2</v>
+        <v>57.98</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>54.05</v>
+        <v>56.07</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>50.69</v>
+        <v>53</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>45.32</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>38.13</v>
+        <v>47.21</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>42.37</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30035,26 +30028,26 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>71.89</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>69.3</v>
+        <v>70.72</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>67.72</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>59.48</v>
+        <v>63.55</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>56.15</v>
+        <v>56.73</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30081,26 +30074,26 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>67.65000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>64.31</v>
+        <v>62.67</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>61.92</v>
+        <v>60.23</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>59.13</v>
+        <v>55.5</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>54.03</v>
+        <v>48.56</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>45.6</v>
+        <v>42.48</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30127,26 +30120,26 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>59.72</v>
+        <v>59</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>60.57</v>
+        <v>59.54</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>61.55</v>
+        <v>60.01</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>62.68</v>
+        <v>59.25</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>63.11</v>
+        <v>58.68</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>64.69</v>
+        <v>59.85</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30173,26 +30166,26 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>49.25</v>
+        <v>47.65</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>47.63</v>
+        <v>46.75</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>46.6</v>
+        <v>47.24</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>46.79</v>
+        <v>48.54</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>47.4</v>
+        <v>50.73</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>49.44</v>
+        <v>54.15</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30219,26 +30212,26 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>34.61</v>
+        <v>35.06</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>33.89</v>
+        <v>35.98</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>34.1</v>
+        <v>35.95</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>32.87</v>
+        <v>36.92</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>31.9</v>
+        <v>37.65</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>30.91</v>
+        <v>35.46</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30265,26 +30258,26 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>49.34</v>
+        <v>48.53</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>48.08</v>
+        <v>47.09</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>46.35</v>
+        <v>46.08</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>44.86</v>
+        <v>44.73</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>42.72</v>
+        <v>43.22</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>40.62</v>
+        <v>40.19</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30311,26 +30304,26 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>55.66</v>
+        <v>57.2</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>59.64</v>
+        <v>61.03</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>63.15</v>
+        <v>62.74</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>64.48</v>
+        <v>63.25</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>63.86</v>
+        <v>63.57</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>64.68000000000001</v>
+        <v>63.22</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30356,27 +30349,27 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E104" s="4" t="n">
-        <v>39.64</v>
+      <c r="E104" s="3" t="n">
+        <v>41.4</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>43.34</v>
+        <v>45.54</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>48.47</v>
+        <v>48.7</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>52.69</v>
+        <v>52.38</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>57.18</v>
+        <v>56.82</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>59.27</v>
+        <v>59.11</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30403,26 +30396,26 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>49.94</v>
+        <v>51.09</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>52.92</v>
+        <v>53.99</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>56.2</v>
+        <v>55.87</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>58.68</v>
+        <v>57.67</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>60.95</v>
+        <v>58.4</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>61.08</v>
+        <v>57.78</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30449,26 +30442,26 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>49.57</v>
+        <v>51.82</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>54.86</v>
+        <v>56.84</v>
       </c>
       <c r="G106" s="3" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="I106" s="3" t="n">
         <v>60.71</v>
       </c>
-      <c r="H106" s="3" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>64.86</v>
-      </c>
       <c r="J106" s="3" t="n">
-        <v>64.66</v>
+        <v>60.06</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30495,26 +30488,26 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>46.69</v>
+        <v>48.41</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>50.54</v>
+        <v>51.63</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>54.2</v>
+        <v>52.99</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>56.26</v>
+        <v>54.15</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>58.11</v>
+        <v>56.73</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>58.94</v>
+        <v>56.91</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30541,26 +30534,26 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>59.5</v>
+        <v>58.46</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>61.5</v>
+        <v>58.57</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>62.3</v>
+        <v>57.39</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>61.93</v>
+        <v>55.26</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>60.62</v>
+        <v>53.58</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>60.39</v>
+        <v>51.48</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30587,26 +30580,26 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>49.65</v>
+        <v>53.11</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>55.9</v>
+        <v>58.26</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>61.62</v>
+        <v>59.84</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>64.03</v>
+        <v>61.06</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>65.64</v>
+        <v>62.5</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>66.47</v>
+        <v>62.6</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30633,26 +30626,26 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>38.65</v>
+        <v>37.95</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>38.05</v>
+        <v>38.46</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>38.59</v>
-      </c>
-      <c r="H110" s="4" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>40.96</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>41.22</v>
+        <v>42.87</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>41.54</v>
+        <v>45.68</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30679,26 +30672,26 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>53.02</v>
+        <v>51.19</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>52.32</v>
+        <v>50.76</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>52.41</v>
+        <v>50.19</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>52.65</v>
+        <v>49.94</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>53.38</v>
+        <v>51.42</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>54.74</v>
+        <v>51.18</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30725,26 +30718,26 @@
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>50.34</v>
+        <v>48.83</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>49.75</v>
+        <v>47.75</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>49.09</v>
+        <v>47.01</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>49.1</v>
+        <v>46.31</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>49.44</v>
+        <v>47.02</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>50.55</v>
+        <v>48.03</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30771,26 +30764,26 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>46.73</v>
+        <v>46.21</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>45.92</v>
+        <v>45.48</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>45.06</v>
+        <v>45.32</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>44.61</v>
+        <v>45.74</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>44.67</v>
+        <v>47.52</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>46.45</v>
+        <v>49.62</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30817,26 +30810,26 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>45.08</v>
+        <v>44.73</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>45.54</v>
+        <v>43.84</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>45.1</v>
+        <v>42.09</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>43.95</v>
+        <v>41.05</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>43.65</v>
+        <v>41.43</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>43.92</v>
+        <v>43.74</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30863,26 +30856,26 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>39.85</v>
+        <v>39.43</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>39.93</v>
+        <v>38.55</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>39.39</v>
+        <v>37.4</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>38.61</v>
+        <v>37.52</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>39.38</v>
+        <v>38.66</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>40.69</v>
+        <v>40.38</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30909,26 +30902,26 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>46.3</v>
+        <v>46.06</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>45.75</v>
+        <v>45.28</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>44.86</v>
+        <v>44.77</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>44.25</v>
+        <v>44.13</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>43.66</v>
+        <v>46.76</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>46.31</v>
+        <v>48.08</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30955,26 +30948,26 @@
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>54.06</v>
+        <v>52.28</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>53.51</v>
+        <v>51.28</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>52.87</v>
+        <v>49.37</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>51.66</v>
+        <v>47.75</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>51.2</v>
+        <v>47.18</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>50.37</v>
+        <v>48.72</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31001,26 +30994,26 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>47.74</v>
+        <v>48.13</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>48.25</v>
+        <v>48.28</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>48.54</v>
+        <v>48.01</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>48.38</v>
+        <v>47.94</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>48.6</v>
+        <v>48.41</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>48.66</v>
+        <v>48.93</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31047,26 +31040,26 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>51.57</v>
+        <v>52.97</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>52.78</v>
+        <v>53.81</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>53.38</v>
+        <v>54.25</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>53.52</v>
+        <v>54.66</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>53.48</v>
+        <v>55.6</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>54.16</v>
+        <v>57.03</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31093,26 +31086,26 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>44.88</v>
+        <v>46.72</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>46.37</v>
+        <v>48.74</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>48.14</v>
+        <v>49.05</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>48.07</v>
+        <v>49.19</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>47.43</v>
+        <v>49.86</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>48.54</v>
+        <v>50.6</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31139,26 +31132,26 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>50.62</v>
+        <v>49.85</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>50.36</v>
+        <v>49.41</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>50.15</v>
+        <v>48.78</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>49.85</v>
+        <v>48.56</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>50.05</v>
+        <v>48.87</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>50.47</v>
+        <v>48.16</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31185,26 +31178,26 @@
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>48.61</v>
+        <v>47.54</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>48.91</v>
+        <v>48.43</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>50.51</v>
+        <v>47.93</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>50.88</v>
+        <v>46.98</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>51</v>
+        <v>47.01</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>50.95</v>
+        <v>46.92</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31231,26 +31224,26 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>68.41</v>
+        <v>67.33</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>62.58</v>
+        <v>61.14</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>58.71</v>
+        <v>57.94</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>54.75</v>
+        <v>55.31</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>51.89</v>
+        <v>51.91</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31277,26 +31270,26 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>49.36</v>
+        <v>50.89</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>50.53</v>
+        <v>52.84</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>52.29</v>
+        <v>55.1</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>54.29</v>
+        <v>55.68</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>54.5</v>
+        <v>54.31</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>50.85</v>
+        <v>53.29</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31323,26 +31316,26 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>43.49</v>
+        <v>43.89</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>42.73</v>
+        <v>45.57</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>43.54</v>
+        <v>47.56</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>44.22</v>
+        <v>49.09</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="J125" s="4" t="n">
-        <v>39.49</v>
+        <v>48.28</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>48.09</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31369,26 +31362,26 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>60.73</v>
+        <v>61.41</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>61.63</v>
+        <v>61.33</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>61.57</v>
+        <v>60.05</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>60.24</v>
+        <v>59.27</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>59.27</v>
+        <v>58.31</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>57.96</v>
+        <v>56.83</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31415,26 +31408,26 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>68.81</v>
+        <v>70.14</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>71.19</v>
+        <v>71.98</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>73.72</v>
+        <v>73.78</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>76.31999999999999</v>
+        <v>73.56</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>77.12</v>
+        <v>73.06</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>76.77</v>
+        <v>73.97</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31461,26 +31454,26 @@
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>71.7</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>74.25</v>
+        <v>74.94</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>77.51000000000001</v>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>80.54000000000001</v>
-      </c>
-      <c r="I128" s="5" t="n">
-        <v>81.98999999999999</v>
-      </c>
-      <c r="J128" s="5" t="n">
-        <v>80.27</v>
+        <v>77.54000000000001</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>78.79000000000001</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>77.65000000000001</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31507,26 +31500,26 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>45.18</v>
+        <v>46.58</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>46.37</v>
+        <v>47.7</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>47.55</v>
+        <v>48.64</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>48.53</v>
+        <v>48.44</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>48.28</v>
+        <v>47.9</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>47.09</v>
+        <v>47.06</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31553,26 +31546,26 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>77.05</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>79.45</v>
+        <v>78.87</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>80.84999999999999</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>81.54000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>83.45</v>
+        <v>84.12</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>84.7</v>
+        <v>84.17</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>84.02</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31599,26 +31592,26 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>67.83</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>72.06</v>
+        <v>67.2</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>73.38</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>73.42</v>
+        <v>60.97</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>73.76000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>72.16</v>
+        <v>54.79</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31645,26 +31638,26 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>63.86</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>63.39</v>
+        <v>64.66</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>62.68</v>
+        <v>64.42</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>61.23</v>
+        <v>63.99</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>58.87</v>
+        <v>62.03</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>53.57</v>
+        <v>61.29</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31691,26 +31684,26 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>42.15</v>
+        <v>42.23</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>41.64</v>
+        <v>43.13</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>41.95</v>
+        <v>44.32</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>42.32</v>
+        <v>44.28</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>41.43</v>
-      </c>
-      <c r="J133" s="4" t="n">
-        <v>36.61</v>
+        <v>42.07</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>40.98</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31737,26 +31730,26 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>41.33</v>
+        <v>42.64</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>43.04</v>
+        <v>42.65</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>43.14</v>
+        <v>42.21</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>42.87</v>
+        <v>42.63</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>43.54</v>
+        <v>43.25</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>43.86</v>
+        <v>41.46</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31783,26 +31776,26 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>42.67</v>
+        <v>42.18</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>42.62</v>
+        <v>41.59</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>42.16</v>
+        <v>42.74</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>43.45</v>
+        <v>44.98</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>45.88</v>
+        <v>45.97</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>46</v>
+        <v>44.94</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31829,26 +31822,26 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>45.36</v>
+        <v>49.95</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>49.78</v>
+        <v>53.45</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>52.94</v>
+        <v>55.38</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>54.35</v>
+        <v>57.75</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>55.93</v>
+        <v>60.11</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>58.83</v>
+        <v>58.27</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31875,26 +31868,26 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>49.65</v>
+        <v>54.48</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>54.5</v>
+        <v>59.88</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>59.74</v>
+        <v>63.32</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>62.99</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>65.2</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>67.62</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31921,26 +31914,26 @@
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>60.03</v>
+        <v>63.41</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>64.37</v>
+        <v>66.81</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>68.16</v>
+        <v>68.19</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>70.20999999999999</v>
+        <v>69.09</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>72.03</v>
+        <v>69.81</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>74.68000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31967,26 +31960,26 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>43.97</v>
+        <v>44.33</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>44.97</v>
+        <v>44.74</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>45.55</v>
+        <v>45.5</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>46.59</v>
+        <v>46.06</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>47.54</v>
+        <v>46.64</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>47.9</v>
+        <v>44.69</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32013,26 +32006,26 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>44.04</v>
+        <v>46.99</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>47.42</v>
+        <v>49.55</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>50.06</v>
+        <v>51.16</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>51.87</v>
+        <v>53.22</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>54.23</v>
+        <v>54.87</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>55.87</v>
+        <v>52.59</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32059,26 +32052,26 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>41.38</v>
+        <v>42.06</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>42.53</v>
+        <v>42.09</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>42.72</v>
+        <v>43.02</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>43.89</v>
+        <v>44.38</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>45.75</v>
+        <v>45.31</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>46.49</v>
+        <v>43.55</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32105,26 +32098,26 @@
         </is>
       </c>
       <c r="E142" s="3" t="n">
-        <v>55.01</v>
+        <v>59.52</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>60.52</v>
+        <v>63.78</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>65.19</v>
+        <v>66.69</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>68.73999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>73.13</v>
+        <v>72.42</v>
       </c>
       <c r="J142" s="3" t="n">
-        <v>75.81999999999999</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32151,26 +32144,26 @@
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>63.21</v>
+        <v>67.87</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>68.39</v>
+        <v>72.45</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>72.92</v>
+        <v>76.19</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>76.66</v>
+        <v>79.81</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>80.31</v>
+        <v>82.77</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>83.14</v>
+        <v>83.92</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32197,26 +32190,26 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>41.49</v>
+        <v>41.95</v>
       </c>
       <c r="F144" s="3" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="H144" s="3" t="n">
         <v>41.81</v>
       </c>
-      <c r="G144" s="3" t="n">
-        <v>40.42</v>
-      </c>
-      <c r="H144" s="4" t="n">
-        <v>39.55</v>
-      </c>
       <c r="I144" s="3" t="n">
-        <v>40.52</v>
+        <v>43.56</v>
       </c>
       <c r="J144" s="3" t="n">
-        <v>41.67</v>
+        <v>42.34</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32243,26 +32236,26 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>48.38</v>
+        <v>49.49</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>49.94</v>
+        <v>49.1</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>49.6</v>
+        <v>49.35</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>49.96</v>
+        <v>51.09</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>51.69</v>
+        <v>52.2</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>52.11</v>
+        <v>50.28</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32289,26 +32282,26 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>46.09</v>
+        <v>47.48</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>48.16</v>
+        <v>48.89</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>49.67</v>
+        <v>50.12</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>51.15</v>
+        <v>51.34</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>52.81</v>
+        <v>51.78</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>52.87</v>
+        <v>50.7</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32335,26 +32328,26 @@
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>50.91</v>
+        <v>57.03</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>57.12</v>
+        <v>62.2</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>62.06</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>63.85</v>
+        <v>67.28</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>66.72</v>
+        <v>69.44</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>69.69</v>
+        <v>69.31</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32381,26 +32374,26 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>41.99</v>
+        <v>42.93</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>43.51</v>
+        <v>44.19</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>47.18</v>
+        <v>47.28</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>48.82</v>
+        <v>48.68</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>50.09</v>
+        <v>46.89</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32427,26 +32420,26 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>59.32</v>
+        <v>58.67</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>60.01</v>
+        <v>58.93</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>60.65</v>
+        <v>58.47</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>60.79</v>
+        <v>57.1</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>60.6</v>
+        <v>56.03</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>61.79</v>
+        <v>56.99</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32473,26 +32466,26 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>49.18</v>
+        <v>50.14</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>51.06</v>
+        <v>51.26</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>52.55</v>
+        <v>51.4</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>53.12</v>
+        <v>50.6</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>52.86</v>
+        <v>54.1</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>57.23</v>
+        <v>55.19</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32519,26 +32512,26 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>49.36</v>
+        <v>51.37</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>51.56</v>
+        <v>53.12</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>53.37</v>
+        <v>53.73</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>53.99</v>
+        <v>52.85</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>53.08</v>
+        <v>54.69</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>55.72</v>
+        <v>54.75</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32565,26 +32558,26 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>52.77</v>
+        <v>52.63</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>53.28</v>
+        <v>51.99</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>52.93</v>
+        <v>51.13</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>52.41</v>
+        <v>51.53</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>53.22</v>
+        <v>52.72</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>56.25</v>
+        <v>54.89</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32611,26 +32604,26 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>52.01</v>
+        <v>51.21</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>52.27</v>
+        <v>50.82</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>52.37</v>
+        <v>52.05</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>53.87</v>
+        <v>52.97</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>55.06</v>
+        <v>54.38</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>56.43</v>
+        <v>57.63</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32657,26 +32650,26 @@
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>52.7</v>
+        <v>51.18</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>51.84</v>
+        <v>48.51</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>49.51</v>
+        <v>45.38</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>46.91</v>
+        <v>43.75</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>46.06</v>
+        <v>44.1</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>48.26</v>
+        <v>47.07</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32703,26 +32696,26 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>48.91</v>
+        <v>48.55</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>47.51</v>
+        <v>45.9</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>44.34</v>
+        <v>42.87</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>40.57</v>
-      </c>
-      <c r="I155" s="4" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="J155" s="4" t="n">
-        <v>37.25</v>
+        <v>41.74</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>42.8</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32749,26 +32742,26 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>60.85</v>
+        <v>61.79</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>62.37</v>
+        <v>62.96</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>63.6</v>
+        <v>64.25</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>64.98999999999999</v>
+        <v>66.14</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>68.13</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>69.79000000000001</v>
+        <v>70.34</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32795,26 +32788,26 @@
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>52.18</v>
+        <v>52.24</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>51.28</v>
+        <v>51.25</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>50.05</v>
+        <v>49.86</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>48.28</v>
+        <v>47.61</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>45.66</v>
+        <v>46.1</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>44.58</v>
+        <v>49.4</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32841,26 +32834,26 @@
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>51.84</v>
+        <v>52.1</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>50.89</v>
+        <v>51.32</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>49.59</v>
+        <v>50.41</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>48.09</v>
+        <v>51.07</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>47.62</v>
+        <v>51.22</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>47.73</v>
+        <v>52.66</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32887,26 +32880,26 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>55.35</v>
+        <v>54.27</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>54.03</v>
+        <v>51.92</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>51.42</v>
+        <v>48.53</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>47.82</v>
+        <v>46.54</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>45.51</v>
+        <v>44.85</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>44.42</v>
+        <v>44.78</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32933,26 +32926,26 @@
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>52.75</v>
+        <v>53.67</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>53.67</v>
+        <v>53.81</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>53.82</v>
+        <v>54.45</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>54.39</v>
+        <v>54.65</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>54.44</v>
+        <v>55.44</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>56.24</v>
+        <v>57.94</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32979,26 +32972,26 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>50.65</v>
+        <v>50.57</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>50.86</v>
+        <v>50.48</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>50.82</v>
+        <v>49.29</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>49.75</v>
+        <v>48.37</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>49.1</v>
+        <v>47.43</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>48.07</v>
+        <v>47.54</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33025,26 +33018,26 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>64.83</v>
+        <v>65.88</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>66.43000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>66.95</v>
+        <v>66.36</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>66.84</v>
+        <v>66.09</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>66.69</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>67.67</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33071,26 +33064,26 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>51.6</v>
+        <v>51.27</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>50.4</v>
+        <v>49.22</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>48.17</v>
+        <v>49.32</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>47.89</v>
+        <v>48.01</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>45.99</v>
+        <v>47.78</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>46.6</v>
+        <v>52.38</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33117,26 +33110,26 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>45.23</v>
+        <v>45.37</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>45.88</v>
+        <v>45.6</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>45.68</v>
+        <v>45.55</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>44.36</v>
+        <v>45.36</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="J164" s="4" t="n">
-        <v>38.71</v>
+        <v>43.27</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>42.74</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33163,26 +33156,26 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>48.2</v>
+        <v>48.73</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>50.24</v>
+        <v>50.51</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>52.37</v>
+        <v>51.24</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>53.04</v>
+        <v>50.47</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>51.82</v>
+        <v>48.44</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>48.48</v>
+        <v>48.1</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33209,26 +33202,26 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>41.09</v>
+        <v>42.34</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>38.98</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>36.93</v>
+        <v>37.64</v>
       </c>
       <c r="H166" s="4" t="n">
-        <v>34.58</v>
+        <v>36.84</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>32.15</v>
+        <v>35.39</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>29.33</v>
+        <v>32.93</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33255,26 +33248,26 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>30.12</v>
+        <v>28.99</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>28.75</v>
+        <v>28.52</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>28.06</v>
+        <v>29.39</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>28.51</v>
+        <v>30.68</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>29.15</v>
+        <v>32.48</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>30.89</v>
+        <v>33.65</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33301,26 +33294,26 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>43.86</v>
+        <v>42.97</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>41.22</v>
+        <v>40.76</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>37.85</v>
+        <v>39.47</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>34.92</v>
+        <v>39.26</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>32.18</v>
+        <v>38.45</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>30.86</v>
+        <v>34.57</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33347,26 +33340,26 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>25.72</v>
+        <v>23.95</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>23.39</v>
+        <v>23.17</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>22.56</v>
+        <v>24.22</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>23.58</v>
+        <v>25.78</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>25.22</v>
+        <v>28.46</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>27.58</v>
+        <v>28.56</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33393,26 +33386,26 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>58.62</v>
+        <v>55.31</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>58.31</v>
+        <v>54.83</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>58.47</v>
+        <v>52.67</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>57.68</v>
+        <v>50.4</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>57.17</v>
+        <v>48.49</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>55.65</v>
+        <v>46.83</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33438,27 +33431,27 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E171" s="3" t="n">
-        <v>41.56</v>
+      <c r="E171" s="4" t="n">
+        <v>39.8</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>39.28</v>
+        <v>37.54</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>36.7</v>
+        <v>37.71</v>
       </c>
       <c r="H171" s="4" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="I171" s="4" t="n">
-        <v>37.64</v>
+        <v>39.47</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>42.78</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>40.89</v>
+        <v>43.01</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33485,26 +33478,26 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F172" s="3" t="n">
-        <v>42.63</v>
+        <v>42.66</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>39.9</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>39.7</v>
+        <v>37.76</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>37.35</v>
+        <v>36.16</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>35.36</v>
+        <v>33.75</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>32.56</v>
+        <v>30.1</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33531,26 +33524,26 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>59.96</v>
+        <v>61.24</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>59.57</v>
+        <v>60.11</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>57.73</v>
+        <v>57.54</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>54.11</v>
+        <v>54.84</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>50.26</v>
+        <v>52.11</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>46.83</v>
+        <v>50.69</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33577,26 +33570,26 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>60.08</v>
+        <v>59.6</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>57.68</v>
+        <v>58.11</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>55.4</v>
+        <v>55.8</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>51.73</v>
+        <v>54.86</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>49.52</v>
+        <v>53.04</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>46.43</v>
+        <v>53.24</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33623,26 +33616,26 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>62.69</v>
+        <v>63.35</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>61.4</v>
+        <v>61.7</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>58.9</v>
+        <v>58.69</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>54.45</v>
+        <v>58.68</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>52.38</v>
+        <v>57.23</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>49.14</v>
+        <v>56.52</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33669,26 +33662,26 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>66.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>63.03</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>63.6</v>
+        <v>61.97</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>62.87</v>
+        <v>60.41</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>61.66</v>
+        <v>58.63</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>60.13</v>
+        <v>59.88</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33715,26 +33708,26 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>66.97</v>
+        <v>65.95</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>64.69</v>
+        <v>62.99</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>61.07</v>
+        <v>60.01</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>57.47</v>
+        <v>56.65</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>53.42</v>
+        <v>54.16</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>50.69</v>
+        <v>50.72</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33761,26 +33754,26 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>50.97</v>
+        <v>52.45</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>51.84</v>
+        <v>52.66</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>51.75</v>
+        <v>50.44</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>49.26</v>
+        <v>49.07</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>47.69</v>
+        <v>47.98</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>46.16</v>
+        <v>46.66</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33807,26 +33800,26 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>60.42</v>
+        <v>62.29</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>60.99</v>
+        <v>62.52</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>60.45</v>
+        <v>60.74</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>57.85</v>
+        <v>58.71</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>54.94</v>
+        <v>58.02</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>53.09</v>
+        <v>56.23</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33853,26 +33846,26 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>71.88</v>
+        <v>73.05</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>72.01000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>70.20999999999999</v>
+        <v>69.19</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>66.81</v>
+        <v>65.98</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>62.5</v>
+        <v>64.94</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>60.65</v>
+        <v>62.66</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33899,26 +33892,26 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>69.79000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>73.69</v>
+        <v>76.59</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>73.48999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>69.23999999999999</v>
+        <v>68.44</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>59.71</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33945,26 +33938,26 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>64.73999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>64.06999999999999</v>
+        <v>66.59</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>64.34</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>65.02</v>
+        <v>67.72</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>62.29</v>
+        <v>63.31</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>54.02</v>
+        <v>58.26</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -33991,26 +33984,26 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>72.25</v>
+        <v>68.83</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>68.73999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>64.09</v>
+        <v>59.72</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>59.33</v>
+        <v>53.59</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>53.31</v>
+        <v>47.62</v>
       </c>
       <c r="J183" s="3" t="n">
-        <v>46.78</v>
+        <v>42.47</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34037,26 +34030,26 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>58.71</v>
+        <v>58.22</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>55.59</v>
+        <v>56.14</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>52.09</v>
+        <v>54.15</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>48.62</v>
+        <v>51.25</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="J184" s="4" t="n">
-        <v>36.76</v>
+        <v>45.86</v>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>41.45</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34083,26 +34076,26 @@
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>54.37</v>
+        <v>60.2</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>57.45</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>59.74</v>
+        <v>67.72</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>60.97</v>
+        <v>69.05</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>58.56</v>
+        <v>67.34</v>
       </c>
       <c r="J185" s="3" t="n">
-        <v>54.63</v>
+        <v>65.66</v>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34129,26 +34122,26 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>69.08</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>65.65000000000001</v>
+        <v>63.93</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>63.33</v>
+        <v>61.47</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>60.58</v>
+        <v>56.85</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>55.65</v>
+        <v>49.94</v>
       </c>
       <c r="J186" s="3" t="n">
-        <v>47.02</v>
+        <v>43.75</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34175,26 +34168,26 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>62.18</v>
+        <v>61.93</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>63.22</v>
+        <v>62.59</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>64.22</v>
+        <v>62.55</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>64.67</v>
+        <v>61.23</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>64.37</v>
+        <v>60.34</v>
       </c>
       <c r="J187" s="3" t="n">
-        <v>65.62</v>
+        <v>61.1</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34221,26 +34214,26 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>49.07</v>
+        <v>49.96</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>50.9</v>
+        <v>51.01</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>52.34</v>
+        <v>51.07</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>52.9</v>
+        <v>50.24</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>52.7</v>
+        <v>53.59</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>56.94</v>
+        <v>54.66</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34267,26 +34260,26 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>52.14</v>
+        <v>54.02</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>54.43</v>
+        <v>55.7</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>56.25</v>
+        <v>55.94</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>56.69</v>
+        <v>54.68</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>55.69</v>
+        <v>56.23</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>58.2</v>
+        <v>56.02</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34313,26 +34306,26 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>53.67</v>
+        <v>53.63</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>54.29</v>
+        <v>53.15</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>54.08</v>
+        <v>52.32</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>53.61</v>
+        <v>52.67</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>54.38</v>
+        <v>53.65</v>
       </c>
       <c r="J190" s="3" t="n">
-        <v>57.17</v>
+        <v>55.77</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34359,26 +34352,26 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>52.49</v>
+        <v>51.72</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>52.77</v>
+        <v>51.3</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>52.82</v>
+        <v>52.52</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>54.31</v>
+        <v>53.41</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>55.46</v>
+        <v>54.78</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>56.79</v>
+        <v>57.98</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34405,26 +34398,26 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>54.48</v>
+        <v>53.18</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>54.11</v>
+        <v>50.62</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>52.08</v>
+        <v>47.57</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>49.83</v>
+        <v>45.87</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>49.34</v>
+        <v>45.92</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>51.34</v>
+        <v>48.79</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34451,26 +34444,26 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>69.75</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>67.28</v>
+        <v>65.33</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>63.46</v>
+        <v>61.91</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>59.36</v>
+        <v>58.6</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>55.25</v>
+        <v>55.91</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>52.32</v>
+        <v>52.24</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34497,26 +34490,26 @@
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>60.79</v>
+        <v>61.39</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>61.69</v>
+        <v>61.28</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>61.63</v>
+        <v>60.06</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>60.41</v>
+        <v>59.29</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>59.54</v>
+        <v>58.42</v>
       </c>
       <c r="J194" s="3" t="n">
-        <v>58.32</v>
+        <v>56.9</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34543,26 +34536,26 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>54.26</v>
+        <v>53.25</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>54.35</v>
+        <v>54.49</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>56.47</v>
+        <v>55.28</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>58.13</v>
+        <v>53.44</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>56.33</v>
+        <v>51.78</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>54.98</v>
+        <v>49.6</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34589,26 +34582,26 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>49.34</v>
+        <v>49.23</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>50.46</v>
+        <v>49.87</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>52.03</v>
+        <v>50.61</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>54.21</v>
+        <v>49.41</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>54.61</v>
+        <v>48.3</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>54.33</v>
+        <v>47.64</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34635,26 +34628,26 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>58.75</v>
+        <v>59.93</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>60.51</v>
+        <v>60.84</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>61.45</v>
+        <v>60.15</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>60.62</v>
+        <v>58.54</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>58.89</v>
+        <v>56.04</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>56.44</v>
+        <v>52.94</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34681,26 +34674,26 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>64.95</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>66.23</v>
+        <v>65.45</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>67.06999999999999</v>
+        <v>63.21</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>64.81999999999999</v>
+        <v>60.53</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>61.22</v>
+        <v>57.15</v>
       </c>
       <c r="J198" s="3" t="n">
-        <v>60</v>
+        <v>54.57</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34727,26 +34720,26 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>58.56</v>
+        <v>58.61</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>59.49</v>
+        <v>59.4</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>60.32</v>
+        <v>58.73</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>59.68</v>
+        <v>57.69</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>58.34</v>
+        <v>56.63</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>57.28</v>
+        <v>54.82</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34773,26 +34766,26 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>69.62</v>
+        <v>70.66</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>69.66</v>
+        <v>69.7</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>68.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>65.31</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>61.37</v>
+        <v>63.44</v>
       </c>
       <c r="J200" s="3" t="n">
-        <v>59.68</v>
+        <v>61.56</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34819,26 +34812,26 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>63.22</v>
+        <v>63.84</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>64.05</v>
+        <v>64.88</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>64.98999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>63.34</v>
+        <v>61.75</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>61.35</v>
+        <v>61.93</v>
       </c>
       <c r="J201" s="3" t="n">
-        <v>61.47</v>
+        <v>61.52</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34865,26 +34858,26 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>38.97</v>
+        <v>39.04</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>37.7</v>
+        <v>38.34</v>
       </c>
       <c r="G202" s="4" t="n">
-        <v>36.07</v>
+        <v>37.24</v>
       </c>
       <c r="H202" s="4" t="n">
-        <v>33.65</v>
+        <v>36.83</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>31.32</v>
+        <v>36.59</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>29.21</v>
+        <v>38.22</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34911,26 +34904,26 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>48.27</v>
+        <v>47.45</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>45.92</v>
+        <v>44.68</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>42.19</v>
+        <v>40.85</v>
       </c>
       <c r="H203" s="4" t="n">
-        <v>37.08</v>
+        <v>37.7</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>32.24</v>
+        <v>35.51</v>
       </c>
       <c r="J203" s="4" t="n">
-        <v>30.32</v>
+        <v>34.13</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34957,26 +34950,26 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>45.82</v>
+        <v>46.81</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>45.13</v>
+        <v>46.1</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>43.24</v>
-      </c>
-      <c r="H204" s="4" t="n">
-        <v>38.91</v>
+        <v>43.44</v>
+      </c>
+      <c r="H204" s="3" t="n">
+        <v>40.68</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>33.84</v>
+        <v>38.87</v>
       </c>
       <c r="J204" s="4" t="n">
-        <v>31.06</v>
+        <v>39.62</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35003,26 +34996,26 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>55.16</v>
+        <v>56.24</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>55.49</v>
+        <v>56.48</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>55.07</v>
+        <v>55.71</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>53.45</v>
+        <v>53.67</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>50.15</v>
+        <v>48.02</v>
       </c>
       <c r="J205" s="3" t="n">
-        <v>45.99</v>
+        <v>40.39</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35049,26 +35042,26 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>65.33</v>
+        <v>66.66</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>64.65000000000001</v>
+        <v>66.27</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>62.94</v>
+        <v>63.95</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>58.82</v>
+        <v>60.79</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>53.26</v>
+        <v>54.36</v>
       </c>
       <c r="J206" s="3" t="n">
-        <v>47.28</v>
+        <v>47.31</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35095,26 +35088,26 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>65.89</v>
+        <v>65.88</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>64.01000000000001</v>
+        <v>65.37</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>62.25</v>
+        <v>63.92</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>58.98</v>
+        <v>61.29</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>53.86</v>
+        <v>57.51</v>
       </c>
       <c r="J207" s="3" t="n">
-        <v>50.71</v>
+        <v>51.44</v>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35141,26 +35134,26 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>70</v>
+        <v>73.42</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>72.11</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>73.52</v>
+        <v>76.44</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>73.06999999999999</v>
+        <v>74</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>68.68000000000001</v>
+        <v>68.14</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>64</v>
+        <v>59.41</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35187,26 +35180,26 @@
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>78.36</v>
+        <v>76.92</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>76.48</v>
+        <v>74.06</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>73.19</v>
+        <v>69.52</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>68.34</v>
+        <v>64.52</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>63.13</v>
+        <v>56.76</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>55.87</v>
+        <v>50.39</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35233,26 +35226,26 @@
         </is>
       </c>
       <c r="E210" s="3" t="n">
-        <v>50.68</v>
+        <v>50.14</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>49.72</v>
+        <v>48.52</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>47.92</v>
+        <v>46.46</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>45.76</v>
+        <v>46.52</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>45.52</v>
+        <v>47.4</v>
       </c>
       <c r="J210" s="3" t="n">
-        <v>46.23</v>
+        <v>49.01</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35279,26 +35272,26 @@
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>51.09</v>
+        <v>51.46</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>50.95</v>
+        <v>51.51</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>50.51</v>
+        <v>52.41</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>50.79</v>
+        <v>53.66</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>51.25</v>
+        <v>53.73</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>50.25</v>
+        <v>54.31</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35325,26 +35318,26 @@
         </is>
       </c>
       <c r="E212" s="3" t="n">
-        <v>51.85</v>
+        <v>51.97</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>50.95</v>
+        <v>51.11</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>49.78</v>
+        <v>50.1</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>48.26</v>
+        <v>48.4</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>45.94</v>
+        <v>47.18</v>
       </c>
       <c r="J212" s="3" t="n">
-        <v>45.19</v>
+        <v>50.33</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35371,26 +35364,26 @@
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>52.39</v>
+        <v>53.07</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>51.68</v>
+        <v>52.49</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>50.45</v>
+        <v>51.84</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>48.97</v>
+        <v>52.6</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>48.28</v>
+        <v>52.58</v>
       </c>
       <c r="J213" s="3" t="n">
-        <v>48.17</v>
+        <v>54.05</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35417,26 +35410,26 @@
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>55.61</v>
+        <v>54.57</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>54.3</v>
+        <v>52.24</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>51.71</v>
+        <v>48.85</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>48.09</v>
+        <v>46.85</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>45.76</v>
+        <v>45.12</v>
       </c>
       <c r="J214" s="3" t="n">
-        <v>44.62</v>
+        <v>45.07</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35463,26 +35456,26 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>51.94</v>
+        <v>53.42</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>53.65</v>
+        <v>54.24</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>54.37</v>
+        <v>54.65</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>54.61</v>
+        <v>56.22</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>55.97</v>
+        <v>55.74</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>54.25</v>
+        <v>57.41</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35509,26 +35502,26 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>50.79</v>
+        <v>50.75</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>50.98</v>
+        <v>50.82</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>51.05</v>
+        <v>49.85</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>50.14</v>
+        <v>49.15</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>49.63</v>
+        <v>48.35</v>
       </c>
       <c r="J216" s="3" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35555,26 +35548,26 @@
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>64.20999999999999</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>65.73</v>
+        <v>65.83</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>66.25</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>66.14</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>65.48</v>
       </c>
       <c r="J217" s="3" t="n">
-        <v>66.89</v>
+        <v>65.44</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35601,26 +35594,26 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>32.55</v>
+        <v>33.13</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>31.85</v>
+        <v>34.06</v>
       </c>
       <c r="G218" s="4" t="n">
-        <v>32.01</v>
+        <v>34.51</v>
       </c>
       <c r="H218" s="4" t="n">
-        <v>31.22</v>
+        <v>36.02</v>
       </c>
       <c r="I218" s="4" t="n">
-        <v>30.71</v>
+        <v>37.69</v>
       </c>
       <c r="J218" s="4" t="n">
-        <v>30.49</v>
+        <v>35.4</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35647,26 +35640,26 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="G219" s="3" t="n">
         <v>50.64</v>
       </c>
-      <c r="F219" s="3" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="G219" s="3" t="n">
-        <v>49.75</v>
-      </c>
       <c r="H219" s="3" t="n">
-        <v>49.12</v>
+        <v>50.8</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>48.33</v>
+        <v>50.83</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>46.29</v>
+        <v>48.28</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35693,26 +35686,26 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>50.81</v>
+        <v>49.73</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>49.09</v>
+        <v>48.81</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>47.9</v>
+        <v>45.77</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>44.43</v>
+        <v>44.85</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>42.58</v>
+        <v>44.04</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>40.44</v>
+        <v>41.47</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35739,26 +35732,26 @@
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>38.55</v>
+        <v>39.06</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>38.19</v>
+        <v>38.59</v>
       </c>
       <c r="G221" s="4" t="n">
-        <v>37.28</v>
+        <v>38.53</v>
       </c>
       <c r="H221" s="4" t="n">
-        <v>36.57</v>
+        <v>38.96</v>
       </c>
       <c r="I221" s="4" t="n">
-        <v>35.97</v>
+        <v>38.23</v>
       </c>
       <c r="J221" s="4" t="n">
-        <v>33.48</v>
+        <v>35.4</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35785,26 +35778,26 @@
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>41.33</v>
+        <v>42.64</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>43.04</v>
+        <v>42.65</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>43.14</v>
+        <v>42.21</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>42.87</v>
+        <v>42.63</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>43.54</v>
+        <v>43.25</v>
       </c>
       <c r="J222" s="3" t="n">
-        <v>43.86</v>
+        <v>41.46</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35831,26 +35824,26 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>49.55</v>
+        <v>51.14</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>51.59</v>
+        <v>51.69</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>52.11</v>
+        <v>51.88</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>52.23</v>
+        <v>51.6</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>51.66</v>
+        <v>51.91</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>51.57</v>
+        <v>50.31</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35877,26 +35870,26 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>45.36</v>
+        <v>49.95</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>49.78</v>
+        <v>53.45</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>52.94</v>
+        <v>55.38</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>54.35</v>
+        <v>57.75</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>55.93</v>
+        <v>60.11</v>
       </c>
       <c r="J224" s="3" t="n">
-        <v>58.83</v>
+        <v>58.27</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35923,26 +35916,26 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>49.65</v>
+        <v>54.48</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>54.5</v>
+        <v>59.88</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>59.74</v>
+        <v>63.32</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>62.99</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>65.2</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="J225" s="3" t="n">
-        <v>67.62</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35969,26 +35962,26 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>46.55</v>
+        <v>50.36</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>50.81</v>
+        <v>53.49</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>54.19</v>
+        <v>55.91</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>56.9</v>
+        <v>58.25</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>59.34</v>
+        <v>59.98</v>
       </c>
       <c r="J226" s="3" t="n">
-        <v>60.58</v>
+        <v>57.99</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36015,26 +36008,26 @@
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>60.03</v>
+        <v>63.41</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>64.37</v>
+        <v>66.81</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>68.16</v>
+        <v>68.19</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>70.20999999999999</v>
+        <v>69.09</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>72.03</v>
+        <v>69.81</v>
       </c>
       <c r="J227" s="3" t="n">
-        <v>74.68000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36061,26 +36054,26 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>44.04</v>
+        <v>46.99</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>47.42</v>
+        <v>49.55</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>50.06</v>
+        <v>51.16</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>51.87</v>
+        <v>53.22</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>54.23</v>
+        <v>54.87</v>
       </c>
       <c r="J228" s="3" t="n">
-        <v>55.87</v>
+        <v>52.59</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36107,26 +36100,26 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>44.04</v>
+        <v>46.99</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>47.42</v>
+        <v>49.55</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>50.06</v>
+        <v>51.16</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>51.87</v>
+        <v>53.22</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>54.23</v>
+        <v>54.87</v>
       </c>
       <c r="J229" s="3" t="n">
-        <v>55.87</v>
+        <v>52.59</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36153,26 +36146,26 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>50.12</v>
+        <v>53.87</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>54.33</v>
+        <v>57.24</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>57.89</v>
+        <v>59.08</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>59.83</v>
+        <v>60.21</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>60.83</v>
+        <v>59.27</v>
       </c>
       <c r="J230" s="3" t="n">
-        <v>60.87</v>
+        <v>57</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36199,26 +36192,26 @@
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>63.21</v>
+        <v>67.87</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>68.39</v>
+        <v>72.45</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>72.92</v>
+        <v>76.19</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>76.66</v>
+        <v>79.81</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>80.31</v>
+        <v>82.77</v>
       </c>
       <c r="J231" s="5" t="n">
-        <v>83.14</v>
+        <v>83.92</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36245,26 +36238,26 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>41.49</v>
+        <v>41.95</v>
       </c>
       <c r="F232" s="3" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="G232" s="3" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="H232" s="3" t="n">
         <v>41.81</v>
       </c>
-      <c r="G232" s="3" t="n">
-        <v>40.42</v>
-      </c>
-      <c r="H232" s="4" t="n">
-        <v>39.55</v>
-      </c>
       <c r="I232" s="3" t="n">
-        <v>40.52</v>
+        <v>43.56</v>
       </c>
       <c r="J232" s="3" t="n">
-        <v>41.67</v>
+        <v>42.34</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36291,26 +36284,26 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>48.38</v>
+        <v>49.49</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>49.94</v>
+        <v>49.1</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>49.6</v>
+        <v>49.35</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>49.96</v>
+        <v>51.09</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>51.69</v>
+        <v>52.2</v>
       </c>
       <c r="J233" s="3" t="n">
-        <v>52.11</v>
+        <v>50.28</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36337,26 +36330,26 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>46.09</v>
+        <v>47.48</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>48.16</v>
+        <v>48.89</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>49.67</v>
+        <v>50.12</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>51.15</v>
+        <v>51.34</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>52.81</v>
+        <v>51.78</v>
       </c>
       <c r="J234" s="3" t="n">
-        <v>52.87</v>
+        <v>50.7</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36383,26 +36376,26 @@
         </is>
       </c>
       <c r="E235" s="3" t="n">
-        <v>50.91</v>
+        <v>57.03</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>57.12</v>
+        <v>62.2</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>62.06</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>63.85</v>
+        <v>67.28</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>66.72</v>
+        <v>69.44</v>
       </c>
       <c r="J235" s="3" t="n">
-        <v>69.69</v>
+        <v>69.31</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36429,26 +36422,26 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>50.44</v>
+        <v>50.72</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>51.27</v>
+        <v>51.5</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>52.32</v>
+        <v>52.7</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>53.88</v>
+        <v>54.74</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>56.04</v>
+        <v>55.52</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36475,26 +36468,26 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>46.84</v>
+        <v>50.36</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>49.57</v>
+        <v>53.51</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>52.22</v>
+        <v>57.17</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>55.09</v>
+        <v>60.97</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>57.56</v>
+        <v>63.85</v>
       </c>
       <c r="J237" s="3" t="n">
-        <v>59.78</v>
+        <v>64.34</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36521,26 +36514,26 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>71.44</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>70.95</v>
+        <v>71.84</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>72.39</v>
+        <v>72.86</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>73.67</v>
+        <v>73.66</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>74.70999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="J238" s="3" t="n">
-        <v>75.54000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36567,26 +36560,26 @@
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>72.27</v>
+        <v>72.92</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>73.25</v>
+        <v>70.84</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>71.12</v>
+        <v>68.56</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>68.83</v>
+        <v>66.81</v>
       </c>
       <c r="I239" s="3" t="n">
         <v>66.72</v>
       </c>
       <c r="J239" s="3" t="n">
-        <v>67.86</v>
+        <v>67.61</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36613,26 +36606,26 @@
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>60.62</v>
+        <v>61.59</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>62.16</v>
+        <v>62.76</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>63.39</v>
+        <v>64.03</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>64.76000000000001</v>
+        <v>65.88</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>66.81999999999999</v>
+        <v>67.81</v>
       </c>
       <c r="J240" s="3" t="n">
-        <v>69.47</v>
+        <v>69.97</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36659,26 +36652,26 @@
         </is>
       </c>
       <c r="E241" s="3" t="n">
-        <v>52.27</v>
+        <v>52.38</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>51.42</v>
+        <v>51.44</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>50.23</v>
+        <v>50.07</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>48.47</v>
+        <v>47.83</v>
       </c>
       <c r="I241" s="3" t="n">
-        <v>45.83</v>
+        <v>46.29</v>
       </c>
       <c r="J241" s="3" t="n">
-        <v>44.79</v>
+        <v>49.52</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36705,26 +36698,26 @@
         </is>
       </c>
       <c r="E242" s="3" t="n">
-        <v>55.4</v>
+        <v>54.31</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>54.06</v>
+        <v>51.94</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>51.44</v>
+        <v>48.53</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>47.82</v>
+        <v>46.53</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>45.51</v>
+        <v>44.8</v>
       </c>
       <c r="J242" s="3" t="n">
-        <v>44.4</v>
+        <v>44.72</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36751,26 +36744,26 @@
         </is>
       </c>
       <c r="E243" s="3" t="n">
-        <v>64.58</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>66.14</v>
+        <v>66.23</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>66.67</v>
+        <v>66.12</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>66.56999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>66.45999999999999</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="J243" s="3" t="n">
-        <v>67.42</v>
+        <v>66.02</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36797,26 +36790,26 @@
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>51.77</v>
+        <v>51.34</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>50.53</v>
+        <v>49.13</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>48.19</v>
+        <v>49.3</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>48.05</v>
+        <v>47.79</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>46.09</v>
+        <v>47.38</v>
       </c>
       <c r="J244" s="3" t="n">
-        <v>46.68</v>
+        <v>52.09</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36843,26 +36836,26 @@
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>60.15</v>
+        <v>61.41</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>59.77</v>
+        <v>60.29</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>57.95</v>
+        <v>57.72</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>54.36</v>
+        <v>54.94</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>50.47</v>
+        <v>52.13</v>
       </c>
       <c r="J245" s="3" t="n">
-        <v>47.01</v>
+        <v>50.65</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36889,26 +36882,26 @@
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>59.03</v>
+        <v>57.25</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>55.67</v>
+        <v>53.91</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>51.58</v>
+        <v>50.71</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>47.29</v>
+        <v>49.56</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>44.98</v>
+        <v>47.43</v>
       </c>
       <c r="J246" s="3" t="n">
-        <v>41.89</v>
+        <v>47.83</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36935,26 +36928,26 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>62.94</v>
+        <v>63.57</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>61.64</v>
+        <v>61.91</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>59.15</v>
+        <v>58.86</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>54.66</v>
+        <v>58.78</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>52.56</v>
+        <v>57.25</v>
       </c>
       <c r="J247" s="3" t="n">
-        <v>49.25</v>
+        <v>56.5</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36981,26 +36974,26 @@
         </is>
       </c>
       <c r="E248" s="3" t="n">
-        <v>42.42</v>
+        <v>40.4</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>39.15</v>
+        <v>37.78</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>36.03</v>
-      </c>
-      <c r="H248" s="4" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="I248" s="4" t="n">
-        <v>36.23</v>
-      </c>
-      <c r="J248" s="4" t="n">
-        <v>32.02</v>
+        <v>37.96</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="I248" s="3" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="J248" s="3" t="n">
+        <v>40.66</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37027,26 +37020,26 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>25.53</v>
+        <v>26.28</v>
       </c>
       <c r="F249" s="4" t="n">
         <v>25.7</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>24.91</v>
+        <v>26.69</v>
       </c>
       <c r="H249" s="4" t="n">
-        <v>25.56</v>
+        <v>29.48</v>
       </c>
       <c r="I249" s="4" t="n">
-        <v>27.76</v>
+        <v>29.66</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>24.54</v>
+        <v>27.78</v>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37073,26 +37066,26 @@
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>45.09</v>
+        <v>45.78</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>43.45</v>
+        <v>44.51</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="H250" s="4" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="I250" s="4" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="J250" s="4" t="n">
-        <v>35.05</v>
+        <v>44.6</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="I250" s="3" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="J250" s="3" t="n">
+        <v>50.37</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37119,26 +37112,26 @@
         </is>
       </c>
       <c r="E251" s="3" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="F251" s="3" t="n">
-        <v>40.02</v>
+        <v>40.45</v>
+      </c>
+      <c r="F251" s="4" t="n">
+        <v>36.72</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>36.21</v>
+        <v>34.51</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>33.99</v>
+        <v>34.58</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>33.91</v>
+        <v>32.8</v>
       </c>
       <c r="J251" s="4" t="n">
-        <v>28.68</v>
+        <v>31.37</v>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37165,26 +37158,26 @@
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>36.57</v>
+        <v>39.09</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>38.43</v>
+        <v>39.83</v>
       </c>
       <c r="G252" s="4" t="n">
-        <v>39.01</v>
+        <v>39.54</v>
       </c>
       <c r="H252" s="4" t="n">
-        <v>38.56</v>
+        <v>39.9</v>
       </c>
       <c r="I252" s="4" t="n">
-        <v>38.7</v>
+        <v>38.44</v>
       </c>
       <c r="J252" s="4" t="n">
-        <v>33.97</v>
+        <v>37.16</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37211,26 +37204,26 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>33.02</v>
+        <v>33.47</v>
       </c>
       <c r="F253" s="4" t="n">
-        <v>32.68</v>
+        <v>32.76</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>31.54</v>
+        <v>32</v>
       </c>
       <c r="H253" s="4" t="n">
-        <v>30.12</v>
+        <v>31.65</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>28.72</v>
+        <v>31.08</v>
       </c>
       <c r="J253" s="4" t="n">
-        <v>24.2</v>
+        <v>29.6</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37257,26 +37250,26 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>30.71</v>
+        <v>31.78</v>
       </c>
       <c r="F254" s="4" t="n">
-        <v>30.52</v>
+        <v>30.21</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>28.46</v>
+        <v>30.26</v>
       </c>
       <c r="H254" s="4" t="n">
-        <v>27.83</v>
+        <v>32.08</v>
       </c>
       <c r="I254" s="4" t="n">
-        <v>28.68</v>
+        <v>31.89</v>
       </c>
       <c r="J254" s="4" t="n">
-        <v>25.27</v>
+        <v>31.07</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37303,26 +37296,26 @@
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>40.32</v>
+        <v>40.24</v>
       </c>
       <c r="F255" s="4" t="n">
-        <v>39.67</v>
+        <v>39.41</v>
       </c>
       <c r="G255" s="4" t="n">
-        <v>38.64</v>
-      </c>
-      <c r="H255" s="4" t="n">
-        <v>38.51</v>
+        <v>39.53</v>
+      </c>
+      <c r="H255" s="3" t="n">
+        <v>40.29</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>38.94</v>
+        <v>39.45</v>
       </c>
       <c r="J255" s="4" t="n">
-        <v>35.36</v>
+        <v>36.14</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37348,27 +37341,27 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E256" s="3" t="n">
-        <v>43.35</v>
+      <c r="E256" s="4" t="n">
+        <v>39.88</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>38.68</v>
+        <v>34.94</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>33.11</v>
+        <v>31.59</v>
       </c>
       <c r="H256" s="4" t="n">
-        <v>28.91</v>
+        <v>29.69</v>
       </c>
       <c r="I256" s="4" t="n">
-        <v>25.72</v>
+        <v>28.48</v>
       </c>
       <c r="J256" s="4" t="n">
-        <v>21.25</v>
+        <v>26.7</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37395,26 +37388,26 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>24.27</v>
+        <v>23.01</v>
       </c>
       <c r="F257" s="4" t="n">
-        <v>22.26</v>
+        <v>21.74</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="H257" s="6" t="n">
-        <v>19.37</v>
-      </c>
-      <c r="I257" s="6" t="n">
-        <v>19.27</v>
-      </c>
-      <c r="J257" s="6" t="n">
-        <v>14.79</v>
+        <v>20.61</v>
+      </c>
+      <c r="H257" s="4" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="I257" s="4" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="J257" s="4" t="n">
+        <v>20.81</v>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37441,26 +37434,26 @@
         </is>
       </c>
       <c r="E258" s="3" t="n">
-        <v>40.77</v>
+        <v>41.19</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="G258" s="4" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="H258" s="4" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="I258" s="4" t="n">
-        <v>39.09</v>
-      </c>
-      <c r="J258" s="4" t="n">
-        <v>35.73</v>
+        <v>41.23</v>
+      </c>
+      <c r="G258" s="3" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="H258" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="I258" s="3" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="J258" s="3" t="n">
+        <v>41.7</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37487,26 +37480,26 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>50.61</v>
+        <v>49.67</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>49.11</v>
+        <v>46.98</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>46.04</v>
+        <v>44.97</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>43.5</v>
+        <v>43.35</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>41.15</v>
+        <v>41.75</v>
       </c>
       <c r="J259" s="4" t="n">
-        <v>37.11</v>
+        <v>38.48</v>
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37533,26 +37526,26 @@
         </is>
       </c>
       <c r="E260" s="3" t="n">
-        <v>45.31</v>
+        <v>46</v>
       </c>
       <c r="F260" s="3" t="n">
-        <v>44.81</v>
+        <v>45.78</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>43.93</v>
+        <v>45.53</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>42.73</v>
+        <v>46.68</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>42.26</v>
-      </c>
-      <c r="J260" s="4" t="n">
-        <v>38.74</v>
+        <v>46.48</v>
+      </c>
+      <c r="J260" s="3" t="n">
+        <v>45.22</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37579,26 +37572,26 @@
         </is>
       </c>
       <c r="E261" s="4" t="n">
-        <v>37.1</v>
+        <v>37.56</v>
       </c>
       <c r="F261" s="4" t="n">
-        <v>36.75</v>
+        <v>36.81</v>
       </c>
       <c r="G261" s="4" t="n">
-        <v>35.75</v>
+        <v>36.32</v>
       </c>
       <c r="H261" s="4" t="n">
-        <v>34.86</v>
+        <v>37.13</v>
       </c>
       <c r="I261" s="4" t="n">
-        <v>34.99</v>
+        <v>37.06</v>
       </c>
       <c r="J261" s="4" t="n">
-        <v>31.04</v>
+        <v>36.5</v>
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37624,27 +37617,27 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E262" s="3" t="n">
-        <v>40.94</v>
+      <c r="E262" s="4" t="n">
+        <v>39.33</v>
       </c>
       <c r="F262" s="4" t="n">
-        <v>38.22</v>
+        <v>37.03</v>
       </c>
       <c r="G262" s="4" t="n">
-        <v>35.34</v>
+        <v>36.58</v>
       </c>
       <c r="H262" s="4" t="n">
-        <v>33.97</v>
+        <v>38.07</v>
       </c>
       <c r="I262" s="4" t="n">
-        <v>34.07</v>
+        <v>39.07</v>
       </c>
       <c r="J262" s="4" t="n">
-        <v>31.16</v>
+        <v>37.89</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37671,26 +37664,26 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>49.84</v>
+        <v>50.67</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>51.9</v>
+        <v>51.28</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>53.18</v>
+        <v>51.41</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>54.1</v>
+        <v>50.77</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>54.5</v>
+        <v>51.89</v>
       </c>
       <c r="J263" s="3" t="n">
-        <v>56.48</v>
+        <v>52.81</v>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37717,26 +37710,26 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>54.1</v>
+        <v>54.15</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>54.91</v>
+        <v>53.67</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>54.76</v>
+        <v>52.85</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>54.36</v>
+        <v>53.21</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>55.26</v>
+        <v>54.13</v>
       </c>
       <c r="J264" s="3" t="n">
-        <v>57.86</v>
+        <v>56.28</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37763,26 +37756,26 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>52.77</v>
+        <v>52.94</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>53.68</v>
+        <v>52.71</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>53.8</v>
+        <v>53.13</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>54.52</v>
+        <v>53.77</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>55.44</v>
+        <v>54.8</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>56.79</v>
+        <v>57.59</v>
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37809,26 +37802,26 @@
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>54.07</v>
+        <v>52.63</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>53.3</v>
+        <v>49.98</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>50.99</v>
+        <v>46.8</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>48.37</v>
+        <v>45.18</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>47.58</v>
+        <v>45.41</v>
       </c>
       <c r="J266" s="3" t="n">
-        <v>49.69</v>
+        <v>48.2</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37855,26 +37848,26 @@
         </is>
       </c>
       <c r="E267" s="4" t="n">
-        <v>28.95</v>
+        <v>27.7</v>
       </c>
       <c r="F267" s="4" t="n">
-        <v>27.5</v>
+        <v>27.18</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>26.81</v>
+        <v>28.22</v>
       </c>
       <c r="H267" s="4" t="n">
-        <v>27.49</v>
+        <v>29.58</v>
       </c>
       <c r="I267" s="4" t="n">
-        <v>28.33</v>
+        <v>31.39</v>
       </c>
       <c r="J267" s="4" t="n">
-        <v>30.09</v>
+        <v>32.76</v>
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37901,26 +37894,26 @@
         </is>
       </c>
       <c r="E268" s="3" t="n">
-        <v>40.58</v>
+        <v>40.19</v>
       </c>
       <c r="F268" s="3" t="n">
-        <v>40.36</v>
+        <v>40.79</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>41</v>
+        <v>41.66</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>41.92</v>
+        <v>42.75</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>43.09</v>
+        <v>43.8</v>
       </c>
       <c r="J268" s="3" t="n">
-        <v>42.71</v>
+        <v>45.69</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25597,32 +25597,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -25658,22 +25658,22 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>43.56</v>
+        <v>47.34</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>45.09</v>
+        <v>50.53</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>46.98</v>
+        <v>53.73</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>48.42</v>
+        <v>55.5</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>47.61</v>
+        <v>56.14</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>47.63</v>
+        <v>52.28</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -25704,22 +25704,22 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>61.36</v>
+        <v>63.19</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>61.44</v>
+        <v>62.54</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>60.23</v>
+        <v>62.79</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>59.55</v>
+        <v>63.17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>58.64</v>
+        <v>62.5</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>57.17</v>
+        <v>60.35</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -25750,22 +25750,22 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>55.5</v>
+        <v>57.01</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>56.44</v>
+        <v>58.16</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>56.99</v>
+        <v>56.4</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>54.9</v>
+        <v>55.53</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>53.28</v>
+        <v>53.99</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>51.58</v>
+        <v>52.05</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -25796,22 +25796,22 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>67.67</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>67.09</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>64.39</v>
+        <v>61.96</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>60.95</v>
+        <v>57.95</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>56.71</v>
+        <v>54.03</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>54.76</v>
+        <v>52.41</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -25842,22 +25842,22 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>44.42</v>
+        <v>46.21</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>45.56</v>
+        <v>47.72</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>46.69</v>
+        <v>48</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>46.39</v>
+        <v>46.26</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>43.7</v>
+        <v>45.19</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>42.08</v>
+        <v>41.72</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -25888,22 +25888,22 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>52.49</v>
+        <v>55.59</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>53.58</v>
+        <v>55.84</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>52.78</v>
+        <v>53.98</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>49.14</v>
+        <v>53.25</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>46.05</v>
+        <v>52.43</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>43.85</v>
+        <v>54.66</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -25934,22 +25934,22 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>59</v>
+        <v>60.33</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>59.24</v>
+        <v>60.4</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>58.9</v>
+        <v>59.87</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>57.45</v>
+        <v>60.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>56.48</v>
+        <v>62.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>57.33</v>
+        <v>68.12</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -25980,22 +25980,22 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>45.78</v>
+        <v>43.98</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>44.72</v>
+        <v>43.75</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44.79</v>
+        <v>44.99</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>46.62</v>
+        <v>47.62</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>49.91</v>
+        <v>51.45</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>54.05</v>
+        <v>54.62</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -26026,22 +26026,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>51.91</v>
+        <v>54.02</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>53.61</v>
+        <v>54.79</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>54.2</v>
+        <v>54.25</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>53.38</v>
+        <v>56.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>55.03</v>
+        <v>57.25</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>54.97</v>
+        <v>58.89</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -26072,22 +26072,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>52.95</v>
+        <v>52.76</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>52.4</v>
+        <v>51.85</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>51.52</v>
+        <v>52.25</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>51.87</v>
+        <v>53.38</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>52.91</v>
+        <v>55.39</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>55.01</v>
+        <v>60.12</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -26118,22 +26118,22 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>51.83</v>
+        <v>52.82</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>51.67</v>
+        <v>53.67</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>52.13</v>
+        <v>54.85</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>52.5</v>
+        <v>56.75</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>53.21</v>
+        <v>59.93</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>56.44</v>
+        <v>64.63</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -26164,22 +26164,22 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>51.58</v>
+        <v>49.51</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>48.9</v>
+        <v>46.54</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45.77</v>
+        <v>45.21</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>44.14</v>
+        <v>46.03</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>44.46</v>
+        <v>48.86</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>47.4</v>
+        <v>54.89</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -26210,22 +26210,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>45.47</v>
+        <v>47.64</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>45.72</v>
+        <v>48.52</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45.7</v>
+        <v>49.81</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>45.54</v>
+        <v>49.94</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>43.48</v>
+        <v>50.79</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>42.96</v>
+        <v>49.89</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -26256,22 +26256,22 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>48.68</v>
+        <v>51.66</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>50.44</v>
+        <v>53.07</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>51.19</v>
+        <v>53.22</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>50.41</v>
+        <v>52.57</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>48.35</v>
+        <v>51.85</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>48.02</v>
+        <v>49.77</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -26302,22 +26302,22 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>42.34</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>38.98</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>37.64</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>35.39</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>32.93</v>
+        <v>40.93</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>41.18</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -26348,22 +26348,22 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>42.91</v>
+        <v>42.01</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>39.18</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>38.93</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>38.13</v>
+        <v>40.97</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>41.37</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>34.24</v>
+        <v>39.94</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -26394,22 +26394,22 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>48.83</v>
+        <v>49.17</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>49.21</v>
+        <v>48.05</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48.28</v>
+        <v>48.76</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>49.28</v>
+        <v>51.04</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>51.78</v>
+        <v>53.3</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>52.65</v>
+        <v>55.82</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -26440,22 +26440,22 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>25.24</v>
+        <v>25.7</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>24.74</v>
+        <v>27.4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>26.27</v>
+        <v>29.39</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>28.12</v>
+        <v>32.18</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>30.71</v>
+        <v>34.41</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>30.44</v>
+        <v>35.63</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -26486,22 +26486,22 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>43.85</v>
+        <v>42.55</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>41.73</v>
+        <v>40.73</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>39.78</v>
+        <v>39.3</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>38.16</v>
+        <v>38.85</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>37.61</v>
+        <v>38.62</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>35.71</v>
+        <v>36.92</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -26532,22 +26532,22 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>37.87</v>
+        <v>35.97</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>35.91</v>
+        <v>36.01</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>36.46</v>
+        <v>36.6</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>37.81</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>39.78</v>
+        <v>38.12</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>40.64</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -26578,22 +26578,22 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>61.25</v>
+        <v>60.3</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>60.14</v>
+        <v>57.99</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>57.58</v>
+        <v>55.78</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>54.88</v>
+        <v>53.99</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>52.14</v>
+        <v>53.06</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>50.71</v>
+        <v>53.01</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -26624,22 +26624,22 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>59.42</v>
+        <v>57.93</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>57.91</v>
+        <v>55.94</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>55.59</v>
+        <v>55.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>54.68</v>
+        <v>55.18</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>52.9</v>
+        <v>55.21</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>53.08</v>
+        <v>55.94</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -26670,22 +26670,22 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>63.25</v>
+        <v>62.18</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>61.58</v>
+        <v>59.62</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>58.58</v>
+        <v>60.53</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>58.61</v>
+        <v>60.35</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>57.17</v>
+        <v>60.54</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>56.5</v>
+        <v>62</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -26716,22 +26716,22 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>64.65000000000001</v>
+        <v>63.57</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>62.73</v>
+        <v>62.98</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>61.55</v>
+        <v>62.36</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>59.95</v>
+        <v>61.66</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>58.11</v>
+        <v>62.15</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>59.3</v>
+        <v>63.72</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -26762,22 +26762,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>50.41</v>
+        <v>49.83</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>51.13</v>
+        <v>50.43</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>52.54</v>
+        <v>51.43</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>54.74</v>
+        <v>51.19</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>55.87</v>
+        <v>51.31</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>54.11</v>
+        <v>52.35</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -26808,22 +26808,22 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>56.76</v>
+        <v>57.92</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>58.42</v>
+        <v>58.82</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>59.52</v>
+        <v>62.72</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>63.52</v>
+        <v>65.64</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>66.13</v>
+        <v>66.73</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>65.11</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -26854,22 +26854,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>50.56</v>
+        <v>52.58</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>53.84</v>
+        <v>55.51</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>57.38</v>
+        <v>58.51</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>61.27</v>
+        <v>60.55</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>64.26000000000001</v>
+        <v>63.02</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.47</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -26900,22 +26900,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>70.03</v>
+        <v>70.78</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>71.28</v>
+        <v>71.72</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>72.28</v>
+        <v>72.45</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>73.19</v>
+        <v>73.39</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>74.43000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>74.3</v>
+        <v>73.05</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -26946,22 +26946,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>72.81</v>
+        <v>70.62</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>71.39</v>
+        <v>67.27</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>68.42</v>
+        <v>64.41</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>66.14</v>
+        <v>62.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>60.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>63.45</v>
+        <v>61.71</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -26992,22 +26992,22 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>52.57</v>
+        <v>53.98</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>53.05</v>
+        <v>54.04</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>52.48</v>
+        <v>54.14</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>51.61</v>
+        <v>53.77</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>49.64</v>
+        <v>52.08</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>45.94</v>
+        <v>50.05</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -27038,22 +27038,22 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>58.16</v>
+        <v>58.45</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>59.88</v>
+        <v>59.64</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>61.5</v>
+        <v>59.8</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>62.24</v>
+        <v>58.79</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>61.24</v>
+        <v>57.96</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>59.53</v>
+        <v>57.66</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -27084,22 +27084,22 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>51.47</v>
+        <v>54.04</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>51.52</v>
+        <v>56.49</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>52.42</v>
+        <v>60.06</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>53.67</v>
+        <v>62.83</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>53.73</v>
+        <v>62.62</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>54.32</v>
+        <v>62.19</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -27130,22 +27130,22 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>51.99</v>
+        <v>51.12</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>51.13</v>
+        <v>50.14</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>50.13</v>
+        <v>48.53</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>48.42</v>
+        <v>47.66</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>47.21</v>
+        <v>49.16</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>50.35</v>
+        <v>50.48</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -27176,22 +27176,22 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>53.08</v>
+        <v>53.51</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>52.5</v>
+        <v>53.41</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>51.85</v>
+        <v>55.15</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>52.62</v>
+        <v>56.53</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>52.62</v>
+        <v>57.71</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>54.09</v>
+        <v>59.09</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -27222,22 +27222,22 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>54.57</v>
+        <v>53.05</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>52.23</v>
+        <v>50.14</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.84</v>
+        <v>48.94</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>46.84</v>
+        <v>48.47</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>45.12</v>
+        <v>48.37</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>45.07</v>
+        <v>49.2</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -27268,22 +27268,22 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>53.49</v>
+        <v>53.13</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>53.7</v>
+        <v>53.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>54.43</v>
+        <v>53.21</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>54.7</v>
+        <v>53.26</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>55.59</v>
+        <v>54.15</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>58.19</v>
+        <v>56.2</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -27314,22 +27314,22 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>50.75</v>
+        <v>52.04</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>50.82</v>
+        <v>51.95</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>49.86</v>
+        <v>52.49</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>49.16</v>
+        <v>53.53</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>48.35</v>
+        <v>54.65</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>48.5</v>
+        <v>57.47</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -27360,22 +27360,22 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>65.03</v>
+        <v>65.59</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>65.64</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>65.5</v>
+        <v>65.58</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>65.26000000000001</v>
+        <v>65.91</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>65.23</v>
+        <v>66.48</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>65.16</v>
+        <v>68.84</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -27406,22 +27406,22 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>51.98</v>
+        <v>50.62</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>49.95</v>
+        <v>50.92</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>49.95</v>
+        <v>49.91</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>48.52</v>
+        <v>50.29</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>48.14</v>
+        <v>53.27</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>52.66</v>
+        <v>57.31</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -27452,22 +27452,22 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>32.99</v>
+        <v>33.63</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>33.92</v>
+        <v>33.83</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>34.4</v>
+        <v>34.93</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>35.9</v>
+        <v>35.93</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>37.53</v>
+        <v>35.6</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>35.22</v>
+        <v>33.49</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -27498,22 +27498,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>50.55</v>
+        <v>51.27</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>50.47</v>
+        <v>51.79</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>50.51</v>
+        <v>52.72</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>50.68</v>
+        <v>53.91</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>50.71</v>
+        <v>54.62</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>48.14</v>
+        <v>54.31</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -27544,22 +27544,22 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>49.87</v>
+        <v>49.28</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>48.9</v>
+        <v>46.22</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45.82</v>
+        <v>45.32</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>44.87</v>
+        <v>44.57</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>44.03</v>
+        <v>43.88</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>41.48</v>
+        <v>42.35</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -27590,22 +27590,22 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>39.05</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>38.58</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>38.53</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>38.23</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>35.4</v>
+        <v>39.86</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>40.32</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>43.63</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -27636,22 +27636,22 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>61.34</v>
+        <v>60.02</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>59.99</v>
+        <v>57.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>57.25</v>
+        <v>55.14</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>54.42</v>
+        <v>53.27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>51.6</v>
+        <v>52.42</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>50.22</v>
+        <v>52.47</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -27682,22 +27682,22 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>56.46</v>
+        <v>57.71</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>57.35</v>
+        <v>58.48</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>57.66</v>
+        <v>56.14</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>55.24</v>
+        <v>54.78</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>53.45</v>
+        <v>52.95</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>51.98</v>
+        <v>50.96</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -27728,22 +27728,22 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>70.48999999999999</v>
+        <v>71.06</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>72.3</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>74.13</v>
+        <v>71.39</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>73.88</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>73.36</v>
+        <v>67.88</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>74.23</v>
+        <v>65.28</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -27774,22 +27774,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46.68</v>
+        <v>48.33</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>47.76</v>
+        <v>49.58</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>48.7</v>
+        <v>49.76</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>48.42</v>
+        <v>49.75</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>47.77</v>
+        <v>49.27</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>46.83</v>
+        <v>48.59</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -27820,22 +27820,22 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>52.6</v>
+        <v>52.63</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>53.44</v>
+        <v>53.26</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>54.36</v>
+        <v>51.14</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>53.12</v>
+        <v>48.67</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>52.01</v>
+        <v>46.33</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>51.61</v>
+        <v>43.34</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -27866,22 +27866,22 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>77.54000000000001</v>
-      </c>
-      <c r="F50" s="3" t="n">
         <v>79.26000000000001</v>
       </c>
+      <c r="F50" s="5" t="n">
+        <v>81.06</v>
+      </c>
       <c r="G50" s="5" t="n">
-        <v>81.03</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>82.45999999999999</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>82.59</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>81.48999999999999</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>78.61</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -27912,22 +27912,22 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>67.64</v>
+        <v>67.53</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>64.47</v>
+        <v>62.17</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>61.1</v>
+        <v>58.2</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>56.89</v>
+        <v>54.37</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>55.02</v>
+        <v>52.82</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -27958,22 +27958,22 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>50.42</v>
+        <v>49.84</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>51.15</v>
+        <v>50.45</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>52.57</v>
+        <v>51.47</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>54.78</v>
+        <v>51.23</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>55.91</v>
+        <v>51.35</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>54.15</v>
+        <v>52.39</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -28004,22 +28004,22 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>56.72</v>
+        <v>57.83</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>58.35</v>
+        <v>58.66</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>59.38</v>
+        <v>62.52</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>63.34</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>65.95</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>64.93000000000001</v>
+        <v>65.81</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -28050,22 +28050,22 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>50.65</v>
+        <v>52.63</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>53.91</v>
+        <v>55.49</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>57.38</v>
+        <v>58.44</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>61.26</v>
+        <v>60.47</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>64.26000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>64.87</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -28096,22 +28096,22 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>66.67</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>69.67</v>
+        <v>70.25</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>71.26000000000001</v>
+        <v>70.42</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>71.3</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -28142,22 +28142,22 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>72.45</v>
+        <v>70.19</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>70.95</v>
+        <v>66.77</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>67.91</v>
+        <v>63.95</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>65.67</v>
+        <v>61.87</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>64.36</v>
+        <v>60.64</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>63.14</v>
+        <v>61.56</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -28188,22 +28188,22 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>52.54</v>
+        <v>53.92</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>53.01</v>
+        <v>53.96</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>52.42</v>
+        <v>53.99</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>51.5</v>
+        <v>53.56</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>49.48</v>
+        <v>51.83</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>45.74</v>
+        <v>49.76</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -28233,23 +28233,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E58" s="4" t="n">
-        <v>39.04</v>
+      <c r="E58" s="3" t="n">
+        <v>40.16</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>37.23</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>36.83</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>38.2</v>
+        <v>39.96</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>43.68</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -28280,22 +28280,22 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>47.26</v>
+        <v>46.45</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>44.55</v>
+        <v>43.47</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>37.74</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>35.58</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>34.2</v>
+        <v>41.62</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>40.28</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -28326,22 +28326,22 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46.31</v>
+        <v>46.18</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>44.7</v>
+        <v>45.37</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>43.05</v>
+        <v>44.1</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>40.52</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>37.77</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>34.98</v>
+        <v>43.33</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>42.81</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -28372,22 +28372,22 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46.76</v>
+        <v>48.17</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>46.03</v>
+        <v>46.53</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>43.38</v>
+        <v>45.19</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>40.66</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>39.64</v>
+        <v>45.38</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>44.25</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -28418,22 +28418,22 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>65.86</v>
+        <v>64.66</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>65.26000000000001</v>
+        <v>61.95</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>62.61</v>
+        <v>58.22</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>59.1</v>
+        <v>51.19</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>52.48</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>45.23</v>
+        <v>44.89</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>37.44</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -28464,22 +28464,22 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>73.31</v>
+        <v>74.73</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>75.75</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>76.56</v>
+        <v>72.31</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>74.19</v>
+        <v>65.77</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>68.45</v>
+        <v>59.51</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>59.7</v>
+        <v>53.7</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -28510,22 +28510,22 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>55.62</v>
+        <v>56.2</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>55.82</v>
+        <v>55.8</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>55.02</v>
+        <v>54.29</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>53.03</v>
+        <v>49.28</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>47.41</v>
-      </c>
-      <c r="J64" s="4" t="n">
-        <v>39.8</v>
+        <v>44.83</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>42.05</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -28556,22 +28556,22 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>65.91</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>65.22</v>
+        <v>63.92</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>63.59</v>
+        <v>61.39</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>60.82</v>
+        <v>57.74</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>56.85</v>
+        <v>54.62</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>50.76</v>
+        <v>50.36</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -28602,22 +28602,22 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>49.08</v>
+        <v>52.62</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>52.49</v>
+        <v>54.91</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>54.56</v>
+        <v>55.3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>54.78</v>
+        <v>50.92</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>50.29</v>
+        <v>46.06</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>42.88</v>
+        <v>41.08</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -28648,22 +28648,22 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>61.53</v>
+        <v>62.19</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>62.65</v>
+        <v>63.34</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>63.89</v>
+        <v>64.91</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>65.65000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>67.54000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>69.64</v>
+        <v>71.67</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
@@ -28694,22 +28694,22 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>50.15</v>
+        <v>49.41</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>48.52</v>
+        <v>47.7</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>46.46</v>
+        <v>48.63</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>46.52</v>
+        <v>51.23</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>47.41</v>
+        <v>53.96</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>49.01</v>
+        <v>57.04</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -28740,22 +28740,22 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>52.42</v>
+        <v>51.63</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>51.64</v>
+        <v>50.63</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>50.62</v>
+        <v>48.98</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>48.86</v>
+        <v>48.06</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>47.59</v>
+        <v>49.5</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>50.69</v>
+        <v>50.73</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
@@ -28786,22 +28786,22 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>53.07</v>
+        <v>53.5</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>52.49</v>
+        <v>53.41</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>51.85</v>
+        <v>55.15</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>52.61</v>
+        <v>56.53</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>52.6</v>
+        <v>57.69</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>54.07</v>
+        <v>59.07</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -28832,22 +28832,22 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>54.58</v>
+        <v>53.06</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>52.24</v>
+        <v>50.14</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>48.85</v>
+        <v>48.94</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>46.85</v>
+        <v>48.47</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>45.12</v>
+        <v>48.37</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>45.07</v>
+        <v>49.2</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
@@ -28878,22 +28878,22 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>53.5</v>
+        <v>53.15</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>53.69</v>
+        <v>53.49</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>54.38</v>
+        <v>53.19</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>54.63</v>
+        <v>53.21</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>55.46</v>
+        <v>54.09</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>58.01</v>
+        <v>56.06</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -28924,22 +28924,22 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>50.75</v>
+        <v>52.04</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>50.82</v>
+        <v>51.95</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>49.87</v>
+        <v>52.5</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>49.17</v>
+        <v>53.54</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>48.37</v>
+        <v>54.66</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>48.51</v>
+        <v>57.48</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
@@ -28970,22 +28970,22 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>64.95</v>
+        <v>65.52</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>65.56</v>
+        <v>65.52</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>65.42</v>
+        <v>65.52</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>65.19</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>66.41</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>65.06</v>
+        <v>68.75</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -29016,22 +29016,22 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>52.16</v>
+        <v>50.82</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>50.21</v>
+        <v>51.1</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>50.24</v>
+        <v>50.15</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>48.93</v>
+        <v>50.55</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>48.65</v>
+        <v>53.49</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>53.18</v>
+        <v>57.28</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
@@ -29062,22 +29062,22 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>48.38</v>
+        <v>47.22</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>46.77</v>
+        <v>47.82</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>47.02</v>
+        <v>49.8</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>48.24</v>
+        <v>52.1</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>49.58</v>
+        <v>54.28</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>52.33</v>
+        <v>55.37</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -29108,22 +29108,22 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>33.82</v>
+        <v>34.4</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>34.72</v>
+        <v>34.55</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>35.14</v>
+        <v>35.43</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>36.44</v>
+        <v>36.16</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>37.8</v>
+        <v>35.65</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>35.41</v>
+        <v>33.46</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
@@ -29154,22 +29154,22 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>40.11</v>
+        <v>40.34</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>38.4</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>39.11</v>
+        <v>36.75</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>37.95</v>
+        <v>34.28</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>34.75</v>
+        <v>32.65</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -29200,22 +29200,22 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>50.48</v>
+        <v>51.22</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>50.44</v>
+        <v>51.75</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>50.49</v>
+        <v>52.68</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>50.67</v>
+        <v>53.85</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>50.7</v>
+        <v>54.53</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>48.11</v>
+        <v>54.2</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -29246,22 +29246,22 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>50.05</v>
+        <v>49.33</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>48.97</v>
+        <v>46.19</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>45.82</v>
+        <v>45.22</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>44.81</v>
+        <v>44.38</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>43.9</v>
+        <v>43.65</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>41.37</v>
+        <v>42.13</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -29292,22 +29292,22 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>39.11</v>
-      </c>
-      <c r="F81" s="4" t="n">
-        <v>38.62</v>
-      </c>
-      <c r="G81" s="4" t="n">
-        <v>38.55</v>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>38.97</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>38.23</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>35.4</v>
+        <v>39.9</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>43.64</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -29338,22 +29338,22 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>48.95</v>
+        <v>47.4</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>47.68</v>
+        <v>46.16</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>46.55</v>
+        <v>45.72</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>46.32</v>
+        <v>45.84</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>46.75</v>
+        <v>47.04</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>49.06</v>
+        <v>47.89</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -29384,22 +29384,22 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>28.67</v>
+        <v>28.62</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>28.15</v>
+        <v>29.4</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>28.99</v>
+        <v>30.7</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>30.29</v>
+        <v>32.61</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>32.12</v>
+        <v>35.44</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>33.45</v>
+        <v>39.8</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -29430,22 +29430,22 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>42.77</v>
+        <v>41.66</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>40.14</v>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v>38.23</v>
-      </c>
-      <c r="H84" s="4" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="I84" s="4" t="n">
-        <v>36.55</v>
+        <v>40.23</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>40.46</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>32.83</v>
+        <v>39.17</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -29476,22 +29476,22 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>45.63</v>
+        <v>44.15</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>42.69</v>
+        <v>42.57</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>40.72</v>
+        <v>42.89</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>40.25</v>
+        <v>44.47</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>40.44</v>
+        <v>47.05</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>42.26</v>
+        <v>49.74</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -29522,22 +29522,22 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>46.17</v>
+        <v>44.6</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>43.91</v>
+        <v>43.19</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>42.4</v>
+        <v>42.28</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>41.39</v>
+        <v>42.5</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>41.59</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>39.85</v>
+        <v>42.8</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>42.02</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -29568,22 +29568,22 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>36.24</v>
+        <v>36.04</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>34.83</v>
+        <v>35.19</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>33.61</v>
-      </c>
-      <c r="H87" s="4" t="n">
-        <v>34.65</v>
-      </c>
-      <c r="I87" s="4" t="n">
-        <v>37.05</v>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>39.71</v>
+        <v>37.03</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>49.66</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -29614,22 +29614,22 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>51.68</v>
+        <v>50.54</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>51.11</v>
+        <v>49.7</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>50.76</v>
+        <v>49.69</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>51.44</v>
+        <v>50.39</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>53.21</v>
+        <v>51.49</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>55.55</v>
+        <v>52.74</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -29660,22 +29660,22 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>61.59</v>
+        <v>60.51</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>60.43</v>
+        <v>58.15</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>57.82</v>
+        <v>55.88</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>55.07</v>
+        <v>54.03</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>52.24</v>
+        <v>53.1</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>50.8</v>
+        <v>53.09</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -29706,22 +29706,22 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>59.22</v>
+        <v>57.68</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>57.67</v>
+        <v>55.64</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>55.32</v>
+        <v>55.62</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>54.44</v>
+        <v>54.95</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>52.74</v>
+        <v>55.02</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>52.89</v>
+        <v>55.74</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -29752,22 +29752,22 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>63.35</v>
+        <v>62.29</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>61.69</v>
+        <v>59.73</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>58.68</v>
+        <v>60.62</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>58.68</v>
+        <v>60.45</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>57.24</v>
+        <v>60.62</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>56.55</v>
+        <v>62.12</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
@@ -29798,22 +29798,22 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>47.33</v>
+        <v>49.12</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>48.32</v>
+        <v>50.68</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>49.53</v>
+        <v>51.41</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>49.73</v>
+        <v>52.42</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>49.95</v>
+        <v>52.81</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>49.61</v>
+        <v>52.33</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -29844,22 +29844,22 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>63.87</v>
+        <v>61.91</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>62.2</v>
+        <v>58.16</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>58.35</v>
+        <v>53.06</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>46.12</v>
+        <v>45.56</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>38.93</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>39.04</v>
+        <v>32.17</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
@@ -29890,22 +29890,22 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>66.87</v>
+        <v>68.7</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>68.38</v>
+        <v>68.33</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>67.8</v>
+        <v>64.42</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>63.57</v>
+        <v>59.11</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>58.54</v>
+        <v>51.56</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -29936,22 +29936,22 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>67.20999999999999</v>
+        <v>64.27</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>63.87</v>
+        <v>60.35</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>59.64</v>
+        <v>54.62</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>53.68</v>
+        <v>49.48</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>44.22</v>
+        <v>44.85</v>
+      </c>
+      <c r="J95" s="4" t="n">
+        <v>39.19</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
@@ -29982,22 +29982,22 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>59.75</v>
+        <v>59.3</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>57.98</v>
+        <v>57.91</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>56.07</v>
+        <v>55.78</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>53</v>
+        <v>51.58</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>47.21</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>42.37</v>
+        <v>40.43</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -30028,22 +30028,22 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>71.26000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>70.72</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>70.06999999999999</v>
+        <v>67.72</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>67.72</v>
+        <v>63.54</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>63.55</v>
+        <v>59.8</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>56.73</v>
+        <v>54.51</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
@@ -30074,22 +30074,22 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>64.72</v>
+        <v>63.55</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>62.67</v>
+        <v>61.51</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>60.23</v>
+        <v>57.25</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>55.5</v>
+        <v>50.76</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="J98" s="3" t="n">
-        <v>42.48</v>
+        <v>44.01</v>
+      </c>
+      <c r="J98" s="4" t="n">
+        <v>37.98</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -30120,22 +30120,22 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>59</v>
+        <v>60.72</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>59.54</v>
+        <v>61.61</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>60.01</v>
+        <v>61.81</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>59.25</v>
+        <v>62.98</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>58.68</v>
+        <v>65.44</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>59.85</v>
+        <v>71.23</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -30166,22 +30166,22 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>47.65</v>
+        <v>45.52</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>46.75</v>
+        <v>45.42</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>47.24</v>
+        <v>45.99</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>48.54</v>
+        <v>47.39</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>50.73</v>
+        <v>50.31</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>54.15</v>
+        <v>52.7</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -30212,22 +30212,22 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>35.06</v>
+        <v>35.86</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>35.98</v>
+        <v>35.69</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>35.95</v>
+        <v>36.43</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>36.92</v>
+        <v>36.79</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>37.65</v>
+        <v>36.42</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>35.46</v>
+        <v>34.13</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -30258,22 +30258,22 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>48.53</v>
+        <v>46.85</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>47.09</v>
+        <v>45.77</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>46.08</v>
+        <v>44.28</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>43.22</v>
-      </c>
-      <c r="J102" s="3" t="n">
-        <v>40.19</v>
+        <v>42.43</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>38.3</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -30304,22 +30304,22 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>57.2</v>
+        <v>60.86</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>61.03</v>
+        <v>62.3</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>62.74</v>
+        <v>62.43</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>63.25</v>
+        <v>62.18</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>63.57</v>
+        <v>62.13</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>63.22</v>
+        <v>63.59</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -30350,22 +30350,22 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>41.4</v>
+        <v>46.11</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>45.54</v>
+        <v>49.24</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>48.7</v>
+        <v>53.06</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>52.38</v>
+        <v>57.84</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>56.82</v>
+        <v>61.18</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>59.11</v>
+        <v>61.88</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -30396,22 +30396,22 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>51.09</v>
+        <v>53.86</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>53.99</v>
+        <v>55.57</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>55.87</v>
+        <v>57.1</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>57.67</v>
+        <v>57.47</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>58.4</v>
+        <v>56.75</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>57.78</v>
+        <v>55.5</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -30442,22 +30442,22 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>51.82</v>
+        <v>56.97</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>56.84</v>
+        <v>59.15</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>59.19</v>
+        <v>60.08</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>60.21</v>
+        <v>60.56</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>60.71</v>
+        <v>60.41</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>60.06</v>
+        <v>60.56</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -30488,22 +30488,22 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>48.41</v>
+        <v>51.62</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>51.63</v>
+        <v>52.7</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>52.99</v>
+        <v>53.68</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>54.15</v>
+        <v>55.98</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>56.73</v>
+        <v>57.34</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>56.91</v>
+        <v>57.54</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -30534,22 +30534,22 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>58.46</v>
+        <v>58.49</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>58.57</v>
+        <v>56.95</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>57.39</v>
+        <v>54.43</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>55.26</v>
+        <v>52.24</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>53.58</v>
+        <v>50.36</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>51.48</v>
+        <v>49.56</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -30580,22 +30580,22 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>53.11</v>
+        <v>57.92</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>58.26</v>
+        <v>59.18</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>59.84</v>
+        <v>59.97</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>61.06</v>
+        <v>60.7</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>62.5</v>
+        <v>61.11</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>62.6</v>
+        <v>61.93</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -30626,22 +30626,22 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="F110" s="4" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="G110" s="4" t="n">
-        <v>39.42</v>
+        <v>39.62</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>43.48</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>40.96</v>
+        <v>46.74</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>42.87</v>
+        <v>50.52</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>45.68</v>
+        <v>53.44</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -30672,22 +30672,22 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>51.19</v>
+        <v>50.6</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>50.76</v>
+        <v>49.99</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>50.19</v>
+        <v>49.7</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>49.94</v>
+        <v>51.22</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>51.42</v>
+        <v>51.87</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>51.18</v>
+        <v>52.92</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
@@ -30718,22 +30718,22 @@
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>48.83</v>
+        <v>48.18</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>47.75</v>
+        <v>47.77</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>47.01</v>
+        <v>47.5</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>46.31</v>
+        <v>48.94</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>47.02</v>
+        <v>50.14</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>48.03</v>
+        <v>51.64</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -30764,22 +30764,22 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>46.21</v>
+        <v>45.48</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>45.48</v>
+        <v>45.35</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>45.32</v>
+        <v>45.8</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>45.74</v>
+        <v>47.63</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>47.52</v>
+        <v>50.22</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>49.62</v>
+        <v>52.19</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
@@ -30810,22 +30810,22 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>44.73</v>
+        <v>43.98</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>43.84</v>
+        <v>42.45</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>42.09</v>
+        <v>41.59</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>41.05</v>
+        <v>42.34</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>41.43</v>
+        <v>43.71</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>43.74</v>
+        <v>45.25</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -30856,22 +30856,22 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>39.43</v>
+        <v>38.08</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>38.55</v>
+        <v>36.95</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>37.4</v>
+        <v>36.99</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>37.52</v>
+        <v>38.12</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>38.66</v>
+        <v>39.31</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>40.38</v>
+        <v>40.02</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
@@ -30902,22 +30902,22 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>46.06</v>
+        <v>45.43</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>45.28</v>
+        <v>45.07</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>44.77</v>
+        <v>44.65</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>44.13</v>
+        <v>47.62</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>46.76</v>
+        <v>49.3</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>48.08</v>
+        <v>51.02</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -30948,22 +30948,22 @@
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>52.28</v>
+        <v>52.39</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>51.28</v>
+        <v>51.19</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>49.37</v>
+        <v>50.7</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>47.75</v>
+        <v>51.96</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>47.18</v>
+        <v>53.36</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>48.72</v>
+        <v>55.1</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
@@ -30994,22 +30994,22 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>48.13</v>
+        <v>48.02</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>48.28</v>
+        <v>47.67</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>48.01</v>
+        <v>47.52</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>47.94</v>
+        <v>47.89</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>48.41</v>
+        <v>47.75</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>48.93</v>
+        <v>47.04</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -31040,22 +31040,22 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>52.97</v>
+        <v>53.73</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>53.81</v>
+        <v>54.27</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>54.25</v>
+        <v>54.67</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>54.66</v>
+        <v>55.6</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>55.6</v>
+        <v>56.4</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>57.03</v>
+        <v>56.03</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
@@ -31086,22 +31086,22 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>46.72</v>
+        <v>48.79</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>48.74</v>
+        <v>49.19</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>49.05</v>
+        <v>49.39</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>49.19</v>
+        <v>50.15</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>49.86</v>
+        <v>51.41</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>50.6</v>
+        <v>52.97</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -31132,22 +31132,22 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>49.85</v>
+        <v>49.02</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>49.41</v>
+        <v>48.08</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>48.78</v>
+        <v>47.44</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>48.56</v>
+        <v>47.17</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>48.87</v>
+        <v>47.17</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>48.16</v>
+        <v>47.7</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
@@ -31178,22 +31178,22 @@
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>47.54</v>
+        <v>49.2</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>48.43</v>
+        <v>49.12</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>47.93</v>
+        <v>48.78</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>46.98</v>
+        <v>49.95</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>47.01</v>
+        <v>50.41</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>46.92</v>
+        <v>52.15</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -31224,22 +31224,22 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>67.33</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>64.38</v>
+        <v>62.7</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>61.14</v>
+        <v>59.94</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>57.94</v>
+        <v>58.1</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>55.31</v>
+        <v>55.43</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>51.91</v>
+        <v>51.66</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
@@ -31270,22 +31270,22 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>50.89</v>
+        <v>54.15</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>52.84</v>
+        <v>57.09</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>55.1</v>
+        <v>58.7</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>55.68</v>
+        <v>58.9</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>54.31</v>
+        <v>58.06</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>53.29</v>
+        <v>55.18</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -31316,22 +31316,22 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>43.89</v>
+        <v>47.74</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>45.57</v>
+        <v>51</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>47.56</v>
+        <v>54.27</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>49.09</v>
+        <v>56.04</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>48.28</v>
+        <v>56.6</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>48.09</v>
+        <v>52.94</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
@@ -31362,22 +31362,22 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>61.41</v>
+        <v>62.97</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>61.33</v>
+        <v>62.23</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>60.05</v>
+        <v>62.37</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>59.27</v>
+        <v>62.66</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>58.31</v>
+        <v>61.9</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>56.83</v>
+        <v>59.6</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -31408,22 +31408,22 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>70.14</v>
+        <v>70.75</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>71.98</v>
+        <v>72.12</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>73.78</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>73.56</v>
+        <v>69.22</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>73.06</v>
+        <v>67.73</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>73.97</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
@@ -31454,22 +31454,22 @@
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>72.26000000000001</v>
+        <v>76.12</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>74.94</v>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>77.54000000000001</v>
-      </c>
-      <c r="H128" s="3" t="n">
-        <v>78.79000000000001</v>
-      </c>
-      <c r="I128" s="3" t="n">
-        <v>78.36</v>
-      </c>
-      <c r="J128" s="3" t="n">
-        <v>77.65000000000001</v>
+        <v>79.39</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>82.73</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>81.91</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>80.69</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -31500,22 +31500,22 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>46.58</v>
+        <v>48.27</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>47.7</v>
+        <v>49.52</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>48.64</v>
+        <v>49.77</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>48.44</v>
+        <v>49.88</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>47.9</v>
+        <v>49.49</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>47.06</v>
+        <v>48.85</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
@@ -31545,23 +31545,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E130" s="3" t="n">
-        <v>78.87</v>
+      <c r="E130" s="5" t="n">
+        <v>81.06</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>80.84999999999999</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>82.7</v>
+        <v>84.55</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>84.12</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>84.17</v>
+        <v>83.83</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>84.26000000000001</v>
+        <v>81.11</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -31592,22 +31592,22 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>67.83</v>
+        <v>67.62</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>67.2</v>
+        <v>65.12</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>64.43000000000001</v>
+        <v>61.96</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>60.97</v>
+        <v>57.88</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>56.7</v>
+        <v>53.94</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>54.79</v>
+        <v>52.41</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
@@ -31638,22 +31638,22 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>64.43000000000001</v>
+        <v>66.78</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>64.66</v>
+        <v>67.62</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>64.42</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>63.99</v>
+        <v>69.12</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>62.03</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>61.29</v>
+        <v>62.58</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -31684,22 +31684,22 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>42.23</v>
+        <v>43.74</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>43.13</v>
+        <v>45.32</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>44.32</v>
+        <v>45.88</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>44.28</v>
+        <v>44.53</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>42.07</v>
+        <v>43.79</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>40.98</v>
+        <v>40.36</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
@@ -31730,22 +31730,22 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>42.64</v>
+        <v>41.88</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>42.65</v>
+        <v>41.22</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>42.21</v>
+        <v>41.3</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>42.63</v>
+        <v>41.74</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>43.25</v>
+        <v>42.57</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>41.46</v>
+        <v>45.1</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -31776,22 +31776,22 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>42.18</v>
+        <v>40.71</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>41.59</v>
+        <v>41.3</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>42.74</v>
+        <v>42.86</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>44.98</v>
+        <v>42.83</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>45.97</v>
+        <v>43.24</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>44.94</v>
+        <v>43.98</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
@@ -31822,22 +31822,22 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>49.95</v>
+        <v>52.61</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>53.45</v>
+        <v>54.14</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>55.38</v>
+        <v>56.01</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>57.75</v>
+        <v>58.04</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>60.11</v>
+        <v>57.82</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>58.27</v>
+        <v>58.63</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -31868,22 +31868,22 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>54.48</v>
+        <v>58.66</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>59.88</v>
+        <v>61.46</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>63.32</v>
+        <v>63.01</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>65.79000000000001</v>
+        <v>63.13</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>67.18000000000001</v>
+        <v>61.96</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>65.43000000000001</v>
+        <v>62.86</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
@@ -31914,22 +31914,22 @@
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>63.41</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>66.81</v>
+        <v>64.05</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>68.19</v>
+        <v>63.04</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>69.09</v>
+        <v>61.21</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>69.81</v>
+        <v>58.96</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>58.86</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -31960,22 +31960,22 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>44.33</v>
+        <v>44.1</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>44.74</v>
+        <v>44.55</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>45.5</v>
+        <v>44.72</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>46.06</v>
+        <v>44.84</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>46.64</v>
+        <v>44.7</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>44.69</v>
+        <v>45.85</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
@@ -32006,22 +32006,22 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>46.99</v>
+        <v>47.94</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>49.55</v>
+        <v>48.75</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>51.16</v>
+        <v>49.89</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>53.22</v>
+        <v>50.43</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>54.87</v>
+        <v>49.82</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>52.59</v>
+        <v>50.62</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -32052,22 +32052,22 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>42.06</v>
+        <v>41.76</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>42.09</v>
+        <v>42.62</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>43.02</v>
+        <v>44.03</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>44.38</v>
+        <v>44.96</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>45.31</v>
+        <v>45.77</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>43.55</v>
+        <v>48.56</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -32098,22 +32098,22 @@
         </is>
       </c>
       <c r="E142" s="3" t="n">
-        <v>59.52</v>
+        <v>61.61</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>63.78</v>
+        <v>63.5</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>66.69</v>
+        <v>65.69</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>70.12</v>
+        <v>66.31</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>72.42</v>
+        <v>66.13</v>
       </c>
       <c r="J142" s="3" t="n">
-        <v>71.76000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -32144,22 +32144,22 @@
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>67.87</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>72.45</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>76.19</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>79.81</v>
+        <v>79.63</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>82.77</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>83.92</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
@@ -32190,22 +32190,22 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>41.95</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>40.77</v>
+        <v>40.16</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>39.29</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>40.26</v>
+        <v>40.32</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>41.81</v>
+        <v>41.85</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>43.56</v>
+        <v>43.13</v>
       </c>
       <c r="J144" s="3" t="n">
-        <v>42.34</v>
+        <v>44.12</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -32236,22 +32236,22 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>49.49</v>
+        <v>47.83</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>49.1</v>
+        <v>47.58</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>49.35</v>
+        <v>48.55</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>51.09</v>
+        <v>48.67</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>52.2</v>
+        <v>48.47</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>50.28</v>
+        <v>48.58</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
@@ -32282,22 +32282,22 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>47.48</v>
+        <v>48.18</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>48.89</v>
+        <v>49.32</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>50.12</v>
+        <v>50.45</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>51.34</v>
+        <v>50.85</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>51.78</v>
+        <v>51.3</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>50.7</v>
+        <v>53.06</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -32328,22 +32328,22 @@
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>57.03</v>
+        <v>61.27</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>62.2</v>
+        <v>62.96</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>64.20999999999999</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>67.28</v>
+        <v>67.41</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>69.44</v>
+        <v>67.95</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>69.31</v>
+        <v>69.97</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
@@ -32374,22 +32374,22 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>42.93</v>
+        <v>43.51</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>44.19</v>
+        <v>44.83</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>46</v>
+        <v>45.79</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>47.28</v>
+        <v>46.61</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>48.68</v>
+        <v>46.81</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>46.89</v>
+        <v>47.88</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -32420,22 +32420,22 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>58.67</v>
+        <v>60.08</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>58.93</v>
+        <v>60.11</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>58.47</v>
+        <v>59.78</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>57.1</v>
+        <v>60.32</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>56.03</v>
+        <v>62.34</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>56.99</v>
+        <v>68.13</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
@@ -32466,22 +32466,22 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>50.14</v>
+        <v>51.76</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>51.26</v>
+        <v>52.08</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>51.4</v>
+        <v>51.53</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>50.6</v>
+        <v>55.73</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>54.1</v>
+        <v>57.88</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>55.19</v>
+        <v>62.69</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -32512,22 +32512,22 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>51.37</v>
+        <v>53.5</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>53.12</v>
+        <v>54.28</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>53.73</v>
+        <v>53.66</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>52.85</v>
+        <v>56.06</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>54.69</v>
+        <v>56.95</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>54.75</v>
+        <v>58.64</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
@@ -32558,22 +32558,22 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>52.63</v>
+        <v>52.25</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>51.99</v>
+        <v>51.3</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>51.13</v>
+        <v>51.65</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>51.53</v>
+        <v>52.81</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>52.72</v>
+        <v>54.91</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>54.89</v>
+        <v>59.72</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -32604,22 +32604,22 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>51.21</v>
+        <v>51.53</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>50.82</v>
+        <v>53.02</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>52.05</v>
+        <v>54.59</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>52.97</v>
+        <v>57.15</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>54.38</v>
+        <v>60.54</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>57.63</v>
+        <v>64.83</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
@@ -32650,22 +32650,22 @@
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>51.18</v>
+        <v>49.12</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>48.51</v>
+        <v>46.16</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>45.38</v>
+        <v>44.85</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>43.75</v>
+        <v>45.72</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>44.1</v>
+        <v>48.59</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>47.07</v>
+        <v>54.65</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -32696,22 +32696,22 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>48.55</v>
+        <v>47.09</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>45.9</v>
+        <v>44.62</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>42.87</v>
+        <v>44.6</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>41.74</v>
+        <v>45.84</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>41.14</v>
+        <v>48.24</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>42.8</v>
+        <v>50.96</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
@@ -32742,22 +32742,22 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>61.79</v>
+        <v>62.51</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>62.96</v>
+        <v>63.73</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>64.25</v>
+        <v>65.44</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>66.14</v>
+        <v>67.12</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>68.13</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>70.34</v>
+        <v>72.52</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -32788,22 +32788,22 @@
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>52.24</v>
+        <v>51.24</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>51.25</v>
+        <v>49.86</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>49.86</v>
+        <v>47.68</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>47.61</v>
+        <v>46.45</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>46.1</v>
+        <v>47.95</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>49.4</v>
+        <v>49.27</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
@@ -32834,22 +32834,22 @@
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>52.1</v>
+        <v>52.24</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>51.32</v>
+        <v>51.82</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>50.41</v>
+        <v>53.4</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>51.07</v>
+        <v>54.94</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>51.22</v>
+        <v>56.34</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>52.66</v>
+        <v>58.18</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -32880,22 +32880,22 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>54.27</v>
+        <v>52.73</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>51.92</v>
+        <v>49.82</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>48.53</v>
+        <v>48.62</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>46.54</v>
+        <v>48.18</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>44.85</v>
+        <v>48.08</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>44.78</v>
+        <v>48.94</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
@@ -32926,22 +32926,22 @@
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>53.67</v>
+        <v>53.24</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>53.81</v>
+        <v>53.52</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>54.45</v>
+        <v>53.17</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>54.65</v>
+        <v>53.11</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>55.44</v>
+        <v>53.9</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>57.94</v>
+        <v>55.73</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -32972,22 +32972,22 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>50.57</v>
+        <v>51.73</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>50.48</v>
+        <v>51.43</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>49.29</v>
+        <v>51.79</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>48.37</v>
+        <v>52.77</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>47.43</v>
+        <v>53.89</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>47.54</v>
+        <v>56.89</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
@@ -33018,22 +33018,22 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>65.88</v>
+        <v>66.41</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>66.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>66.36</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>66.09</v>
+        <v>66.75</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>66.26000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -33064,22 +33064,22 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>51.27</v>
+        <v>49.82</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>49.22</v>
+        <v>50.18</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>49.32</v>
+        <v>49.23</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>48.01</v>
+        <v>49.66</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>47.78</v>
+        <v>52.68</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>52.38</v>
+        <v>56.59</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
@@ -33110,22 +33110,22 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>45.37</v>
+        <v>47.52</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>45.6</v>
+        <v>48.37</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>45.55</v>
+        <v>49.64</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>45.36</v>
+        <v>49.75</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>43.27</v>
+        <v>50.6</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>42.74</v>
+        <v>49.72</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -33156,22 +33156,22 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>48.73</v>
+        <v>51.71</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>50.51</v>
+        <v>53.09</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>51.24</v>
+        <v>53.24</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>50.47</v>
+        <v>52.61</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>48.44</v>
+        <v>51.89</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>48.1</v>
+        <v>49.83</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
@@ -33202,22 +33202,22 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>42.34</v>
-      </c>
-      <c r="F166" s="4" t="n">
-        <v>38.98</v>
-      </c>
-      <c r="G166" s="4" t="n">
-        <v>37.64</v>
-      </c>
-      <c r="H166" s="4" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="I166" s="4" t="n">
-        <v>35.39</v>
-      </c>
-      <c r="J166" s="4" t="n">
-        <v>32.93</v>
+        <v>40.93</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="J166" s="3" t="n">
+        <v>41.18</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -33248,22 +33248,22 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>28.99</v>
+        <v>28.97</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>28.52</v>
+        <v>29.78</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>29.39</v>
+        <v>31.03</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>30.68</v>
+        <v>32.87</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>32.48</v>
+        <v>35.53</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>33.65</v>
+        <v>39.73</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
@@ -33294,22 +33294,22 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>42.97</v>
+        <v>42.16</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>40.76</v>
-      </c>
-      <c r="G168" s="4" t="n">
-        <v>39.47</v>
-      </c>
-      <c r="H168" s="4" t="n">
-        <v>39.26</v>
-      </c>
-      <c r="I168" s="4" t="n">
-        <v>38.45</v>
-      </c>
-      <c r="J168" s="4" t="n">
-        <v>34.57</v>
+        <v>41.24</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="J168" s="3" t="n">
+        <v>40.17</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -33340,22 +33340,22 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>23.95</v>
+        <v>23.97</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>23.17</v>
+        <v>25.12</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>24.22</v>
+        <v>26.74</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>25.78</v>
+        <v>29.46</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>28.46</v>
+        <v>31.88</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>28.56</v>
+        <v>33.76</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
@@ -33386,22 +33386,22 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>55.31</v>
+        <v>55.35</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>54.83</v>
+        <v>53.32</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>52.67</v>
+        <v>51.26</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>50.4</v>
+        <v>49.5</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>48.49</v>
+        <v>47.71</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>46.83</v>
+        <v>46.54</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -33432,22 +33432,22 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>39.8</v>
+        <v>37.39</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>37.54</v>
+        <v>37</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>37.71</v>
+        <v>37.91</v>
       </c>
       <c r="H171" s="4" t="n">
-        <v>39.47</v>
+        <v>39.99</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>42.78</v>
+        <v>42.09</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>43.01</v>
+        <v>43.58</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
@@ -33478,22 +33478,22 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>42.66</v>
+        <v>41.35</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>39.9</v>
+        <v>39.78</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>37.76</v>
+        <v>39.22</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>36.16</v>
+        <v>38.54</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>33.75</v>
+        <v>37.73</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>30.1</v>
+        <v>39.86</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -33524,22 +33524,22 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>61.24</v>
+        <v>60.27</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>60.11</v>
+        <v>57.95</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>57.54</v>
+        <v>55.74</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>54.84</v>
+        <v>53.95</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>52.11</v>
+        <v>53.03</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>50.69</v>
+        <v>52.99</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
@@ -33570,22 +33570,22 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>59.6</v>
+        <v>58.12</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>58.11</v>
+        <v>56.15</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>55.8</v>
+        <v>56.09</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>54.86</v>
+        <v>55.33</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>53.04</v>
+        <v>55.34</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>53.24</v>
+        <v>56.08</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -33616,22 +33616,22 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>63.35</v>
+        <v>62.3</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>61.7</v>
+        <v>59.75</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>58.69</v>
+        <v>60.62</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>58.68</v>
+        <v>60.44</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>57.23</v>
+        <v>60.59</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>56.52</v>
+        <v>62.08</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
@@ -33662,22 +33662,22 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>63.97</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>63.03</v>
+        <v>63.52</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>61.97</v>
+        <v>62.92</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>60.41</v>
+        <v>62.27</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>58.63</v>
+        <v>62.79</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>59.88</v>
+        <v>64.28</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -33708,22 +33708,22 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>65.95</v>
+        <v>64.11</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>62.99</v>
+        <v>61.37</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>60.01</v>
+        <v>58.31</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>56.65</v>
+        <v>56.51</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>54.16</v>
+        <v>53.75</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>50.72</v>
+        <v>50</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
@@ -33754,22 +33754,22 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>52.45</v>
+        <v>53.03</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>52.66</v>
+        <v>50.75</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>50.44</v>
+        <v>48.96</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>49.07</v>
+        <v>47.36</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>47.98</v>
+        <v>45.66</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>46.66</v>
+        <v>44.58</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -33800,22 +33800,22 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>62.29</v>
+        <v>63.26</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>62.52</v>
+        <v>61.65</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>60.74</v>
+        <v>59.71</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>58.71</v>
+        <v>59.36</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>58.02</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>56.23</v>
+        <v>55.75</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
@@ -33846,22 +33846,22 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>73.05</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>71.87</v>
+        <v>69.47</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>69.19</v>
+        <v>66.38</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>65.98</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>64.94</v>
+        <v>63.43</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>62.66</v>
+        <v>59.67</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -33892,22 +33892,22 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>73.31</v>
+        <v>74.77</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>75.76000000000001</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>76.59</v>
+        <v>72.3</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>74.15000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>68.44</v>
+        <v>59.61</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>59.71</v>
+        <v>53.95</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
@@ -33938,22 +33938,22 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>65.53</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>66.59</v>
+        <v>68.92</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>68.43000000000001</v>
+        <v>68.53</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>67.72</v>
+        <v>64.53</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>63.31</v>
+        <v>59.21</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>58.26</v>
+        <v>51.95</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -33984,22 +33984,22 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>68.83</v>
+        <v>65.17</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>64.38</v>
+        <v>60.97</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>59.72</v>
+        <v>55.3</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>53.59</v>
+        <v>49.48</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="J183" s="3" t="n">
-        <v>42.47</v>
+        <v>43.56</v>
+      </c>
+      <c r="J183" s="4" t="n">
+        <v>37.8</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
@@ -34030,22 +34030,22 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>58.22</v>
+        <v>57.43</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>56.14</v>
+        <v>55.93</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>54.15</v>
+        <v>53.92</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>51.25</v>
+        <v>50.11</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="J184" s="3" t="n">
-        <v>41.45</v>
+        <v>46.2</v>
+      </c>
+      <c r="J184" s="4" t="n">
+        <v>39.61</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -34076,22 +34076,22 @@
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>60.2</v>
+        <v>65.02</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>64.20999999999999</v>
+        <v>68.89</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>67.72</v>
+        <v>70.89</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>69.05</v>
+        <v>70.14</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>67.34</v>
+        <v>67.45</v>
       </c>
       <c r="J185" s="3" t="n">
-        <v>65.66</v>
+        <v>62.32</v>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
@@ -34122,22 +34122,22 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>65.95999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>63.93</v>
+        <v>62.64</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>61.47</v>
+        <v>58.47</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>56.85</v>
+        <v>51.97</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="J186" s="3" t="n">
-        <v>43.75</v>
+        <v>45.09</v>
+      </c>
+      <c r="J186" s="4" t="n">
+        <v>39.05</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -34168,22 +34168,22 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>61.93</v>
+        <v>63.64</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>62.59</v>
+        <v>63.96</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>62.55</v>
+        <v>63.52</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>61.23</v>
+        <v>64.11</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>60.34</v>
+        <v>65.97</v>
       </c>
       <c r="J187" s="3" t="n">
-        <v>61.1</v>
+        <v>71.09</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
@@ -34214,22 +34214,22 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>49.96</v>
+        <v>51.54</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>51.01</v>
+        <v>51.81</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>51.07</v>
+        <v>51.23</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>50.24</v>
+        <v>55.32</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>53.59</v>
+        <v>57.45</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>54.66</v>
+        <v>62.37</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -34260,22 +34260,22 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>54.02</v>
+        <v>56.06</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>55.7</v>
+        <v>56.45</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>55.94</v>
+        <v>55.4</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>54.68</v>
+        <v>57.4</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>56.23</v>
+        <v>57.77</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>56.02</v>
+        <v>59.46</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
@@ -34306,22 +34306,22 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>53.63</v>
+        <v>53.47</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>53.15</v>
+        <v>52.6</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>52.32</v>
+        <v>52.97</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>52.67</v>
+        <v>54.08</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>53.65</v>
+        <v>56.15</v>
       </c>
       <c r="J190" s="3" t="n">
-        <v>55.77</v>
+        <v>60.99</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -34352,22 +34352,22 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>51.72</v>
+        <v>52.02</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>51.3</v>
+        <v>53.5</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>52.52</v>
+        <v>55.08</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>53.41</v>
+        <v>57.65</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>54.78</v>
+        <v>61.02</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>57.98</v>
+        <v>65.37</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
@@ -34398,22 +34398,22 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>53.18</v>
+        <v>51.69</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>50.62</v>
+        <v>49.09</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>47.57</v>
+        <v>48.13</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>45.87</v>
+        <v>49.38</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>45.92</v>
+        <v>52.3</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>48.79</v>
+        <v>59.17</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -34444,22 +34444,22 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>68.51000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>65.33</v>
+        <v>63.51</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>61.91</v>
+        <v>60.67</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>58.6</v>
+        <v>58.82</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>55.91</v>
+        <v>55.95</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>52.24</v>
+        <v>52.1</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
@@ -34490,22 +34490,22 @@
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>61.39</v>
+        <v>62.86</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>61.28</v>
+        <v>62.13</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>60.06</v>
+        <v>62.22</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>59.29</v>
+        <v>62.51</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>58.42</v>
+        <v>61.76</v>
       </c>
       <c r="J194" s="3" t="n">
-        <v>56.9</v>
+        <v>59.59</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -34536,22 +34536,22 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>53.25</v>
+        <v>55.4</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>54.49</v>
+        <v>57.06</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>55.28</v>
+        <v>55.96</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>53.44</v>
+        <v>55.67</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>51.78</v>
+        <v>54.32</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>49.6</v>
+        <v>52.17</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
@@ -34582,22 +34582,22 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>49.23</v>
+        <v>49.61</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>49.87</v>
+        <v>50.35</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>50.61</v>
+        <v>48.74</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>49.41</v>
+        <v>46.95</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>48.3</v>
+        <v>44.95</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>47.64</v>
+        <v>42.08</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -34628,22 +34628,22 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>59.93</v>
+        <v>60.8</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>60.84</v>
+        <v>60.49</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>60.15</v>
+        <v>59.36</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>58.54</v>
+        <v>57.21</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>56.04</v>
+        <v>54.15</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>52.94</v>
+        <v>51.89</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
@@ -34674,22 +34674,22 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>64.54000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>65.45</v>
+        <v>63.37</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>63.21</v>
+        <v>60.89</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>60.53</v>
+        <v>57.79</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>57.15</v>
+        <v>54.81</v>
       </c>
       <c r="J198" s="3" t="n">
-        <v>54.57</v>
+        <v>52.3</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -34720,22 +34720,22 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>58.61</v>
+        <v>59.12</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>59.4</v>
+        <v>58.53</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>58.73</v>
+        <v>57.51</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>57.69</v>
+        <v>56.36</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>56.63</v>
+        <v>54.29</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>54.82</v>
+        <v>52.52</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
@@ -34766,22 +34766,22 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>70.66</v>
+        <v>69.66</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>69.7</v>
+        <v>67.48</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>64.48</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>63.46</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>63.44</v>
+        <v>61.85</v>
       </c>
       <c r="J200" s="3" t="n">
-        <v>61.56</v>
+        <v>58.5</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -34812,22 +34812,22 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>63.84</v>
+        <v>65.94</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>64.88</v>
+        <v>64.67</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>63.36</v>
+        <v>63.29</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>61.75</v>
+        <v>64.08</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>61.93</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="J201" s="3" t="n">
-        <v>61.52</v>
+        <v>62.19</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
@@ -34857,23 +34857,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E202" s="4" t="n">
-        <v>39.04</v>
+      <c r="E202" s="3" t="n">
+        <v>40.18</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="G202" s="4" t="n">
-        <v>37.24</v>
-      </c>
-      <c r="H202" s="4" t="n">
-        <v>36.83</v>
-      </c>
-      <c r="I202" s="4" t="n">
-        <v>36.59</v>
-      </c>
-      <c r="J202" s="4" t="n">
-        <v>38.22</v>
+        <v>39.98</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="I202" s="3" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="J202" s="3" t="n">
+        <v>43.7</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -34904,22 +34904,22 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>47.45</v>
+        <v>46.58</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>44.68</v>
+        <v>43.5</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>40.85</v>
-      </c>
-      <c r="H203" s="4" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="I203" s="4" t="n">
-        <v>35.51</v>
-      </c>
-      <c r="J203" s="4" t="n">
-        <v>34.13</v>
+        <v>41.53</v>
+      </c>
+      <c r="H203" s="3" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="I203" s="3" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="J203" s="3" t="n">
+        <v>40.07</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
@@ -34950,22 +34950,22 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>46.81</v>
+        <v>48.24</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>46.1</v>
+        <v>46.57</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>43.44</v>
+        <v>45.19</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>40.68</v>
-      </c>
-      <c r="I204" s="4" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="J204" s="4" t="n">
-        <v>39.62</v>
+        <v>45.35</v>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="J204" s="3" t="n">
+        <v>44.17</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -34996,22 +34996,22 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>56.24</v>
+        <v>56.84</v>
       </c>
       <c r="F205" s="3" t="n">
         <v>56.48</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>55.71</v>
+        <v>54.93</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>53.67</v>
+        <v>49.88</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>48.02</v>
+        <v>45.39</v>
       </c>
       <c r="J205" s="3" t="n">
-        <v>40.39</v>
+        <v>42.51</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
@@ -35042,22 +35042,22 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>66.66</v>
+        <v>65.66</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>66.27</v>
+        <v>63.25</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>63.95</v>
+        <v>59.85</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>60.79</v>
+        <v>52.96</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>54.36</v>
-      </c>
-      <c r="J206" s="3" t="n">
-        <v>47.31</v>
+        <v>47.04</v>
+      </c>
+      <c r="J206" s="4" t="n">
+        <v>39.49</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -35088,22 +35088,22 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>65.88</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>65.37</v>
+        <v>64.22</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>63.92</v>
+        <v>61.8</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>61.29</v>
+        <v>58.27</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>57.51</v>
+        <v>55.1</v>
       </c>
       <c r="J207" s="3" t="n">
-        <v>51.44</v>
+        <v>50.62</v>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
@@ -35134,22 +35134,22 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>73.42</v>
+        <v>74.72</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>75.76000000000001</v>
+        <v>75.12</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>76.44</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>74</v>
+        <v>65.44</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>68.14</v>
+        <v>59.15</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>59.41</v>
+        <v>53.19</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -35180,22 +35180,22 @@
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>76.92</v>
+        <v>73.55</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>74.06</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>69.52</v>
+        <v>63.46</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>64.52</v>
+        <v>55.07</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>56.76</v>
+        <v>49.45</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>50.39</v>
+        <v>45.46</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
@@ -35226,22 +35226,22 @@
         </is>
       </c>
       <c r="E210" s="3" t="n">
-        <v>50.14</v>
+        <v>49.4</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>48.52</v>
+        <v>47.7</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>46.46</v>
+        <v>48.63</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>46.52</v>
+        <v>51.22</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>47.4</v>
+        <v>53.95</v>
       </c>
       <c r="J210" s="3" t="n">
-        <v>49.01</v>
+        <v>57.03</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -35272,22 +35272,22 @@
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>51.46</v>
+        <v>54.04</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>51.51</v>
+        <v>56.48</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>52.41</v>
+        <v>60.07</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>53.66</v>
+        <v>62.84</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>53.73</v>
+        <v>62.62</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>54.31</v>
+        <v>62.18</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
@@ -35318,22 +35318,22 @@
         </is>
       </c>
       <c r="E212" s="3" t="n">
-        <v>51.97</v>
+        <v>51.1</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>51.11</v>
+        <v>50.11</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>50.1</v>
+        <v>48.5</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>48.4</v>
+        <v>47.63</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>47.18</v>
+        <v>49.13</v>
       </c>
       <c r="J212" s="3" t="n">
-        <v>50.33</v>
+        <v>50.45</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -35364,22 +35364,22 @@
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>53.07</v>
+        <v>53.51</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>52.49</v>
+        <v>53.41</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>51.84</v>
+        <v>55.14</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>52.6</v>
+        <v>56.51</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>52.58</v>
+        <v>57.68</v>
       </c>
       <c r="J213" s="3" t="n">
-        <v>54.05</v>
+        <v>59.07</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
@@ -35410,22 +35410,22 @@
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>54.57</v>
+        <v>53.06</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>52.24</v>
+        <v>50.14</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>48.85</v>
+        <v>48.95</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>46.85</v>
+        <v>48.48</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>45.12</v>
+        <v>48.37</v>
       </c>
       <c r="J214" s="3" t="n">
-        <v>45.07</v>
+        <v>49.2</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -35456,22 +35456,22 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>53.42</v>
+        <v>56.47</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>54.24</v>
+        <v>58.33</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>54.65</v>
+        <v>61.62</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>56.22</v>
+        <v>62.81</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>55.74</v>
+        <v>63.81</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>57.41</v>
+        <v>62.65</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
@@ -35502,22 +35502,22 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>50.75</v>
+        <v>52.03</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>50.82</v>
+        <v>51.94</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>49.85</v>
+        <v>52.48</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>49.15</v>
+        <v>53.53</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>48.35</v>
+        <v>54.65</v>
       </c>
       <c r="J216" s="3" t="n">
-        <v>48.5</v>
+        <v>57.47</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -35548,22 +35548,22 @@
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>65.20999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>65.83</v>
+        <v>65.78</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>65.70999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>66.12</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>65.48</v>
+        <v>66.72</v>
       </c>
       <c r="J217" s="3" t="n">
-        <v>65.44</v>
+        <v>69.08</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
@@ -35594,22 +35594,22 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>33.13</v>
+        <v>33.78</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>34.06</v>
+        <v>33.95</v>
       </c>
       <c r="G218" s="4" t="n">
-        <v>34.51</v>
+        <v>35.07</v>
       </c>
       <c r="H218" s="4" t="n">
-        <v>36.02</v>
+        <v>36.12</v>
       </c>
       <c r="I218" s="4" t="n">
-        <v>37.69</v>
+        <v>35.83</v>
       </c>
       <c r="J218" s="4" t="n">
-        <v>35.4</v>
+        <v>33.71</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -35640,22 +35640,22 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>50.85</v>
+        <v>51.55</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>50.76</v>
+        <v>51.91</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>50.64</v>
+        <v>52.82</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>50.8</v>
+        <v>53.99</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>50.83</v>
+        <v>54.7</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>48.28</v>
+        <v>54.38</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
@@ -35686,22 +35686,22 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>49.73</v>
+        <v>49.21</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>48.81</v>
+        <v>46.18</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>45.77</v>
+        <v>45.32</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>44.85</v>
+        <v>44.6</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>44.04</v>
+        <v>43.92</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>41.47</v>
+        <v>42.38</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -35732,22 +35732,22 @@
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>39.06</v>
-      </c>
-      <c r="F221" s="4" t="n">
-        <v>38.59</v>
-      </c>
-      <c r="G221" s="4" t="n">
-        <v>38.53</v>
-      </c>
-      <c r="H221" s="4" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="I221" s="4" t="n">
-        <v>38.23</v>
-      </c>
-      <c r="J221" s="4" t="n">
-        <v>35.4</v>
+        <v>39.86</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>40.32</v>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="H221" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I221" s="3" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="J221" s="3" t="n">
+        <v>43.62</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
@@ -35778,22 +35778,22 @@
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>42.64</v>
+        <v>41.88</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>42.65</v>
+        <v>41.22</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>42.21</v>
+        <v>41.3</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>42.63</v>
+        <v>41.74</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>43.25</v>
+        <v>42.57</v>
       </c>
       <c r="J222" s="3" t="n">
-        <v>41.46</v>
+        <v>45.1</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -35824,22 +35824,22 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>51.14</v>
+        <v>51.89</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>51.69</v>
+        <v>52.3</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>51.88</v>
+        <v>52.46</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>51.6</v>
+        <v>53.53</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>51.91</v>
+        <v>53.81</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>50.31</v>
+        <v>54.97</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
@@ -35870,22 +35870,22 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>49.95</v>
+        <v>52.61</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>53.45</v>
+        <v>54.14</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>55.38</v>
+        <v>56.01</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>57.75</v>
+        <v>58.04</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>60.11</v>
+        <v>57.82</v>
       </c>
       <c r="J224" s="3" t="n">
-        <v>58.27</v>
+        <v>58.63</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -35916,22 +35916,22 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>54.48</v>
+        <v>58.66</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>59.88</v>
+        <v>61.46</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>63.32</v>
+        <v>63.01</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>65.79000000000001</v>
+        <v>63.13</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>67.18000000000001</v>
+        <v>61.96</v>
       </c>
       <c r="J225" s="3" t="n">
-        <v>65.43000000000001</v>
+        <v>62.86</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
@@ -35962,22 +35962,22 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>50.36</v>
+        <v>52.51</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>53.49</v>
+        <v>54.48</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>55.91</v>
+        <v>56.21</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>58.25</v>
+        <v>57.45</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>59.98</v>
+        <v>57.54</v>
       </c>
       <c r="J226" s="3" t="n">
-        <v>57.99</v>
+        <v>58.77</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -36008,22 +36008,22 @@
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>63.41</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>66.81</v>
+        <v>64.05</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>68.19</v>
+        <v>63.04</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>69.09</v>
+        <v>61.21</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>69.81</v>
+        <v>58.96</v>
       </c>
       <c r="J227" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>58.86</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
@@ -36054,22 +36054,22 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>46.99</v>
+        <v>47.94</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>49.55</v>
+        <v>48.75</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>51.16</v>
+        <v>49.89</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>53.22</v>
+        <v>50.43</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>54.87</v>
+        <v>49.82</v>
       </c>
       <c r="J228" s="3" t="n">
-        <v>52.59</v>
+        <v>50.62</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -36100,22 +36100,22 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>46.99</v>
+        <v>47.94</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>49.55</v>
+        <v>48.75</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>51.16</v>
+        <v>49.89</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>53.22</v>
+        <v>50.43</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>54.87</v>
+        <v>49.82</v>
       </c>
       <c r="J229" s="3" t="n">
-        <v>52.59</v>
+        <v>50.62</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
@@ -36146,22 +36146,22 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>53.87</v>
+        <v>56.01</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>57.24</v>
+        <v>57.22</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>59.08</v>
+        <v>57.45</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>60.21</v>
+        <v>55.43</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>59.27</v>
+        <v>54.32</v>
       </c>
       <c r="J230" s="3" t="n">
-        <v>57</v>
+        <v>56.19</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -36192,22 +36192,22 @@
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>67.87</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>72.45</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>76.19</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>79.81</v>
+        <v>79.63</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>82.77</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="J231" s="5" t="n">
-        <v>83.92</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
@@ -36238,22 +36238,22 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>41.95</v>
-      </c>
-      <c r="F232" s="3" t="n">
-        <v>40.77</v>
+        <v>40.16</v>
+      </c>
+      <c r="F232" s="4" t="n">
+        <v>39.29</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>40.26</v>
+        <v>40.32</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>41.81</v>
+        <v>41.85</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>43.56</v>
+        <v>43.13</v>
       </c>
       <c r="J232" s="3" t="n">
-        <v>42.34</v>
+        <v>44.12</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -36284,22 +36284,22 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>49.49</v>
+        <v>47.83</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>49.1</v>
+        <v>47.58</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>49.35</v>
+        <v>48.55</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>51.09</v>
+        <v>48.67</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>52.2</v>
+        <v>48.47</v>
       </c>
       <c r="J233" s="3" t="n">
-        <v>50.28</v>
+        <v>48.58</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
@@ -36330,22 +36330,22 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>47.48</v>
+        <v>48.18</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>48.89</v>
+        <v>49.32</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>50.12</v>
+        <v>50.45</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>51.34</v>
+        <v>50.85</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>51.78</v>
+        <v>51.3</v>
       </c>
       <c r="J234" s="3" t="n">
-        <v>50.7</v>
+        <v>53.06</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -36376,22 +36376,22 @@
         </is>
       </c>
       <c r="E235" s="3" t="n">
-        <v>57.03</v>
+        <v>61.27</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>62.2</v>
+        <v>62.96</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>64.20999999999999</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>67.28</v>
+        <v>67.41</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>69.44</v>
+        <v>67.95</v>
       </c>
       <c r="J235" s="3" t="n">
-        <v>69.31</v>
+        <v>69.97</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
@@ -36422,22 +36422,22 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>50.72</v>
+        <v>50.14</v>
       </c>
       <c r="F236" s="3" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="G236" s="3" t="n">
         <v>51.5</v>
       </c>
-      <c r="G236" s="3" t="n">
-        <v>52.7</v>
-      </c>
       <c r="H236" s="3" t="n">
-        <v>54.74</v>
+        <v>51.24</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>55.52</v>
+        <v>51.74</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>53.85</v>
+        <v>53.55</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -36468,22 +36468,22 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>50.36</v>
+        <v>52.31</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>53.51</v>
+        <v>55.42</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>57.17</v>
+        <v>58.43</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>60.97</v>
+        <v>60.69</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>63.85</v>
+        <v>63.21</v>
       </c>
       <c r="J237" s="3" t="n">
-        <v>64.34</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
@@ -36514,22 +36514,22 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>70.65000000000001</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>71.84</v>
+        <v>72.28</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>72.86</v>
+        <v>72.88</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>73.66</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>74.8</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="J238" s="3" t="n">
-        <v>74.66</v>
+        <v>73.33</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -36560,22 +36560,22 @@
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>72.92</v>
+        <v>69.75</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>70.84</v>
+        <v>66.91</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>68.56</v>
+        <v>65.27</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>66.81</v>
+        <v>65.03</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>66.72</v>
+        <v>65.58</v>
       </c>
       <c r="J239" s="3" t="n">
-        <v>67.61</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
@@ -36606,22 +36606,22 @@
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>61.59</v>
+        <v>62.31</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>62.76</v>
+        <v>63.5</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>64.03</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>65.88</v>
+        <v>66.77</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>67.81</v>
+        <v>68.84</v>
       </c>
       <c r="J240" s="3" t="n">
-        <v>69.97</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -36652,22 +36652,22 @@
         </is>
       </c>
       <c r="E241" s="3" t="n">
-        <v>52.38</v>
+        <v>51.45</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>51.44</v>
+        <v>50.11</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>50.07</v>
+        <v>47.97</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>47.83</v>
+        <v>46.75</v>
       </c>
       <c r="I241" s="3" t="n">
-        <v>46.29</v>
+        <v>48.22</v>
       </c>
       <c r="J241" s="3" t="n">
-        <v>49.52</v>
+        <v>49.67</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
@@ -36698,22 +36698,22 @@
         </is>
       </c>
       <c r="E242" s="3" t="n">
-        <v>54.31</v>
+        <v>52.76</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>51.94</v>
+        <v>49.82</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>48.53</v>
+        <v>48.61</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>46.53</v>
+        <v>48.14</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>44.8</v>
+        <v>48.01</v>
       </c>
       <c r="J242" s="3" t="n">
-        <v>44.72</v>
+        <v>48.84</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -36744,22 +36744,22 @@
         </is>
       </c>
       <c r="E243" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>66.16</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>66.23</v>
+        <v>66.17</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>66.12</v>
+        <v>66.16</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>66.56</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>65.95999999999999</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="J243" s="3" t="n">
-        <v>66.02</v>
+        <v>69.64</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
@@ -36790,22 +36790,22 @@
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>51.34</v>
+        <v>49.85</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>49.13</v>
+        <v>50.33</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>49.3</v>
+        <v>49.28</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>47.79</v>
+        <v>49.7</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>47.38</v>
+        <v>52.84</v>
       </c>
       <c r="J244" s="3" t="n">
-        <v>52.09</v>
+        <v>57.23</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -36836,22 +36836,22 @@
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>61.41</v>
+        <v>60.45</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>60.29</v>
+        <v>58.12</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>57.72</v>
+        <v>55.83</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>54.94</v>
+        <v>53.96</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>52.13</v>
+        <v>52.98</v>
       </c>
       <c r="J245" s="3" t="n">
-        <v>50.65</v>
+        <v>52.93</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
@@ -36882,22 +36882,22 @@
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>57.25</v>
+        <v>54.61</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>53.91</v>
+        <v>51.75</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>50.71</v>
+        <v>51.38</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>49.56</v>
+        <v>50.34</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>47.43</v>
+        <v>50.69</v>
       </c>
       <c r="J246" s="3" t="n">
-        <v>47.83</v>
+        <v>51.13</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -36928,22 +36928,22 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>63.57</v>
+        <v>62.54</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>61.91</v>
+        <v>59.94</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>58.86</v>
+        <v>60.76</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>58.78</v>
+        <v>60.5</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>57.25</v>
+        <v>60.62</v>
       </c>
       <c r="J247" s="3" t="n">
-        <v>56.5</v>
+        <v>62.13</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
@@ -36973,23 +36973,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E248" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="F248" s="4" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>37.96</v>
+      <c r="E248" s="4" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>44.35</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>40.22</v>
+        <v>47.13</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>40.67</v>
+        <v>48.69</v>
       </c>
       <c r="J248" s="3" t="n">
-        <v>40.66</v>
+        <v>45.75</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -37020,22 +37020,22 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>26.28</v>
+        <v>27.12</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>25.7</v>
+        <v>28.82</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>26.69</v>
+        <v>32.94</v>
       </c>
       <c r="H249" s="4" t="n">
-        <v>29.48</v>
+        <v>35.36</v>
       </c>
       <c r="I249" s="4" t="n">
-        <v>29.66</v>
+        <v>35.47</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>27.78</v>
+        <v>31.94</v>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
@@ -37066,22 +37066,22 @@
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>45.78</v>
+        <v>45.76</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>44.51</v>
+        <v>46.48</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>44.6</v>
+        <v>49.69</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>46.75</v>
+        <v>53.43</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>48.84</v>
+        <v>56.47</v>
       </c>
       <c r="J250" s="3" t="n">
-        <v>50.37</v>
+        <v>52</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -37111,23 +37111,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E251" s="3" t="n">
-        <v>40.45</v>
+      <c r="E251" s="4" t="n">
+        <v>38.35</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>36.72</v>
+        <v>37.03</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>34.51</v>
+        <v>38.36</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>34.58</v>
+        <v>38.64</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>32.8</v>
+        <v>38.26</v>
       </c>
       <c r="J251" s="4" t="n">
-        <v>31.37</v>
+        <v>34.64</v>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
@@ -37157,23 +37157,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E252" s="4" t="n">
-        <v>39.09</v>
-      </c>
-      <c r="F252" s="4" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="G252" s="4" t="n">
-        <v>39.54</v>
-      </c>
-      <c r="H252" s="4" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="I252" s="4" t="n">
-        <v>38.44</v>
+      <c r="E252" s="3" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="G252" s="3" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="I252" s="3" t="n">
+        <v>42.73</v>
       </c>
       <c r="J252" s="4" t="n">
-        <v>37.16</v>
+        <v>38.24</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -37204,22 +37204,22 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>33.47</v>
+        <v>34.4</v>
       </c>
       <c r="F253" s="4" t="n">
-        <v>32.76</v>
+        <v>34.59</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>32</v>
+        <v>35.78</v>
       </c>
       <c r="H253" s="4" t="n">
-        <v>31.65</v>
+        <v>37.76</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>31.08</v>
+        <v>38.43</v>
       </c>
       <c r="J253" s="4" t="n">
-        <v>29.6</v>
+        <v>35.82</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
@@ -37250,22 +37250,22 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>31.78</v>
+        <v>31.58</v>
       </c>
       <c r="F254" s="4" t="n">
-        <v>30.21</v>
+        <v>32.23</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>30.26</v>
+        <v>35.08</v>
       </c>
       <c r="H254" s="4" t="n">
-        <v>32.08</v>
+        <v>36.55</v>
       </c>
       <c r="I254" s="4" t="n">
-        <v>31.89</v>
+        <v>37.13</v>
       </c>
       <c r="J254" s="4" t="n">
-        <v>31.07</v>
+        <v>33.4</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -37296,22 +37296,22 @@
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="F255" s="4" t="n">
-        <v>39.41</v>
-      </c>
-      <c r="G255" s="4" t="n">
-        <v>39.53</v>
+        <v>40.79</v>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="G255" s="3" t="n">
+        <v>43.36</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="I255" s="4" t="n">
-        <v>39.45</v>
+        <v>44.26</v>
+      </c>
+      <c r="I255" s="3" t="n">
+        <v>42.92</v>
       </c>
       <c r="J255" s="4" t="n">
-        <v>36.14</v>
+        <v>37.96</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
@@ -37342,22 +37342,22 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>39.88</v>
+        <v>37.32</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>34.94</v>
+        <v>35.12</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>31.59</v>
+        <v>35.05</v>
       </c>
       <c r="H256" s="4" t="n">
-        <v>29.69</v>
+        <v>36.94</v>
       </c>
       <c r="I256" s="4" t="n">
-        <v>28.48</v>
+        <v>37.59</v>
       </c>
       <c r="J256" s="4" t="n">
-        <v>26.7</v>
+        <v>34.58</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -37388,22 +37388,22 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>23.01</v>
+        <v>24.32</v>
       </c>
       <c r="F257" s="4" t="n">
-        <v>21.74</v>
+        <v>24.71</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>20.61</v>
+        <v>27.74</v>
       </c>
       <c r="H257" s="4" t="n">
-        <v>21.02</v>
+        <v>31.74</v>
       </c>
       <c r="I257" s="4" t="n">
-        <v>20.74</v>
+        <v>33.99</v>
       </c>
       <c r="J257" s="4" t="n">
-        <v>20.81</v>
+        <v>31.94</v>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
@@ -37434,22 +37434,22 @@
         </is>
       </c>
       <c r="E258" s="3" t="n">
-        <v>41.19</v>
+        <v>43.22</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>41.23</v>
+        <v>44.53</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>41.64</v>
+        <v>47.64</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>43.2</v>
+        <v>50.4</v>
       </c>
       <c r="I258" s="3" t="n">
-        <v>43.32</v>
+        <v>51.05</v>
       </c>
       <c r="J258" s="3" t="n">
-        <v>41.7</v>
+        <v>49.02</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -37480,22 +37480,22 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>49.67</v>
+        <v>48.81</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>46.98</v>
+        <v>47.76</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>44.97</v>
+        <v>47.61</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>43.35</v>
+        <v>48.4</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>41.75</v>
-      </c>
-      <c r="J259" s="4" t="n">
-        <v>38.48</v>
+        <v>47.26</v>
+      </c>
+      <c r="J259" s="3" t="n">
+        <v>41.91</v>
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
@@ -37526,22 +37526,22 @@
         </is>
       </c>
       <c r="E260" s="3" t="n">
-        <v>46</v>
+        <v>48.11</v>
       </c>
       <c r="F260" s="3" t="n">
-        <v>45.78</v>
+        <v>48.73</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>45.53</v>
+        <v>51.21</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>46.68</v>
+        <v>53.46</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>46.48</v>
+        <v>53.78</v>
       </c>
       <c r="J260" s="3" t="n">
-        <v>45.22</v>
+        <v>51.71</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -37572,22 +37572,22 @@
         </is>
       </c>
       <c r="E261" s="4" t="n">
-        <v>37.56</v>
+        <v>38.21</v>
       </c>
       <c r="F261" s="4" t="n">
-        <v>36.81</v>
-      </c>
-      <c r="G261" s="4" t="n">
-        <v>36.32</v>
-      </c>
-      <c r="H261" s="4" t="n">
-        <v>37.13</v>
-      </c>
-      <c r="I261" s="4" t="n">
-        <v>37.06</v>
+        <v>38.44</v>
+      </c>
+      <c r="G261" s="3" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="H261" s="3" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="I261" s="3" t="n">
+        <v>43.6</v>
       </c>
       <c r="J261" s="4" t="n">
-        <v>36.5</v>
+        <v>39.19</v>
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
@@ -37618,22 +37618,22 @@
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>39.33</v>
+        <v>39.08</v>
       </c>
       <c r="F262" s="4" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="G262" s="4" t="n">
-        <v>36.58</v>
-      </c>
-      <c r="H262" s="4" t="n">
-        <v>38.07</v>
-      </c>
-      <c r="I262" s="4" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="J262" s="4" t="n">
-        <v>37.89</v>
+        <v>39.76</v>
+      </c>
+      <c r="G262" s="3" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="H262" s="3" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="I262" s="3" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="J262" s="3" t="n">
+        <v>46.47</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -37664,22 +37664,22 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>50.67</v>
+        <v>52.16</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>51.28</v>
+        <v>52.62</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>51.41</v>
+        <v>52.49</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>50.77</v>
+        <v>54.53</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>51.89</v>
+        <v>56.25</v>
       </c>
       <c r="J263" s="3" t="n">
-        <v>52.81</v>
+        <v>61.38</v>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
@@ -37710,22 +37710,22 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>54.15</v>
+        <v>54.06</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>53.67</v>
+        <v>53.22</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>52.85</v>
+        <v>53.64</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>53.21</v>
+        <v>54.73</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>54.13</v>
+        <v>56.73</v>
       </c>
       <c r="J264" s="3" t="n">
-        <v>56.28</v>
+        <v>61.4</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -37756,22 +37756,22 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>52.94</v>
+        <v>53.6</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>52.71</v>
+        <v>54.3</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>53.13</v>
+        <v>55.56</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>53.77</v>
+        <v>57.58</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>54.8</v>
+        <v>60.52</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>57.59</v>
+        <v>65.03</v>
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
@@ -37802,22 +37802,22 @@
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>52.63</v>
+        <v>50.62</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>49.98</v>
+        <v>47.63</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>46.8</v>
+        <v>46.36</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>45.18</v>
+        <v>47.15</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>45.41</v>
+        <v>49.87</v>
       </c>
       <c r="J266" s="3" t="n">
-        <v>48.2</v>
+        <v>55.91</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -37848,22 +37848,22 @@
         </is>
       </c>
       <c r="E267" s="4" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="F267" s="4" t="n">
-        <v>27.18</v>
+        <v>28.57</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>28.22</v>
+        <v>29.87</v>
       </c>
       <c r="H267" s="4" t="n">
-        <v>29.58</v>
+        <v>31.67</v>
       </c>
       <c r="I267" s="4" t="n">
-        <v>31.39</v>
+        <v>34.5</v>
       </c>
       <c r="J267" s="4" t="n">
-        <v>32.76</v>
+        <v>38.83</v>
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
@@ -37894,22 +37894,22 @@
         </is>
       </c>
       <c r="E268" s="3" t="n">
-        <v>40.19</v>
+        <v>42.06</v>
       </c>
       <c r="F268" s="3" t="n">
-        <v>40.79</v>
+        <v>43.48</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>41.66</v>
+        <v>45.49</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>42.75</v>
+        <v>48.02</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>43.8</v>
+        <v>51.1</v>
       </c>
       <c r="J268" s="3" t="n">
-        <v>45.69</v>
+        <v>53.71</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25597,32 +25597,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -25658,26 +25658,26 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>47.34</v>
+        <v>50.75</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>50.53</v>
+        <v>54.29</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>53.73</v>
+        <v>57.14</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>55.5</v>
+        <v>59.64</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>56.14</v>
+        <v>58.73</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>52.28</v>
+        <v>55.6</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25704,26 +25704,26 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>63.19</v>
+        <v>62.43</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>62.54</v>
+        <v>62.49</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>62.79</v>
+        <v>62.6</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>63.17</v>
+        <v>61.69</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>62.5</v>
+        <v>59.35</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>60.35</v>
+        <v>55.29</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25750,26 +25750,26 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>57.01</v>
+        <v>63.52</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>58.16</v>
+        <v>63.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>56.4</v>
+        <v>64.77</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>55.53</v>
+        <v>64.44</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>53.99</v>
+        <v>60.61</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>52.05</v>
+        <v>55.43</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25796,26 +25796,26 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>67.51000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>71.56</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>61.96</v>
+        <v>71.81</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>57.95</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>54.03</v>
+        <v>70.36</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>52.41</v>
+        <v>66.27</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25842,26 +25842,26 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46.21</v>
+        <v>48.16</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>47.72</v>
+        <v>48.53</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>48</v>
+        <v>47.35</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>45.19</v>
+        <v>46.38</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>41.72</v>
+        <v>44.78</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25888,26 +25888,26 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>55.59</v>
+        <v>58.16</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>55.84</v>
+        <v>57.96</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>53.98</v>
+        <v>59.64</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>53.25</v>
+        <v>62.5</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>52.43</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>54.66</v>
+        <v>67.48</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25934,26 +25934,26 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>60.33</v>
+        <v>61.69</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>60.4</v>
+        <v>61.72</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>59.87</v>
+        <v>63.18</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>60.4</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>62.4</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>68.12</v>
+        <v>73.77</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25980,26 +25980,26 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>43.98</v>
+        <v>42.69</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>43.75</v>
+        <v>43.18</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44.99</v>
+        <v>44.63</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>47.62</v>
+        <v>46.62</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>51.45</v>
+        <v>49.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>54.62</v>
+        <v>51.58</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26026,26 +26026,26 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>54.02</v>
+        <v>56.26</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>54.79</v>
+        <v>56.23</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>54.25</v>
+        <v>59.61</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>56.5</v>
+        <v>61.99</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>57.25</v>
+        <v>64.23</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>58.89</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26072,26 +26072,26 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>52.76</v>
+        <v>51.52</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>51.85</v>
+        <v>51.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>52.25</v>
+        <v>52.99</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>53.38</v>
+        <v>54.94</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>55.39</v>
+        <v>58.55</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>60.12</v>
+        <v>62.13</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26118,26 +26118,26 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>52.82</v>
+        <v>53.2</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>54.85</v>
+        <v>55.9</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>56.75</v>
+        <v>58.8</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>59.93</v>
+        <v>63.16</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>64.63</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26164,26 +26164,26 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>49.51</v>
+        <v>47.18</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46.54</v>
+        <v>46.26</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45.21</v>
+        <v>47.79</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>46.03</v>
+        <v>51.64</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>48.86</v>
+        <v>56.61</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>54.89</v>
+        <v>61.18</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26210,26 +26210,26 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>47.64</v>
+        <v>49.56</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>48.52</v>
+        <v>51.52</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>49.81</v>
+        <v>52.54</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>49.94</v>
+        <v>55.26</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>50.79</v>
+        <v>57.79</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>49.89</v>
+        <v>58.22</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26256,26 +26256,26 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>51.66</v>
+        <v>53.64</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>53.07</v>
+        <v>54.11</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>53.22</v>
+        <v>53.95</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>52.57</v>
+        <v>53.98</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>51.85</v>
+        <v>53.63</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>49.77</v>
+        <v>53.26</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26302,26 +26302,26 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>40.93</v>
+        <v>42.36</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>40.46</v>
+        <v>44.18</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>41.1</v>
+        <v>46.65</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>41.73</v>
+        <v>50.78</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>42.7</v>
+        <v>53.78</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>41.18</v>
+        <v>52.94</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26348,26 +26348,26 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>42.01</v>
+        <v>42.54</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>40.97</v>
+        <v>44.04</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>41.37</v>
+        <v>46.04</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>41.64</v>
+        <v>48.62</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>39.94</v>
+        <v>50.34</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>48.97</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26394,26 +26394,26 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>49.17</v>
+        <v>49.45</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>48.05</v>
+        <v>51.22</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48.76</v>
+        <v>55.09</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>51.04</v>
+        <v>59.55</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>53.3</v>
+        <v>63.61</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>55.82</v>
+        <v>66.02</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26440,26 +26440,26 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>25.7</v>
+        <v>28.62</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>27.4</v>
+        <v>31.64</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>29.39</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>35.63</v>
+        <v>36.18</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>47.7</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26486,26 +26486,26 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>42.55</v>
+        <v>41.78</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>40.73</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>38.85</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>38.62</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>36.92</v>
+        <v>41.01</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>43.54</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26532,26 +26532,26 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>35.97</v>
+        <v>36.61</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>36.01</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>38.12</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>39.61</v>
+        <v>37.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>45.76</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>40.64</v>
+        <v>46.89</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26578,26 +26578,26 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>60.3</v>
+        <v>56.27</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>57.99</v>
+        <v>53.41</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>55.78</v>
+        <v>50.99</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>53.99</v>
+        <v>49.63</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>53.06</v>
+        <v>49.69</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>53.01</v>
+        <v>49.28</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26624,26 +26624,26 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>57.93</v>
+        <v>53.19</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>55.94</v>
+        <v>52.35</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>55.9</v>
+        <v>50.96</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>55.18</v>
+        <v>50.84</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>55.21</v>
+        <v>52.17</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>55.94</v>
+        <v>53.84</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26670,26 +26670,26 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>62.18</v>
+        <v>57.06</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>59.62</v>
+        <v>56.9</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>60.53</v>
+        <v>55.94</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>60.35</v>
+        <v>56.15</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>60.54</v>
+        <v>58.54</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>62</v>
+        <v>60.59</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26716,26 +26716,26 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>63.57</v>
+        <v>62.9</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>62.98</v>
+        <v>62.65</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>62.36</v>
+        <v>62.42</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>61.66</v>
+        <v>63.65</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>62.15</v>
+        <v>65.83</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>63.72</v>
+        <v>68.78</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26762,26 +26762,26 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>49.83</v>
+        <v>51.29</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>50.43</v>
+        <v>52.96</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>51.43</v>
+        <v>53.61</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>51.19</v>
+        <v>55.15</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>51.31</v>
+        <v>57.01</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>52.35</v>
+        <v>59.72</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26808,26 +26808,26 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>57.92</v>
+        <v>58.58</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>58.82</v>
+        <v>62.64</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>62.72</v>
+        <v>65.92</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>65.64</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>66.73</v>
+        <v>67.58</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>66.04000000000001</v>
+        <v>65.31</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26854,26 +26854,26 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>52.58</v>
+        <v>55.91</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>55.51</v>
+        <v>59.48</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>58.51</v>
+        <v>62.27</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>60.55</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>63.02</v>
+        <v>68.14</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>64.47</v>
+        <v>69.97</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26900,26 +26900,26 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>70.78</v>
+        <v>71.03</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>71.72</v>
+        <v>71.45</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>72.45</v>
+        <v>71.87</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>73.39</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>73.2</v>
+        <v>69.31</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>73.05</v>
+        <v>68.63</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26946,26 +26946,26 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>70.62</v>
+        <v>67.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>67.27</v>
+        <v>64.31</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>64.41</v>
+        <v>62.04</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>62.2</v>
+        <v>60.71</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>60.9</v>
+        <v>60.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>61.71</v>
+        <v>60.61</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -26992,26 +26992,26 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>53.98</v>
+        <v>55.01</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>54.04</v>
+        <v>55.62</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>54.14</v>
+        <v>56.12</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>53.77</v>
+        <v>55.97</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>52.08</v>
+        <v>55.29</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>50.05</v>
+        <v>52.61</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27038,26 +27038,26 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>58.45</v>
+        <v>60.35</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>59.64</v>
+        <v>61.15</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>59.8</v>
+        <v>61.09</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>58.79</v>
+        <v>61.74</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>57.96</v>
+        <v>61.27</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>57.66</v>
+        <v>60.95</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27084,26 +27084,26 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>54.04</v>
+        <v>54.67</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>56.49</v>
+        <v>57.45</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>60.06</v>
+        <v>60</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>62.83</v>
+        <v>59.88</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>62.62</v>
+        <v>59.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>62.19</v>
+        <v>58.36</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27130,26 +27130,26 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>51.12</v>
+        <v>47.63</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>50.14</v>
+        <v>44.38</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>48.53</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>50.48</v>
+        <v>41.23</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>37.16</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27176,26 +27176,26 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>53.51</v>
+        <v>51.56</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>53.41</v>
+        <v>52.26</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>55.15</v>
+        <v>52.25</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>56.53</v>
+        <v>51.64</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>57.71</v>
+        <v>52.32</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>59.09</v>
+        <v>51.72</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27222,26 +27222,26 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>53.05</v>
+        <v>49.27</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>50.14</v>
+        <v>47.45</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.94</v>
+        <v>46.01</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>48.47</v>
+        <v>44.47</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>48.37</v>
+        <v>43.75</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>49.2</v>
+        <v>42.78</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27268,26 +27268,26 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>53.13</v>
+        <v>52.27</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>53.5</v>
+        <v>51.24</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>53.21</v>
+        <v>50.18</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>53.26</v>
+        <v>49.35</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>54.15</v>
+        <v>50.08</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>56.2</v>
+        <v>51.59</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27314,26 +27314,26 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>52.04</v>
+        <v>51.36</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>51.95</v>
+        <v>51.76</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>52.49</v>
+        <v>52.66</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>53.53</v>
+        <v>53.77</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>54.65</v>
+        <v>55.6</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>57.47</v>
+        <v>54.86</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27363,23 +27363,23 @@
         <v>65.59</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>65.48</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>65.58</v>
+        <v>65.72</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>65.91</v>
+        <v>66.16</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>66.48</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>68.84</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27406,26 +27406,26 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>50.62</v>
+        <v>48.63</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>50.92</v>
+        <v>46.53</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>49.91</v>
+        <v>45.14</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>50.29</v>
+        <v>45.02</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>53.27</v>
+        <v>46.72</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>57.31</v>
+        <v>47.88</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27452,26 +27452,26 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>33.63</v>
+        <v>35.17</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>33.83</v>
+        <v>36.97</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>34.93</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>33.49</v>
+        <v>39.14</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>42.59</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27498,26 +27498,26 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>51.27</v>
+        <v>53.04</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>51.79</v>
+        <v>54.53</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>52.72</v>
+        <v>56.64</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>53.91</v>
+        <v>58.89</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>54.62</v>
+        <v>60.69</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>54.31</v>
+        <v>60.69</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27544,26 +27544,26 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>49.28</v>
+        <v>47.24</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>46.22</v>
+        <v>46.77</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45.32</v>
+        <v>46.71</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>44.57</v>
+        <v>47.05</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>43.88</v>
+        <v>47.29</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>42.35</v>
+        <v>46.41</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27589,27 +27589,27 @@
           <t>大麦</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n">
-        <v>39.86</v>
+      <c r="E44" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>40.32</v>
+        <v>43.12</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>41.6</v>
+        <v>44.77</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>42.3</v>
+        <v>47.51</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>43.55</v>
+        <v>48.87</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>43.63</v>
+        <v>45.43</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27636,26 +27636,26 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>60.02</v>
+        <v>55.83</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>57.5</v>
+        <v>52.81</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>55.14</v>
+        <v>50.31</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>53.27</v>
+        <v>49.02</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>52.42</v>
+        <v>49.18</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>52.47</v>
+        <v>48.85</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27682,26 +27682,26 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>57.71</v>
+        <v>64.08</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>58.48</v>
+        <v>63.14</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>56.14</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>54.78</v>
+        <v>63.98</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>52.95</v>
+        <v>60.14</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>50.96</v>
+        <v>55.19</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27728,26 +27728,26 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>71.06</v>
+        <v>71.95</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>72.43000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>71.39</v>
+        <v>68.33</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>69.45999999999999</v>
+        <v>65.83</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>67.88</v>
+        <v>61.85</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>65.28</v>
+        <v>57.23</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27774,26 +27774,26 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>48.33</v>
+        <v>50.14</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>49.58</v>
+        <v>50.78</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>49.76</v>
+        <v>51.41</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>49.75</v>
+        <v>51.88</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>49.27</v>
+        <v>52.5</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>48.59</v>
+        <v>53.1</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27820,26 +27820,26 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>52.63</v>
+        <v>57.39</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>53.26</v>
+        <v>56.75</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>51.14</v>
+        <v>56.47</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>48.67</v>
+        <v>55.2</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46.33</v>
+        <v>50.19</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>43.34</v>
+        <v>46.49</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27865,27 +27865,27 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
-        <v>79.26000000000001</v>
+      <c r="E50" s="5" t="n">
+        <v>80.54000000000001</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>81.06</v>
+        <v>81.78</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>82.65000000000001</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>81.48999999999999</v>
+        <v>81.59</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>75.67</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>78.61</v>
+        <v>71.22</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27912,26 +27912,26 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>67.53</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>65.2</v>
+        <v>71.75</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>62.17</v>
+        <v>71.98</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>58.2</v>
+        <v>72.66</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>54.37</v>
+        <v>70.7</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>52.82</v>
+        <v>66.75</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27958,26 +27958,26 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>49.84</v>
+        <v>51.31</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>50.45</v>
+        <v>52.99</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>51.47</v>
+        <v>53.64</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>51.23</v>
+        <v>55.17</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>51.35</v>
+        <v>57.03</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>52.39</v>
+        <v>59.71</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28004,26 +28004,26 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>57.83</v>
+        <v>58.41</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>58.66</v>
+        <v>62.42</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>62.52</v>
+        <v>65.66</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>65.43000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>66.51000000000001</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>65.81</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28050,26 +28050,26 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>52.63</v>
+        <v>55.88</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>55.49</v>
+        <v>59.4</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>58.44</v>
+        <v>62.17</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>60.47</v>
+        <v>65.58</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>62.9</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>64.34999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28096,26 +28096,26 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>67.26000000000001</v>
+        <v>67.44</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>68.04000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>68.95999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>70.25</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>70.42</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>70.34999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28142,26 +28142,26 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>70.19</v>
+        <v>66.69</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>66.77</v>
+        <v>63.84</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>63.95</v>
+        <v>61.69</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>61.87</v>
+        <v>60.44</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>60.64</v>
+        <v>60.41</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>61.56</v>
+        <v>60.5</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28188,26 +28188,26 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>53.92</v>
+        <v>54.92</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>53.96</v>
+        <v>55.46</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>53.99</v>
+        <v>55.9</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>53.56</v>
+        <v>55.69</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>51.83</v>
+        <v>54.97</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>49.76</v>
+        <v>52.29</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28234,26 +28234,26 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>39.96</v>
+        <v>40.09</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>40.94</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>40.99</v>
+        <v>42.69</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>43.1</v>
+        <v>43.71</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>44.69</v>
+        <v>44.81</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>43.68</v>
+        <v>45.16</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28280,26 +28280,26 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46.45</v>
+        <v>44.71</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>43.47</v>
+        <v>43.66</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>41.62</v>
+        <v>44.52</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>41.33</v>
+        <v>46.71</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>41.75</v>
+        <v>48.02</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>40.28</v>
+        <v>46.85</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28326,26 +28326,26 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46.18</v>
+        <v>47.5</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>45.37</v>
+        <v>47.17</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>44.1</v>
+        <v>48.23</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>43.33</v>
+        <v>49.71</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>41.92</v>
+        <v>50.78</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>42.81</v>
+        <v>50.99</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28372,26 +28372,26 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>48.17</v>
+        <v>47.1</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>46.53</v>
+        <v>45.89</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45.19</v>
+        <v>46.2</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>45.38</v>
+        <v>47.02</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>46.02</v>
+        <v>48.08</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>44.25</v>
+        <v>48.07</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28418,26 +28418,26 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>64.66</v>
+        <v>62.31</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>61.95</v>
+        <v>58.77</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>58.22</v>
+        <v>51.83</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>44.89</v>
+        <v>45.52</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>38.98</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>37.44</v>
+        <v>33.27</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28464,26 +28464,26 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>74.73</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>75.26000000000001</v>
+        <v>73.44</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>72.31</v>
+        <v>67.34</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>65.77</v>
+        <v>61.59</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>59.51</v>
+        <v>55.64</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>53.7</v>
+        <v>48.06</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28510,26 +28510,26 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>56.2</v>
+        <v>57.28</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>55.8</v>
+        <v>56.67</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>54.29</v>
+        <v>52.8</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>49.28</v>
+        <v>50.09</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>44.83</v>
+        <v>47.51</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>42.05</v>
+        <v>41.16</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28556,26 +28556,26 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>65.31999999999999</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>63.92</v>
+        <v>63.29</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>61.39</v>
+        <v>60.61</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>57.74</v>
+        <v>58.79</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>54.62</v>
+        <v>55.3</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>50.36</v>
+        <v>49.56</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28602,26 +28602,26 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>52.62</v>
+        <v>56.42</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>54.91</v>
+        <v>57.65</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>55.3</v>
+        <v>54.42</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>50.92</v>
+        <v>51.08</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>46.06</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>41.08</v>
+        <v>46.32</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>38.28</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28648,26 +28648,26 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>62.19</v>
+        <v>63.47</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>63.34</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>64.91</v>
+        <v>66.33</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>66.45999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>68.48</v>
+        <v>70.28</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>71.67</v>
+        <v>71.72</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28694,26 +28694,26 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>49.41</v>
+        <v>46.7</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>47.7</v>
+        <v>46.87</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>48.63</v>
+        <v>48.06</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>51.23</v>
+        <v>48.91</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>53.96</v>
+        <v>50.37</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>57.04</v>
+        <v>49.95</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28740,26 +28740,26 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>51.63</v>
+        <v>48.11</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>50.63</v>
+        <v>44.84</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>48.98</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>50.73</v>
+        <v>41.66</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>37.47</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28786,26 +28786,26 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>53.5</v>
+        <v>51.56</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>53.41</v>
+        <v>52.26</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>55.15</v>
+        <v>52.25</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>56.53</v>
+        <v>51.64</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>57.69</v>
+        <v>52.31</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>59.07</v>
+        <v>51.71</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28832,26 +28832,26 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>53.06</v>
+        <v>49.28</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>50.14</v>
+        <v>47.46</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>48.94</v>
+        <v>46.01</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>48.47</v>
+        <v>44.47</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>48.37</v>
+        <v>43.75</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>49.2</v>
+        <v>42.79</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28878,26 +28878,26 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>53.15</v>
+        <v>52.27</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>53.49</v>
+        <v>51.25</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>53.19</v>
+        <v>50.18</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>53.21</v>
+        <v>49.36</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>54.09</v>
+        <v>50.03</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>56.06</v>
+        <v>51.45</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28924,26 +28924,26 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>52.04</v>
+        <v>51.37</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>51.95</v>
+        <v>51.77</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>52.5</v>
+        <v>52.67</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>53.54</v>
+        <v>53.78</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>54.66</v>
+        <v>55.61</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>57.48</v>
+        <v>54.87</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28973,23 +28973,23 @@
         <v>65.52</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>65.52</v>
+        <v>65.42</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>65.52</v>
+        <v>65.66</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>65.84999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>66.41</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>68.75</v>
+        <v>66.62</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29016,26 +29016,26 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>50.82</v>
+        <v>48.83</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>51.1</v>
+        <v>46.79</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>50.15</v>
+        <v>45.41</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>50.55</v>
+        <v>45.25</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>53.49</v>
+        <v>46.83</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>57.28</v>
+        <v>48</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29062,26 +29062,26 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>47.22</v>
+        <v>45.93</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>47.82</v>
+        <v>46.72</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>49.8</v>
+        <v>47.68</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>52.1</v>
+        <v>47.97</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>54.28</v>
+        <v>48.64</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>55.37</v>
+        <v>49.35</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29108,26 +29108,26 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>34.4</v>
+        <v>35.84</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>34.55</v>
+        <v>37.41</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>35.43</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>35.65</v>
-      </c>
-      <c r="J77" s="4" t="n">
-        <v>33.46</v>
+        <v>39.25</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>42.19</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29154,26 +29154,26 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>40.34</v>
+        <v>40.17</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>39.65</v>
+        <v>39.15</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>38.4</v>
+        <v>37.92</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>36.75</v>
+        <v>36.13</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>34.28</v>
+        <v>35.58</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>32.65</v>
+        <v>37.13</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29200,26 +29200,26 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>51.22</v>
+        <v>53</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>51.75</v>
+        <v>54.49</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>52.68</v>
+        <v>56.6</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>53.85</v>
+        <v>58.82</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>54.53</v>
+        <v>60.6</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>54.2</v>
+        <v>60.62</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29246,26 +29246,26 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>49.33</v>
+        <v>47.2</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.19</v>
+        <v>46.65</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>45.22</v>
+        <v>46.5</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>44.38</v>
+        <v>46.8</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>43.65</v>
+        <v>47.05</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>42.13</v>
+        <v>46.25</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29291,27 +29291,27 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E81" s="4" t="n">
-        <v>39.9</v>
+      <c r="E81" s="3" t="n">
+        <v>41.32</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>40.34</v>
+        <v>43.11</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>41.61</v>
+        <v>44.75</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>42.3</v>
+        <v>47.48</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>43.55</v>
+        <v>48.84</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>43.64</v>
+        <v>45.4</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29338,26 +29338,26 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>47.4</v>
+        <v>44.78</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>46.16</v>
+        <v>43.52</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>45.72</v>
+        <v>42.14</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>45.84</v>
+        <v>40.95</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>47.04</v>
+        <v>40.8</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>47.89</v>
+        <v>41.51</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29384,26 +29384,26 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>28.62</v>
+        <v>29.97</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>29.4</v>
+        <v>31.96</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>30.7</v>
+        <v>34.83</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>32.61</v>
-      </c>
-      <c r="I83" s="4" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="J83" s="4" t="n">
-        <v>39.8</v>
+        <v>39.22</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>49.64</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29430,26 +29430,26 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>41.66</v>
+        <v>41.79</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>40.23</v>
+        <v>42.94</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>40.28</v>
+        <v>44.95</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>40.59</v>
+        <v>47.67</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>40.46</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>39.17</v>
+        <v>49.63</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>48.74</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29476,26 +29476,26 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>44.15</v>
+        <v>42.08</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>42.57</v>
+        <v>42.14</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>42.89</v>
+        <v>43.29</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>44.47</v>
+        <v>45.23</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>47.05</v>
+        <v>48.74</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>49.74</v>
+        <v>51.27</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29522,26 +29522,26 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>44.6</v>
+        <v>44.19</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>43.19</v>
+        <v>43.97</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>42.28</v>
+        <v>45.23</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>42.5</v>
+        <v>47.03</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>42.8</v>
+        <v>48.16</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>42.02</v>
+        <v>48.85</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29568,26 +29568,26 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>36.04</v>
+        <v>35.81</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>35.19</v>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v>37.03</v>
+        <v>38.24</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>42.88</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>40.84</v>
+        <v>48.01</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>44.72</v>
+        <v>53.42</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>49.66</v>
+        <v>57.44</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29614,26 +29614,26 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>50.54</v>
+        <v>48.34</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>49.7</v>
+        <v>47.49</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>49.69</v>
+        <v>46.78</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>50.39</v>
+        <v>45.9</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>51.49</v>
+        <v>45.96</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>52.74</v>
+        <v>47.26</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29660,26 +29660,26 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>60.51</v>
+        <v>56.46</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>58.15</v>
+        <v>53.56</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>55.88</v>
+        <v>51.09</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>54.03</v>
+        <v>49.73</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>53.1</v>
+        <v>49.8</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>53.09</v>
+        <v>49.41</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29706,26 +29706,26 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>57.68</v>
+        <v>52.81</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>55.64</v>
+        <v>51.96</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>55.62</v>
+        <v>50.61</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>54.95</v>
+        <v>50.51</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>55.02</v>
+        <v>51.85</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>55.74</v>
+        <v>53.51</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29752,26 +29752,26 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>62.29</v>
+        <v>57.19</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>59.73</v>
+        <v>57.01</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>60.62</v>
+        <v>56.07</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>60.45</v>
+        <v>56.28</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>60.62</v>
+        <v>58.68</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>62.12</v>
+        <v>60.74</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29798,26 +29798,26 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>49.12</v>
+        <v>51.58</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>50.68</v>
+        <v>52.97</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>51.41</v>
+        <v>54.93</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>52.42</v>
+        <v>56.65</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>52.81</v>
+        <v>58.01</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>52.33</v>
+        <v>59.23</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29844,26 +29844,26 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>61.91</v>
+        <v>58.74</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>58.16</v>
+        <v>53.88</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>53.06</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>45.56</v>
+        <v>46.5</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>39.9</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>38.93</v>
+        <v>34.07</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>32.17</v>
+        <v>30.57</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29890,26 +29890,26 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>67.06999999999999</v>
+        <v>67.88</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>68.7</v>
+        <v>66.92</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>68.33</v>
+        <v>61.8</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>64.42</v>
+        <v>55.57</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>59.11</v>
+        <v>51.55</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>51.56</v>
+        <v>49.3</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29936,26 +29936,26 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>64.27</v>
+        <v>61.41</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>60.35</v>
+        <v>56.01</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>54.62</v>
+        <v>51.2</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>49.48</v>
+        <v>46.93</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>44.85</v>
+        <v>41.38</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>39.19</v>
+        <v>37.22</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -29982,26 +29982,26 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>59.3</v>
+        <v>57.72</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>57.91</v>
+        <v>55.46</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>55.78</v>
+        <v>50.97</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>51.58</v>
+        <v>46.35</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>47.21</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>40.43</v>
+        <v>42.15</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>39.14</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30028,26 +30028,26 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>70.56999999999999</v>
+        <v>71.37</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>70.01000000000001</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>67.72</v>
+        <v>66.64</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>63.54</v>
+        <v>64.23</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>59.8</v>
+        <v>59.66</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>54.51</v>
+        <v>52.8</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30074,26 +30074,26 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>63.55</v>
+        <v>61.47</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>61.51</v>
+        <v>57.18</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>57.25</v>
+        <v>50.64</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>50.76</v>
-      </c>
-      <c r="I98" s="3" t="n">
-        <v>44.01</v>
+        <v>44.08</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>39.38</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>37.98</v>
+        <v>37.19</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30120,26 +30120,26 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>60.72</v>
+        <v>62.75</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>61.61</v>
+        <v>63.46</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>61.81</v>
+        <v>65.45</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>62.98</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>65.44</v>
+        <v>73.39</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>71.23</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30166,26 +30166,26 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>45.52</v>
+        <v>44.27</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>45.42</v>
+        <v>44.12</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>45.99</v>
+        <v>44.33</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>47.39</v>
+        <v>45.45</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>50.31</v>
+        <v>47.07</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>52.7</v>
+        <v>49.12</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30212,26 +30212,26 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>35.86</v>
+        <v>36.85</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>35.69</v>
+        <v>38.18</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>36.43</v>
-      </c>
-      <c r="H101" s="4" t="n">
-        <v>36.79</v>
-      </c>
-      <c r="I101" s="4" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="J101" s="4" t="n">
-        <v>34.13</v>
+        <v>39.5</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>41.77</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30258,26 +30258,26 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>46.85</v>
+        <v>46.17</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>45.77</v>
+        <v>44.86</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>44.28</v>
+        <v>43.32</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="I102" s="4" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="J102" s="4" t="n">
-        <v>38.3</v>
+        <v>41.36</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>41.47</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30304,26 +30304,26 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>60.86</v>
+        <v>63.6</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>62.3</v>
+        <v>64.27</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>62.43</v>
+        <v>64.8</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>62.18</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>62.13</v>
+        <v>67.33</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>63.59</v>
+        <v>68.31</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30350,26 +30350,26 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>46.11</v>
+        <v>50.93</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>49.24</v>
+        <v>55.75</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>53.06</v>
+        <v>61.92</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>57.84</v>
+        <v>67.22</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>61.18</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>61.88</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30396,26 +30396,26 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>53.86</v>
+        <v>55.94</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>55.57</v>
+        <v>57.64</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>57.1</v>
+        <v>58.28</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>57.47</v>
+        <v>58.01</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>56.75</v>
+        <v>57.21</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>55.5</v>
+        <v>56.17</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30442,26 +30442,26 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>56.97</v>
+        <v>62.38</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>59.15</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>60.08</v>
+        <v>65.8</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>60.56</v>
+        <v>67.11</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>60.41</v>
+        <v>67.14</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>60.56</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30488,26 +30488,26 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>51.62</v>
+        <v>53.44</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>52.7</v>
+        <v>54.82</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>53.68</v>
+        <v>58.02</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>55.98</v>
+        <v>61.1</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>57.34</v>
+        <v>62.87</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>57.54</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30534,26 +30534,26 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>58.49</v>
+        <v>58.37</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>56.95</v>
+        <v>56.39</v>
       </c>
       <c r="G108" s="3" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="H108" s="3" t="n">
         <v>54.43</v>
       </c>
-      <c r="H108" s="3" t="n">
-        <v>52.24</v>
-      </c>
       <c r="I108" s="3" t="n">
-        <v>50.36</v>
+        <v>53.4</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>49.56</v>
+        <v>53.4</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30580,26 +30580,26 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>57.92</v>
+        <v>60.38</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>59.18</v>
+        <v>61.95</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>59.97</v>
+        <v>63.87</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>60.7</v>
+        <v>66.23</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>61.11</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>61.93</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30625,27 +30625,27 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E110" s="4" t="n">
-        <v>39.62</v>
+      <c r="E110" s="3" t="n">
+        <v>40.48</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>41.09</v>
+        <v>42.73</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>43.48</v>
+        <v>45.73</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>46.74</v>
+        <v>49.18</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>50.52</v>
+        <v>52.12</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>53.44</v>
+        <v>52.19</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30672,26 +30672,26 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>50.6</v>
+        <v>50.17</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>49.99</v>
+        <v>50.02</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>49.7</v>
+        <v>51.89</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>51.22</v>
+        <v>53.02</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>51.87</v>
+        <v>53.51</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>52.92</v>
+        <v>53.1</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30718,26 +30718,26 @@
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>48.18</v>
+        <v>47.48</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>47.77</v>
+        <v>47.32</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>47.5</v>
+        <v>48.87</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>48.94</v>
+        <v>50.09</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>50.14</v>
+        <v>51.01</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>51.64</v>
+        <v>51.24</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30764,26 +30764,26 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>45.48</v>
+        <v>45.78</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>45.35</v>
+        <v>46.5</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>45.8</v>
+        <v>48.91</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>47.63</v>
+        <v>52.75</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>50.22</v>
+        <v>55.86</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>52.19</v>
+        <v>57.67</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30810,26 +30810,26 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>43.98</v>
+        <v>41.91</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>42.45</v>
+        <v>41</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>41.59</v>
+        <v>41.5</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>42.34</v>
+        <v>42.53</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>43.71</v>
+        <v>44.31</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>45.25</v>
+        <v>46.81</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30856,26 +30856,26 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>38.08</v>
+        <v>37.44</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>36.95</v>
+        <v>37.83</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>36.99</v>
-      </c>
-      <c r="H115" s="4" t="n">
-        <v>38.12</v>
-      </c>
-      <c r="I115" s="4" t="n">
-        <v>39.31</v>
+        <v>39.64</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>43.39</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>40.02</v>
+        <v>46.6</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30902,26 +30902,26 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>45.43</v>
+        <v>45.33</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>45.07</v>
+        <v>45.23</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>44.65</v>
+        <v>48.77</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>47.62</v>
+        <v>51.51</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>49.3</v>
+        <v>54.2</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>51.02</v>
+        <v>56.62</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30948,26 +30948,26 @@
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>52.39</v>
+        <v>50.55</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>51.19</v>
+        <v>50</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>50.7</v>
+        <v>51.05</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>51.96</v>
+        <v>52.05</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>53.36</v>
+        <v>52.91</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>55.1</v>
+        <v>53.34</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -30994,26 +30994,26 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>48.02</v>
+        <v>47.4</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>47.67</v>
+        <v>47.16</v>
       </c>
       <c r="G118" s="3" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="I118" s="3" t="n">
         <v>47.52</v>
       </c>
-      <c r="H118" s="3" t="n">
-        <v>47.89</v>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>47.75</v>
-      </c>
       <c r="J118" s="3" t="n">
-        <v>47.04</v>
+        <v>48.73</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31040,26 +31040,26 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>53.73</v>
+        <v>54.1</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>54.27</v>
+        <v>54.5</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>54.67</v>
+        <v>55.23</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>55.6</v>
+        <v>55.69</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>56.4</v>
+        <v>55.75</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>56.03</v>
+        <v>56.27</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31086,26 +31086,26 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>48.79</v>
+        <v>49.21</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>49.19</v>
+        <v>49.53</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>49.39</v>
+        <v>50.46</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>50.15</v>
+        <v>51.79</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>51.41</v>
+        <v>53.62</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>52.97</v>
+        <v>54</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31132,26 +31132,26 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>49.02</v>
+        <v>48.21</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>48.08</v>
+        <v>47.91</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>47.44</v>
+        <v>48.09</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>47.17</v>
+        <v>48.78</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>47.17</v>
+        <v>49.37</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>47.7</v>
+        <v>49.62</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31178,26 +31178,26 @@
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>49.2</v>
+        <v>49.15</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>49.12</v>
+        <v>49.14</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>48.78</v>
+        <v>50.74</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>49.95</v>
+        <v>51.71</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>50.41</v>
+        <v>52.45</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>52.15</v>
+        <v>51.98</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31224,26 +31224,26 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>63.09</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>62.7</v>
+        <v>60.46</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>59.94</v>
+        <v>58.86</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>58.1</v>
+        <v>56.43</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>55.43</v>
+        <v>53</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>51.66</v>
+        <v>48.77</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31270,26 +31270,26 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>54.15</v>
+        <v>57.94</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>57.09</v>
+        <v>60</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>58.7</v>
+        <v>60.98</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>58.9</v>
+        <v>61.43</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>58.06</v>
+        <v>60.94</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>55.18</v>
+        <v>60.08</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31316,26 +31316,26 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>47.74</v>
+        <v>50.96</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>51</v>
+        <v>54.52</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>54.27</v>
+        <v>57.35</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>56.04</v>
+        <v>59.85</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>56.6</v>
+        <v>59.11</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>52.94</v>
+        <v>55.95</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31362,26 +31362,26 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>62.97</v>
+        <v>62.05</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>62.23</v>
+        <v>61.97</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>62.37</v>
+        <v>61.97</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>62.66</v>
+        <v>60.98</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>61.9</v>
+        <v>58.57</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>59.6</v>
+        <v>54.53</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31408,26 +31408,26 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>70.75</v>
+        <v>71.58</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>72.12</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>69.22</v>
+        <v>65.55</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>67.73</v>
+        <v>61.64</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>65.29000000000001</v>
+        <v>57.01</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31453,27 +31453,27 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E128" s="3" t="n">
-        <v>76.12</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>79.39</v>
+      <c r="E128" s="5" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>83.22</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>81.58</v>
+        <v>85.25</v>
       </c>
       <c r="H128" s="5" t="n">
-        <v>82.73</v>
+        <v>85.62</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>81.91</v>
+        <v>85.16</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>80.69</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31500,26 +31500,26 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>48.27</v>
+        <v>50.07</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>49.52</v>
+        <v>50.77</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>49.77</v>
+        <v>51.52</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>49.88</v>
+        <v>52.06</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>49.49</v>
+        <v>52.72</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>48.85</v>
+        <v>53.35</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31546,26 +31546,26 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>81.06</v>
+        <v>82.52</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>83.04000000000001</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>84.55</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>84.93000000000001</v>
-      </c>
-      <c r="I130" s="5" t="n">
-        <v>83.83</v>
-      </c>
-      <c r="J130" s="5" t="n">
-        <v>81.11</v>
+        <v>82.29000000000001</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>78.76000000000001</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>74.77</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31592,26 +31592,26 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>67.62</v>
+        <v>71.53</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>65.12</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>61.96</v>
+        <v>71.67</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>57.88</v>
+        <v>72.41</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>53.94</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>52.41</v>
+        <v>66.89</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31638,26 +31638,26 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>66.78</v>
+        <v>67.73</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>67.62</v>
+        <v>69.16</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>68.76000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>69.12</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>67.98999999999999</v>
+        <v>67.27</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>62.58</v>
+        <v>63.98</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31684,26 +31684,26 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>43.74</v>
+        <v>45.68</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>45.32</v>
+        <v>46.28</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>45.88</v>
+        <v>45.5</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>44.53</v>
+        <v>45.98</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>43.79</v>
+        <v>45.13</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>40.36</v>
+        <v>43.77</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31730,26 +31730,26 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>41.88</v>
+        <v>42.15</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>41.22</v>
+        <v>42.87</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>41.3</v>
+        <v>44.29</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>41.74</v>
+        <v>46.83</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>42.57</v>
+        <v>50.49</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>45.1</v>
+        <v>53.07</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31776,26 +31776,26 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>40.71</v>
+        <v>41.59</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>41.3</v>
+        <v>43.25</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>42.86</v>
+        <v>43.53</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>42.83</v>
+        <v>44.44</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>43.24</v>
+        <v>45.74</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>43.98</v>
+        <v>47.05</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31822,26 +31822,26 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>52.61</v>
+        <v>54.45</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>54.14</v>
+        <v>56.56</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>56.01</v>
+        <v>59.05</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>58.04</v>
+        <v>59.68</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>57.82</v>
+        <v>60.69</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>58.63</v>
+        <v>61.4</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31868,26 +31868,26 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>58.66</v>
+        <v>61.23</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>61.46</v>
+        <v>62.8</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>63.01</v>
+        <v>62.98</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>63.13</v>
+        <v>62.02</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>61.96</v>
+        <v>62.26</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>62.86</v>
+        <v>63.27</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31914,26 +31914,26 @@
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>64.04000000000001</v>
+        <v>63.61</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>64.05</v>
+        <v>62.21</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>63.04</v>
+        <v>59.79</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>61.21</v>
+        <v>56.62</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>58.96</v>
+        <v>54.22</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>58.86</v>
+        <v>54.38</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31960,26 +31960,26 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>44.1</v>
+        <v>44.81</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>44.55</v>
+        <v>45.15</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>44.72</v>
+        <v>45.69</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>44.84</v>
+        <v>46.28</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>44.7</v>
+        <v>47.76</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>45.85</v>
+        <v>48.43</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32006,26 +32006,26 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>47.94</v>
+        <v>49.08</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>48.75</v>
+        <v>50.64</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>49.89</v>
+        <v>51.92</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>50.43</v>
+        <v>52.44</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>49.82</v>
+        <v>53.97</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>50.62</v>
+        <v>56.07</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32052,26 +32052,26 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>41.76</v>
+        <v>43.24</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>42.62</v>
+        <v>45.05</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>44.03</v>
+        <v>46.65</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>44.96</v>
+        <v>48.69</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>45.77</v>
+        <v>51.75</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>48.56</v>
+        <v>52.77</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32098,26 +32098,26 @@
         </is>
       </c>
       <c r="E142" s="3" t="n">
-        <v>61.61</v>
+        <v>63.32</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>63.5</v>
+        <v>65.5</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>65.69</v>
+        <v>66.12</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>66.31</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>66.13</v>
+        <v>65.09</v>
       </c>
       <c r="J142" s="3" t="n">
-        <v>66.45</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32144,26 +32144,26 @@
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>71.01000000000001</v>
+        <v>73.78</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>74.23999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="H143" s="3" t="n">
-        <v>79.63</v>
+        <v>78.78</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>80.29000000000001</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>81.51000000000001</v>
-      </c>
-      <c r="J143" s="5" t="n">
-        <v>82.31999999999999</v>
+        <v>80.27</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>79.95</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32189,27 +32189,27 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E144" s="3" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="F144" s="4" t="n">
-        <v>39.29</v>
+      <c r="E144" s="4" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>40.98</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>40.32</v>
+        <v>43.04</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>41.85</v>
+        <v>45.35</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>43.13</v>
+        <v>47.7</v>
       </c>
       <c r="J144" s="3" t="n">
-        <v>44.12</v>
+        <v>48.98</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32236,26 +32236,26 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>47.83</v>
+        <v>48.29</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>47.58</v>
+        <v>49.77</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>48.55</v>
+        <v>50.68</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>48.67</v>
+        <v>51.83</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>48.47</v>
+        <v>52.8</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>48.58</v>
+        <v>54.83</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32282,26 +32282,26 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>48.18</v>
+        <v>49.85</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>49.32</v>
+        <v>51.37</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>50.45</v>
+        <v>52.49</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>50.85</v>
+        <v>54.13</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>51.3</v>
+        <v>56.43</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>53.06</v>
+        <v>58.06</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32328,26 +32328,26 @@
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>61.27</v>
+        <v>62.42</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>62.96</v>
+        <v>64.75</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>65.65000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>67.41</v>
+        <v>66.16</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>67.95</v>
+        <v>66.63</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>69.97</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32374,26 +32374,26 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>43.51</v>
+        <v>45.33</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>44.83</v>
+        <v>46.56</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>45.79</v>
+        <v>47.9</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>46.61</v>
+        <v>48.91</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>46.81</v>
+        <v>49.77</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>47.88</v>
+        <v>50.03</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32420,26 +32420,26 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>60.08</v>
+        <v>61.42</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>60.11</v>
+        <v>61.68</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>59.78</v>
+        <v>63.16</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>60.32</v>
+        <v>66.59</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>62.34</v>
+        <v>70.87</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>68.13</v>
+        <v>73.88</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32466,26 +32466,26 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>51.76</v>
+        <v>52.73</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>52.08</v>
+        <v>52.4</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>51.53</v>
+        <v>57.32</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>55.73</v>
+        <v>60.38</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>57.88</v>
+        <v>64.53</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>62.69</v>
+        <v>66.83</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32512,26 +32512,26 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>53.5</v>
+        <v>55.74</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>54.28</v>
+        <v>55.61</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>53.66</v>
+        <v>59.17</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>56.06</v>
+        <v>61.67</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>56.95</v>
+        <v>63.95</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>58.64</v>
+        <v>66</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32558,26 +32558,26 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>52.25</v>
+        <v>50.92</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>51.3</v>
+        <v>51.23</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>51.65</v>
+        <v>52.3</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>52.81</v>
+        <v>54.26</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>54.91</v>
+        <v>57.93</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>59.72</v>
+        <v>61.55</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32604,26 +32604,26 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>51.53</v>
+        <v>52.58</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>53.02</v>
+        <v>54</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>54.59</v>
+        <v>56.33</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>57.15</v>
+        <v>59.43</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>60.54</v>
+        <v>63.21</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>64.83</v>
+        <v>65.92</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32650,26 +32650,26 @@
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>49.12</v>
+        <v>46.78</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>46.16</v>
+        <v>45.87</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>44.85</v>
+        <v>47.43</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>45.72</v>
+        <v>51.28</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>48.59</v>
+        <v>56.29</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>54.65</v>
+        <v>60.91</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32696,26 +32696,26 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>47.09</v>
+        <v>43.33</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>44.62</v>
+        <v>42.29</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>44.6</v>
+        <v>41.9</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>45.84</v>
+        <v>41.88</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>48.24</v>
+        <v>43.21</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>50.96</v>
+        <v>43.09</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32742,26 +32742,26 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>62.51</v>
+        <v>63.86</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>63.73</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>65.44</v>
+        <v>66.97</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>67.12</v>
+        <v>68.94</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>69.23999999999999</v>
+        <v>71.05</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>72.52</v>
+        <v>72.48</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32788,26 +32788,26 @@
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>51.24</v>
+        <v>47.33</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>49.86</v>
+        <v>43.54</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>47.68</v>
-      </c>
-      <c r="H157" s="3" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="I157" s="3" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="J157" s="3" t="n">
-        <v>49.27</v>
+        <v>40.01</v>
+      </c>
+      <c r="H157" s="4" t="n">
+        <v>37.78</v>
+      </c>
+      <c r="I157" s="4" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="J157" s="4" t="n">
+        <v>35.87</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32834,26 +32834,26 @@
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>52.24</v>
+        <v>50.17</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>51.82</v>
+        <v>50.78</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>53.4</v>
+        <v>50.97</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>54.94</v>
+        <v>50.59</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>56.34</v>
+        <v>51.46</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>58.18</v>
+        <v>50.96</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32880,26 +32880,26 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>52.73</v>
+        <v>48.98</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>49.82</v>
+        <v>47.17</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>48.62</v>
+        <v>45.78</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>48.18</v>
+        <v>44.26</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>48.08</v>
+        <v>43.58</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>48.94</v>
+        <v>42.68</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32926,26 +32926,26 @@
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>53.24</v>
+        <v>52.26</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>53.52</v>
+        <v>51.15</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>53.17</v>
+        <v>49.97</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>53.11</v>
+        <v>49</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>53.9</v>
+        <v>49.57</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>55.73</v>
+        <v>50.89</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32972,26 +32972,26 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>51.73</v>
+        <v>50.92</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>51.43</v>
+        <v>51.17</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>51.79</v>
+        <v>52.06</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>52.77</v>
+        <v>53.21</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>53.89</v>
+        <v>55.14</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>56.89</v>
+        <v>54.47</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33018,26 +33018,26 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>66.41</v>
+        <v>66.34</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>66.34999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>66.75</v>
+        <v>66.98</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>67.45999999999999</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>67.53</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33064,26 +33064,26 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>49.82</v>
+        <v>47.94</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>50.18</v>
+        <v>45.91</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>49.23</v>
+        <v>44.6</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>49.66</v>
+        <v>44.57</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>52.68</v>
+        <v>46.32</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>56.59</v>
+        <v>47.7</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33110,26 +33110,26 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>47.52</v>
+        <v>49.4</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>48.37</v>
+        <v>51.32</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>49.64</v>
+        <v>52.33</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>49.75</v>
+        <v>55.04</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>50.6</v>
+        <v>57.57</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>49.72</v>
+        <v>58</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33156,26 +33156,26 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>51.71</v>
+        <v>53.66</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>53.09</v>
+        <v>54.12</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>53.24</v>
+        <v>53.99</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>52.61</v>
+        <v>54.02</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>51.89</v>
+        <v>53.67</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>49.83</v>
+        <v>53.32</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33202,26 +33202,26 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>40.93</v>
+        <v>42.36</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>40.46</v>
+        <v>44.18</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>41.1</v>
+        <v>46.65</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>41.73</v>
+        <v>50.78</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>42.7</v>
+        <v>53.78</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>41.18</v>
+        <v>52.94</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33248,26 +33248,26 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>28.97</v>
+        <v>30.35</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>29.78</v>
+        <v>32.31</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>31.03</v>
+        <v>35.11</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>32.87</v>
-      </c>
-      <c r="I167" s="4" t="n">
-        <v>35.53</v>
-      </c>
-      <c r="J167" s="4" t="n">
-        <v>39.73</v>
+        <v>39.33</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="J167" s="3" t="n">
+        <v>49.52</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33294,26 +33294,26 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>42.16</v>
+        <v>42.79</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>41.24</v>
+        <v>44.3</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>41.67</v>
+        <v>46.24</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>41.9</v>
+        <v>48.79</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>41.62</v>
+        <v>50.47</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>40.17</v>
+        <v>49.01</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33340,26 +33340,26 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>23.97</v>
+        <v>26.12</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>25.12</v>
+        <v>28.65</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>26.74</v>
+        <v>32.91</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>29.46</v>
-      </c>
-      <c r="I169" s="4" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="J169" s="4" t="n">
-        <v>33.76</v>
+        <v>37.94</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="J169" s="3" t="n">
+        <v>44.81</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33386,26 +33386,26 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>55.35</v>
+        <v>54.28</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>53.32</v>
+        <v>52.68</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>51.26</v>
+        <v>51.68</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>49.5</v>
+        <v>50.97</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>47.71</v>
+        <v>49.65</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>46.54</v>
+        <v>48.53</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33432,26 +33432,26 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>37.39</v>
+        <v>37.22</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="G171" s="4" t="n">
-        <v>37.91</v>
-      </c>
-      <c r="H171" s="4" t="n">
-        <v>39.99</v>
+        <v>38.5</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>44.41</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>42.09</v>
+        <v>46.87</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>43.58</v>
+        <v>48.2</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33478,26 +33478,26 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="F172" s="3" t="n">
         <v>41.35</v>
       </c>
-      <c r="F172" s="4" t="n">
-        <v>39.78</v>
-      </c>
-      <c r="G172" s="4" t="n">
-        <v>39.22</v>
-      </c>
-      <c r="H172" s="4" t="n">
-        <v>38.54</v>
-      </c>
-      <c r="I172" s="4" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="J172" s="4" t="n">
-        <v>39.86</v>
+      <c r="G172" s="3" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="J172" s="3" t="n">
+        <v>49.66</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33524,26 +33524,26 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>60.27</v>
+        <v>56.23</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>57.95</v>
+        <v>53.37</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>55.74</v>
+        <v>50.96</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>53.95</v>
+        <v>49.61</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>53.03</v>
+        <v>49.66</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>52.99</v>
+        <v>49.26</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33570,26 +33570,26 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>58.12</v>
+        <v>53.43</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>56.15</v>
+        <v>52.58</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>56.09</v>
+        <v>51.16</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>55.33</v>
+        <v>51.02</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>55.34</v>
+        <v>52.32</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>56.08</v>
+        <v>54.01</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33616,26 +33616,26 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>62.3</v>
+        <v>57.23</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>59.75</v>
+        <v>57.06</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>60.62</v>
+        <v>56.12</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>60.44</v>
+        <v>56.32</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>60.59</v>
+        <v>58.7</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>62.08</v>
+        <v>60.75</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33662,26 +33662,26 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>63.97</v>
+        <v>63.44</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>63.52</v>
+        <v>63.22</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>62.92</v>
+        <v>63.06</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>62.27</v>
+        <v>64.34</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>62.79</v>
+        <v>66.5</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>64.28</v>
+        <v>69.62</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33708,26 +33708,26 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>64.11</v>
+        <v>61.83</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>61.37</v>
+        <v>58.89</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>58.31</v>
+        <v>57.3</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>56.51</v>
+        <v>54.79</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>53.75</v>
+        <v>51.3</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>50</v>
+        <v>47.18</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33754,26 +33754,26 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>53.03</v>
+        <v>50.37</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>50.75</v>
+        <v>48.71</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>48.96</v>
+        <v>47.27</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>47.36</v>
+        <v>45.81</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>45.66</v>
+        <v>45.29</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>44.58</v>
+        <v>46.45</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33800,26 +33800,26 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>63.26</v>
+        <v>62.29</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>61.65</v>
+        <v>60.63</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>59.71</v>
+        <v>60.9</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>59.36</v>
+        <v>60.03</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>58.02</v>
+        <v>58.76</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>55.75</v>
+        <v>56.84</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33846,26 +33846,26 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>71.93000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>69.47</v>
+        <v>67</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>66.38</v>
+        <v>66.67</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>65.51000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>63.43</v>
+        <v>62.19</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>59.67</v>
+        <v>58.25</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33892,26 +33892,26 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>74.77</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>75.31999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>72.3</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>65.84</v>
+        <v>61.72</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>59.61</v>
+        <v>55.92</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>53.95</v>
+        <v>48.44</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33938,26 +33938,26 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>68.05</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>68.92</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>68.53</v>
+        <v>62.05</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>64.53</v>
+        <v>55.9</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>59.21</v>
+        <v>51.92</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>51.95</v>
+        <v>49.57</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -33984,26 +33984,26 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>65.17</v>
+        <v>62.18</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>60.97</v>
+        <v>56.95</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>55.3</v>
+        <v>51.6</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>49.48</v>
+        <v>46.03</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>43.56</v>
+        <v>40.35</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>37.8</v>
+        <v>36.56</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34030,26 +34030,26 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>57.43</v>
+        <v>55.81</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>55.93</v>
+        <v>53.7</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>53.92</v>
+        <v>49.66</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>50.11</v>
+        <v>45.58</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>46.2</v>
+        <v>41.57</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>39.61</v>
+        <v>38.64</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34076,26 +34076,26 @@
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>65.02</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>68.89</v>
+        <v>69.28</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>70.89</v>
+        <v>67.7</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>70.14</v>
+        <v>63.83</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>67.45</v>
+        <v>61.2</v>
       </c>
       <c r="J185" s="3" t="n">
-        <v>62.32</v>
+        <v>59.7</v>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34122,26 +34122,26 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>64.73</v>
+        <v>62.53</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>62.64</v>
+        <v>58.28</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>58.47</v>
+        <v>51.67</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>51.97</v>
+        <v>44.93</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>45.09</v>
+        <v>40.24</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>39.05</v>
+        <v>38.05</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34168,26 +34168,26 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>63.64</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>63.96</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>63.52</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>64.11</v>
+        <v>69.91</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>65.97</v>
+        <v>73.67</v>
       </c>
       <c r="J187" s="3" t="n">
-        <v>71.09</v>
+        <v>76.2</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34214,26 +34214,26 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>51.54</v>
+        <v>52.44</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>51.81</v>
+        <v>52.09</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>51.23</v>
+        <v>56.88</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>55.32</v>
+        <v>59.91</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>57.45</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>62.37</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34260,26 +34260,26 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>56.06</v>
+        <v>58.21</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>56.45</v>
+        <v>57.77</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>55.4</v>
+        <v>61.06</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>57.4</v>
+        <v>63.32</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>57.77</v>
+        <v>65.73</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>59.46</v>
+        <v>68.17</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34306,26 +34306,26 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>53.47</v>
+        <v>52.21</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>52.6</v>
+        <v>52.52</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>52.97</v>
+        <v>53.54</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>54.08</v>
+        <v>55.44</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>56.15</v>
+        <v>59.12</v>
       </c>
       <c r="J190" s="3" t="n">
-        <v>60.99</v>
+        <v>62.6</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34352,26 +34352,26 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>52.02</v>
+        <v>53.07</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>53.5</v>
+        <v>54.48</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>55.08</v>
+        <v>56.81</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>57.65</v>
+        <v>59.89</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>61.02</v>
+        <v>63.68</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>65.37</v>
+        <v>66.3</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34398,26 +34398,26 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>51.69</v>
+        <v>49.87</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>49.09</v>
+        <v>49.37</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>48.13</v>
+        <v>51.39</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>49.38</v>
+        <v>55.3</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>52.3</v>
+        <v>60.53</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>59.17</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34444,26 +34444,26 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>63.95</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>63.51</v>
+        <v>61.25</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>60.67</v>
+        <v>59.67</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>58.82</v>
+        <v>57.08</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>55.95</v>
+        <v>53.56</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>52.1</v>
+        <v>49.19</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34490,26 +34490,26 @@
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>62.86</v>
+        <v>61.94</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>62.13</v>
+        <v>61.79</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>62.22</v>
+        <v>61.78</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>62.51</v>
+        <v>60.75</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>61.76</v>
+        <v>58.43</v>
       </c>
       <c r="J194" s="3" t="n">
-        <v>59.59</v>
+        <v>54.5</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34536,26 +34536,26 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>55.4</v>
+        <v>61.47</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>57.06</v>
+        <v>61.5</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>55.96</v>
+        <v>63.47</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>55.67</v>
+        <v>63.18</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>54.32</v>
+        <v>59.46</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>52.17</v>
+        <v>54.25</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34582,26 +34582,26 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>49.61</v>
+        <v>53.9</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>50.35</v>
+        <v>53.49</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>48.74</v>
+        <v>53.26</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>46.95</v>
+        <v>51.81</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>44.95</v>
+        <v>46.74</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>42.08</v>
+        <v>43.46</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34628,26 +34628,26 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>60.8</v>
+        <v>61.53</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>60.49</v>
+        <v>60.96</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>59.36</v>
+        <v>59.81</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>57.21</v>
+        <v>58.01</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>54.15</v>
+        <v>56.38</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>51.89</v>
+        <v>54.31</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34674,26 +34674,26 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>65.44</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>63.37</v>
+        <v>64.08</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>60.89</v>
+        <v>62.27</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>57.79</v>
+        <v>60.65</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>54.81</v>
+        <v>58.2</v>
       </c>
       <c r="J198" s="3" t="n">
-        <v>52.3</v>
+        <v>55.73</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34720,26 +34720,26 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>59.12</v>
+        <v>60.33</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>58.53</v>
+        <v>60.24</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>57.51</v>
+        <v>60.7</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>56.36</v>
+        <v>60.1</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>54.29</v>
+        <v>59.31</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>52.52</v>
+        <v>56.31</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34766,26 +34766,26 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>69.66</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>67.48</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>64.48</v>
+        <v>64.11</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>63.46</v>
+        <v>62.69</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>61.85</v>
+        <v>60.21</v>
       </c>
       <c r="J200" s="3" t="n">
-        <v>58.5</v>
+        <v>56.44</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34812,26 +34812,26 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>65.94</v>
+        <v>64.73</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>64.67</v>
+        <v>63.14</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>63.29</v>
+        <v>63.76</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>64.08</v>
+        <v>63.79</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>64.23999999999999</v>
+        <v>61.86</v>
       </c>
       <c r="J201" s="3" t="n">
-        <v>62.19</v>
+        <v>58.9</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34858,26 +34858,26 @@
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="F202" s="4" t="n">
-        <v>39.98</v>
+        <v>40.12</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>40.97</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>41.02</v>
+        <v>42.72</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>43.13</v>
+        <v>43.74</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>44.72</v>
+        <v>44.83</v>
       </c>
       <c r="J202" s="3" t="n">
-        <v>43.7</v>
+        <v>45.19</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34904,26 +34904,26 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>46.58</v>
+        <v>44.75</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>43.5</v>
+        <v>43.59</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>41.53</v>
+        <v>44.37</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>41.16</v>
+        <v>46.55</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>41.57</v>
+        <v>47.84</v>
       </c>
       <c r="J203" s="3" t="n">
-        <v>40.07</v>
+        <v>46.65</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34950,26 +34950,26 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>48.24</v>
+        <v>47.15</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>46.57</v>
+        <v>45.91</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>45.19</v>
+        <v>46.18</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>45.35</v>
+        <v>46.98</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>45.96</v>
+        <v>48.01</v>
       </c>
       <c r="J204" s="3" t="n">
-        <v>44.17</v>
+        <v>47.97</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -34996,26 +34996,26 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>56.84</v>
+        <v>57.94</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>56.48</v>
+        <v>57.29</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>54.93</v>
+        <v>53.38</v>
       </c>
       <c r="H205" s="3" t="n">
-        <v>49.88</v>
+        <v>50.63</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>45.39</v>
+        <v>47.97</v>
       </c>
       <c r="J205" s="3" t="n">
-        <v>42.51</v>
+        <v>41.56</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35042,26 +35042,26 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>65.66</v>
+        <v>63.56</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>63.25</v>
+        <v>60.38</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>59.85</v>
+        <v>53.63</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>52.96</v>
+        <v>47.78</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>47.04</v>
+        <v>41.17</v>
       </c>
       <c r="J206" s="4" t="n">
-        <v>39.49</v>
+        <v>34.85</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35088,26 +35088,26 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>65.48</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>64.22</v>
+        <v>63.66</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>61.8</v>
+        <v>61.08</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>58.27</v>
+        <v>59.17</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>55.1</v>
+        <v>55.41</v>
       </c>
       <c r="J207" s="3" t="n">
-        <v>50.62</v>
+        <v>49.47</v>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35134,26 +35134,26 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>74.72</v>
+        <v>75.83</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>75.12</v>
+        <v>73.2</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>65.44</v>
+        <v>61.14</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>59.15</v>
+        <v>55.05</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>53.19</v>
+        <v>47.4</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35180,26 +35180,26 @@
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>73.55</v>
+        <v>69.83</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>68.76000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>63.46</v>
+        <v>56.49</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>55.07</v>
+        <v>51</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>49.45</v>
+        <v>46.45</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>45.46</v>
+        <v>43.7</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35226,26 +35226,26 @@
         </is>
       </c>
       <c r="E210" s="3" t="n">
-        <v>49.4</v>
+        <v>46.69</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>47.7</v>
+        <v>46.87</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>48.63</v>
+        <v>48.06</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>51.22</v>
+        <v>48.91</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>53.95</v>
+        <v>50.37</v>
       </c>
       <c r="J210" s="3" t="n">
-        <v>57.03</v>
+        <v>49.94</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35272,26 +35272,26 @@
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>54.04</v>
+        <v>54.66</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>56.48</v>
+        <v>57.45</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>60.07</v>
+        <v>60</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>62.84</v>
+        <v>59.88</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>62.62</v>
+        <v>59.79</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>62.18</v>
+        <v>58.35</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35318,26 +35318,26 @@
         </is>
       </c>
       <c r="E212" s="3" t="n">
-        <v>51.1</v>
+        <v>47.59</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>50.11</v>
+        <v>44.34</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="H212" s="3" t="n">
-        <v>47.63</v>
-      </c>
-      <c r="I212" s="3" t="n">
-        <v>49.13</v>
-      </c>
-      <c r="J212" s="3" t="n">
-        <v>50.45</v>
+        <v>41.18</v>
+      </c>
+      <c r="H212" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="I212" s="4" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="J212" s="4" t="n">
+        <v>37.11</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35364,26 +35364,26 @@
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>53.51</v>
+        <v>51.56</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>53.41</v>
+        <v>52.26</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>55.14</v>
+        <v>52.24</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>56.51</v>
+        <v>51.63</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>57.68</v>
+        <v>52.31</v>
       </c>
       <c r="J213" s="3" t="n">
-        <v>59.07</v>
+        <v>51.71</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35410,26 +35410,26 @@
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>53.06</v>
+        <v>49.28</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>50.14</v>
+        <v>47.46</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>48.95</v>
+        <v>46.02</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>48.48</v>
+        <v>44.47</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>48.37</v>
+        <v>43.75</v>
       </c>
       <c r="J214" s="3" t="n">
-        <v>49.2</v>
+        <v>42.78</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35456,26 +35456,26 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>56.47</v>
+        <v>57.32</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>58.33</v>
+        <v>60.53</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>61.62</v>
+        <v>62.11</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>62.81</v>
+        <v>64.38</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>63.81</v>
+        <v>64.81</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>62.65</v>
+        <v>64.98</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35502,26 +35502,26 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>52.03</v>
+        <v>51.35</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>51.94</v>
+        <v>51.75</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>52.48</v>
+        <v>52.65</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>53.53</v>
+        <v>53.76</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>54.65</v>
+        <v>55.59</v>
       </c>
       <c r="J216" s="3" t="n">
-        <v>57.47</v>
+        <v>54.86</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35551,23 +35551,23 @@
         <v>65.77</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>65.78</v>
+        <v>65.66</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>65.77</v>
+        <v>65.92</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>66.12</v>
+        <v>66.38</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>66.72</v>
+        <v>67.23</v>
       </c>
       <c r="J217" s="3" t="n">
-        <v>69.08</v>
+        <v>66.92</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35594,26 +35594,26 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>33.78</v>
+        <v>35.29</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>33.95</v>
+        <v>37.12</v>
       </c>
       <c r="G218" s="4" t="n">
-        <v>35.07</v>
-      </c>
-      <c r="H218" s="4" t="n">
-        <v>36.12</v>
-      </c>
-      <c r="I218" s="4" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="J218" s="4" t="n">
-        <v>33.71</v>
+        <v>39.35</v>
+      </c>
+      <c r="H218" s="3" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="I218" s="3" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="J218" s="3" t="n">
+        <v>42.89</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35640,26 +35640,26 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>51.55</v>
+        <v>53.15</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>51.91</v>
+        <v>54.61</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>52.82</v>
+        <v>56.71</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>53.99</v>
+        <v>58.95</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>54.7</v>
+        <v>60.75</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>54.38</v>
+        <v>60.78</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35686,26 +35686,26 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>49.21</v>
+        <v>47.2</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>46.18</v>
+        <v>46.77</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>45.32</v>
+        <v>46.75</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>44.6</v>
+        <v>47.11</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>43.92</v>
+        <v>47.38</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>42.38</v>
+        <v>46.49</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35731,27 +35731,27 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E221" s="4" t="n">
-        <v>39.86</v>
+      <c r="E221" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>40.32</v>
+        <v>43.12</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>41.6</v>
+        <v>44.77</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>42.3</v>
+        <v>47.51</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>43.55</v>
+        <v>48.87</v>
       </c>
       <c r="J221" s="3" t="n">
-        <v>43.62</v>
+        <v>45.43</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35778,26 +35778,26 @@
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>41.88</v>
+        <v>42.15</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>41.22</v>
+        <v>42.87</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>41.3</v>
+        <v>44.29</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>41.74</v>
+        <v>46.83</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>42.57</v>
+        <v>50.49</v>
       </c>
       <c r="J222" s="3" t="n">
-        <v>45.1</v>
+        <v>53.07</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35824,26 +35824,26 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>51.89</v>
+        <v>52.51</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>52.3</v>
+        <v>52.73</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>52.46</v>
+        <v>53.89</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>53.53</v>
+        <v>54.52</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>53.81</v>
+        <v>55.29</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>54.97</v>
+        <v>53.55</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35870,26 +35870,26 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>52.61</v>
+        <v>54.45</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>54.14</v>
+        <v>56.56</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>56.01</v>
+        <v>59.05</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>58.04</v>
+        <v>59.68</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>57.82</v>
+        <v>60.69</v>
       </c>
       <c r="J224" s="3" t="n">
-        <v>58.63</v>
+        <v>61.4</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35916,26 +35916,26 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>58.66</v>
+        <v>61.23</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>61.46</v>
+        <v>62.8</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>63.01</v>
+        <v>62.98</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>63.13</v>
+        <v>62.02</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>61.96</v>
+        <v>62.26</v>
       </c>
       <c r="J225" s="3" t="n">
-        <v>62.86</v>
+        <v>63.27</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35962,26 +35962,26 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>52.51</v>
+        <v>55.02</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>54.48</v>
+        <v>57.11</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>56.21</v>
+        <v>58.96</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>57.45</v>
+        <v>60.01</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>57.54</v>
+        <v>61.13</v>
       </c>
       <c r="J226" s="3" t="n">
-        <v>58.77</v>
+        <v>60.86</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36008,26 +36008,26 @@
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>64.04000000000001</v>
+        <v>63.61</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>64.05</v>
+        <v>62.21</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>63.04</v>
+        <v>59.79</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>61.21</v>
+        <v>56.62</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>58.96</v>
+        <v>54.22</v>
       </c>
       <c r="J227" s="3" t="n">
-        <v>58.86</v>
+        <v>54.38</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36054,26 +36054,26 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>47.94</v>
+        <v>49.08</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>48.75</v>
+        <v>50.64</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>49.89</v>
+        <v>51.92</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>50.43</v>
+        <v>52.44</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>49.82</v>
+        <v>53.97</v>
       </c>
       <c r="J228" s="3" t="n">
-        <v>50.62</v>
+        <v>56.07</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36100,26 +36100,26 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>47.94</v>
+        <v>49.08</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>48.75</v>
+        <v>50.64</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>49.89</v>
+        <v>51.92</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>50.43</v>
+        <v>52.44</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>49.82</v>
+        <v>53.97</v>
       </c>
       <c r="J229" s="3" t="n">
-        <v>50.62</v>
+        <v>56.07</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36146,26 +36146,26 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>56.01</v>
+        <v>57.51</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>57.22</v>
+        <v>57.99</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>57.45</v>
+        <v>56.31</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>55.43</v>
+        <v>55.75</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>54.32</v>
+        <v>56.89</v>
       </c>
       <c r="J230" s="3" t="n">
-        <v>56.19</v>
+        <v>57.07</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36192,26 +36192,26 @@
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>71.01000000000001</v>
+        <v>73.78</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>74.23999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="H231" s="3" t="n">
-        <v>79.63</v>
+        <v>78.78</v>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>80.29000000000001</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>81.51000000000001</v>
-      </c>
-      <c r="J231" s="5" t="n">
-        <v>82.31999999999999</v>
+        <v>80.27</v>
+      </c>
+      <c r="J231" s="3" t="n">
+        <v>79.95</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36237,27 +36237,27 @@
           <t>葵籽</t>
         </is>
       </c>
-      <c r="E232" s="3" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="F232" s="4" t="n">
-        <v>39.29</v>
+      <c r="E232" s="4" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>40.98</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>40.32</v>
+        <v>43.04</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>41.85</v>
+        <v>45.35</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>43.13</v>
+        <v>47.7</v>
       </c>
       <c r="J232" s="3" t="n">
-        <v>44.12</v>
+        <v>48.98</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36284,26 +36284,26 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>47.83</v>
+        <v>48.29</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>47.58</v>
+        <v>49.77</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>48.55</v>
+        <v>50.68</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>48.67</v>
+        <v>51.83</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>48.47</v>
+        <v>52.8</v>
       </c>
       <c r="J233" s="3" t="n">
-        <v>48.58</v>
+        <v>54.83</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36330,26 +36330,26 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>48.18</v>
+        <v>49.85</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>49.32</v>
+        <v>51.37</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>50.45</v>
+        <v>52.49</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>50.85</v>
+        <v>54.13</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>51.3</v>
+        <v>56.43</v>
       </c>
       <c r="J234" s="3" t="n">
-        <v>53.06</v>
+        <v>58.06</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36376,26 +36376,26 @@
         </is>
       </c>
       <c r="E235" s="3" t="n">
-        <v>61.27</v>
+        <v>62.42</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>62.96</v>
+        <v>64.75</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>65.65000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>67.41</v>
+        <v>66.16</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>67.95</v>
+        <v>66.63</v>
       </c>
       <c r="J235" s="3" t="n">
-        <v>69.97</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36422,26 +36422,26 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>50.14</v>
+        <v>51.31</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>50.48</v>
+        <v>53.01</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>51.5</v>
+        <v>53.7</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>51.24</v>
+        <v>55.58</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>51.74</v>
+        <v>58.02</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>53.55</v>
+        <v>60.71</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36468,26 +36468,26 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>52.31</v>
+        <v>55.78</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>55.42</v>
+        <v>59.35</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>58.43</v>
+        <v>62.34</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>60.69</v>
+        <v>65.91</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>63.21</v>
+        <v>68.47</v>
       </c>
       <c r="J237" s="3" t="n">
-        <v>64.56999999999999</v>
+        <v>70.39</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36514,26 +36514,26 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>71.31999999999999</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>72.28</v>
+        <v>71.84</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>72.88</v>
+        <v>72.08</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>73.68000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>73.45999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J238" s="3" t="n">
-        <v>73.33</v>
+        <v>68.69</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36560,26 +36560,26 @@
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>69.75</v>
+        <v>66.92</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>66.91</v>
+        <v>65.33</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>65.27</v>
+        <v>64.97</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>65.03</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>65.58</v>
+        <v>66.05</v>
       </c>
       <c r="J239" s="3" t="n">
-        <v>67.43000000000001</v>
+        <v>66.94</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36606,26 +36606,26 @@
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>62.31</v>
+        <v>63.63</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>63.5</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>66.63</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>66.77</v>
+        <v>68.56</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>68.84</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="J240" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>72.11</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36652,26 +36652,26 @@
         </is>
       </c>
       <c r="E241" s="3" t="n">
-        <v>51.45</v>
+        <v>47.58</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>50.11</v>
+        <v>43.83</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>47.97</v>
-      </c>
-      <c r="H241" s="3" t="n">
-        <v>46.75</v>
-      </c>
-      <c r="I241" s="3" t="n">
-        <v>48.22</v>
-      </c>
-      <c r="J241" s="3" t="n">
-        <v>49.67</v>
+        <v>40.36</v>
+      </c>
+      <c r="H241" s="4" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I241" s="4" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="J241" s="4" t="n">
+        <v>36.16</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36698,26 +36698,26 @@
         </is>
       </c>
       <c r="E242" s="3" t="n">
-        <v>52.76</v>
+        <v>48.98</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>49.82</v>
+        <v>47.16</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>48.61</v>
+        <v>45.74</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>48.14</v>
+        <v>44.19</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>48.01</v>
+        <v>43.46</v>
       </c>
       <c r="J242" s="3" t="n">
-        <v>48.84</v>
+        <v>42.53</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36744,26 +36744,26 @@
         </is>
       </c>
       <c r="E243" s="3" t="n">
-        <v>66.16</v>
+        <v>66.14</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>66.17</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>66.16</v>
+        <v>66.31</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>66.56</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>67.23999999999999</v>
+        <v>67.69</v>
       </c>
       <c r="J243" s="3" t="n">
-        <v>69.64</v>
+        <v>67.38</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36790,26 +36790,26 @@
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>49.85</v>
+        <v>48.01</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>50.33</v>
+        <v>45.85</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>49.28</v>
+        <v>44.47</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>49.7</v>
+        <v>44.46</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>52.84</v>
+        <v>46.41</v>
       </c>
       <c r="J244" s="3" t="n">
-        <v>57.23</v>
+        <v>47.84</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36836,26 +36836,26 @@
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>60.45</v>
+        <v>56.45</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>58.12</v>
+        <v>53.54</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>55.83</v>
+        <v>51.07</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>53.96</v>
+        <v>49.68</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>52.98</v>
+        <v>49.72</v>
       </c>
       <c r="J245" s="3" t="n">
-        <v>52.93</v>
+        <v>49.31</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36882,26 +36882,26 @@
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>54.61</v>
+        <v>50.27</v>
       </c>
       <c r="F246" s="3" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="I246" s="3" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="J246" s="3" t="n">
         <v>51.75</v>
       </c>
-      <c r="G246" s="3" t="n">
-        <v>51.38</v>
-      </c>
-      <c r="H246" s="3" t="n">
-        <v>50.34</v>
-      </c>
-      <c r="I246" s="3" t="n">
-        <v>50.69</v>
-      </c>
-      <c r="J246" s="3" t="n">
-        <v>51.13</v>
-      </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36928,26 +36928,26 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>62.54</v>
+        <v>57.47</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>59.94</v>
+        <v>57.29</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>60.76</v>
+        <v>56.3</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>60.5</v>
+        <v>56.49</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>60.62</v>
+        <v>58.89</v>
       </c>
       <c r="J247" s="3" t="n">
-        <v>62.13</v>
+        <v>60.96</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36974,26 +36974,26 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>39.73</v>
+        <v>39.71</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>40.76</v>
+        <v>42.87</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>44.35</v>
+        <v>44.9</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>47.13</v>
+        <v>45.45</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>48.69</v>
-      </c>
-      <c r="J248" s="3" t="n">
-        <v>45.75</v>
+        <v>43.48</v>
+      </c>
+      <c r="J248" s="4" t="n">
+        <v>37.24</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37020,26 +37020,26 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>27.12</v>
+        <v>28.85</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>28.82</v>
+        <v>33.1</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>32.94</v>
+        <v>35.73</v>
       </c>
       <c r="H249" s="4" t="n">
-        <v>35.36</v>
+        <v>36.2</v>
       </c>
       <c r="I249" s="4" t="n">
-        <v>35.47</v>
+        <v>33.64</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>31.94</v>
+        <v>27.48</v>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37066,26 +37066,26 @@
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>45.76</v>
+        <v>46.58</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>46.48</v>
+        <v>49.84</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>49.69</v>
+        <v>53.73</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>53.43</v>
+        <v>57.04</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>56.47</v>
+        <v>56.6</v>
       </c>
       <c r="J250" s="3" t="n">
-        <v>52</v>
+        <v>53.28</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37112,26 +37112,26 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>38.35</v>
+        <v>37.22</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>37.03</v>
+        <v>38.84</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>38.36</v>
+        <v>39.47</v>
       </c>
       <c r="H251" s="4" t="n">
-        <v>38.64</v>
+        <v>39.66</v>
       </c>
       <c r="I251" s="4" t="n">
-        <v>38.26</v>
+        <v>37.63</v>
       </c>
       <c r="J251" s="4" t="n">
-        <v>34.64</v>
+        <v>33.19</v>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37158,26 +37158,26 @@
         </is>
       </c>
       <c r="E252" s="3" t="n">
-        <v>41.25</v>
+        <v>41.78</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>41.59</v>
+        <v>43.27</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>42.96</v>
+        <v>43.7</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>43.24</v>
+        <v>43.48</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>42.73</v>
+        <v>40.89</v>
       </c>
       <c r="J252" s="4" t="n">
-        <v>38.24</v>
+        <v>37.16</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37204,26 +37204,26 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>34.4</v>
+        <v>33.22</v>
       </c>
       <c r="F253" s="4" t="n">
-        <v>34.59</v>
+        <v>33.48</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>35.78</v>
+        <v>33.98</v>
       </c>
       <c r="H253" s="4" t="n">
-        <v>37.76</v>
+        <v>32.87</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>38.43</v>
+        <v>30.67</v>
       </c>
       <c r="J253" s="4" t="n">
-        <v>35.82</v>
+        <v>24.83</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37250,26 +37250,26 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>31.58</v>
+        <v>32.28</v>
       </c>
       <c r="F254" s="4" t="n">
-        <v>32.23</v>
+        <v>35.1</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>35.08</v>
+        <v>36.4</v>
       </c>
       <c r="H254" s="4" t="n">
-        <v>36.55</v>
+        <v>36.69</v>
       </c>
       <c r="I254" s="4" t="n">
-        <v>37.13</v>
+        <v>34.49</v>
       </c>
       <c r="J254" s="4" t="n">
-        <v>33.4</v>
+        <v>29.43</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37296,26 +37296,26 @@
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>40.79</v>
+        <v>42.46</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>41.56</v>
+        <v>44.72</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>43.36</v>
+        <v>46.34</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>44.26</v>
+        <v>46.03</v>
       </c>
       <c r="I255" s="3" t="n">
-        <v>42.92</v>
+        <v>43.1</v>
       </c>
       <c r="J255" s="4" t="n">
-        <v>37.96</v>
+        <v>37.95</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37342,26 +37342,26 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>37.32</v>
+        <v>35.07</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>35.12</v>
+        <v>34.94</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>35.05</v>
+        <v>36.71</v>
       </c>
       <c r="H256" s="4" t="n">
-        <v>36.94</v>
+        <v>37.06</v>
       </c>
       <c r="I256" s="4" t="n">
-        <v>37.59</v>
+        <v>35.32</v>
       </c>
       <c r="J256" s="4" t="n">
-        <v>34.58</v>
+        <v>29.27</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37388,26 +37388,26 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>24.32</v>
+        <v>23.95</v>
       </c>
       <c r="F257" s="4" t="n">
-        <v>24.71</v>
+        <v>26.53</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>27.74</v>
+        <v>29.81</v>
       </c>
       <c r="H257" s="4" t="n">
-        <v>31.74</v>
+        <v>31.03</v>
       </c>
       <c r="I257" s="4" t="n">
-        <v>33.99</v>
+        <v>30.51</v>
       </c>
       <c r="J257" s="4" t="n">
-        <v>31.94</v>
+        <v>26.08</v>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37434,26 +37434,26 @@
         </is>
       </c>
       <c r="E258" s="3" t="n">
-        <v>43.22</v>
+        <v>43.71</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>44.53</v>
+        <v>46.37</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>47.64</v>
+        <v>48.5</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>50.4</v>
+        <v>48.45</v>
       </c>
       <c r="I258" s="3" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="J258" s="3" t="n">
-        <v>49.02</v>
+        <v>46.45</v>
+      </c>
+      <c r="J258" s="4" t="n">
+        <v>39.57</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37480,26 +37480,26 @@
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>48.81</v>
+        <v>48.94</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>47.76</v>
+        <v>49.43</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>47.61</v>
+        <v>51.13</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>48.4</v>
+        <v>51.43</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>47.26</v>
+        <v>48.83</v>
       </c>
       <c r="J259" s="3" t="n">
-        <v>41.91</v>
+        <v>44.08</v>
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37526,26 +37526,26 @@
         </is>
       </c>
       <c r="E260" s="3" t="n">
-        <v>48.11</v>
+        <v>47.33</v>
       </c>
       <c r="F260" s="3" t="n">
-        <v>48.73</v>
+        <v>49.25</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>51.21</v>
+        <v>50.66</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>53.46</v>
+        <v>49.9</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>53.78</v>
+        <v>47.75</v>
       </c>
       <c r="J260" s="3" t="n">
-        <v>51.71</v>
+        <v>41.55</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37572,26 +37572,26 @@
         </is>
       </c>
       <c r="E261" s="4" t="n">
-        <v>38.21</v>
-      </c>
-      <c r="F261" s="4" t="n">
-        <v>38.44</v>
+        <v>39</v>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>41.58</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>40.52</v>
+        <v>44.18</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>42.41</v>
+        <v>46.74</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="J261" s="4" t="n">
-        <v>39.19</v>
+        <v>45.01</v>
+      </c>
+      <c r="J261" s="3" t="n">
+        <v>40.63</v>
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37617,27 +37617,27 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E262" s="4" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="F262" s="4" t="n">
-        <v>39.76</v>
+      <c r="E262" s="3" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>43.64</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>43.13</v>
+        <v>47.95</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>47.32</v>
+        <v>49.88</v>
       </c>
       <c r="I262" s="3" t="n">
-        <v>49.13</v>
+        <v>48.98</v>
       </c>
       <c r="J262" s="3" t="n">
-        <v>46.47</v>
+        <v>42.4</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37664,26 +37664,26 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>52.16</v>
+        <v>53.14</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>52.62</v>
+        <v>53.23</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>52.49</v>
+        <v>55.83</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>54.53</v>
+        <v>58.27</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>56.25</v>
+        <v>62.51</v>
       </c>
       <c r="J263" s="3" t="n">
-        <v>61.38</v>
+        <v>64.67</v>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37710,26 +37710,26 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>54.06</v>
+        <v>52.83</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>53.22</v>
+        <v>53.21</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>53.64</v>
+        <v>54.23</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>54.73</v>
+        <v>56.09</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>56.73</v>
+        <v>59.68</v>
       </c>
       <c r="J264" s="3" t="n">
-        <v>61.4</v>
+        <v>63.24</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37756,26 +37756,26 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>53.6</v>
+        <v>53.82</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>54.3</v>
+        <v>54.89</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>55.56</v>
+        <v>56.65</v>
       </c>
       <c r="H265" s="3" t="n">
-        <v>57.58</v>
+        <v>59.27</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>60.52</v>
+        <v>63.19</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>65.03</v>
+        <v>65.8</v>
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37802,26 +37802,26 @@
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>50.62</v>
+        <v>48.29</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>47.63</v>
+        <v>47.47</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>46.36</v>
+        <v>49</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>47.15</v>
+        <v>52.75</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>49.87</v>
+        <v>57.72</v>
       </c>
       <c r="J266" s="3" t="n">
-        <v>55.91</v>
+        <v>62.21</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37848,26 +37848,26 @@
         </is>
       </c>
       <c r="E267" s="4" t="n">
-        <v>27.6</v>
+        <v>29.11</v>
       </c>
       <c r="F267" s="4" t="n">
-        <v>28.57</v>
+        <v>31.08</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>29.87</v>
+        <v>33.83</v>
       </c>
       <c r="H267" s="4" t="n">
-        <v>31.67</v>
-      </c>
-      <c r="I267" s="4" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="J267" s="4" t="n">
-        <v>38.83</v>
+        <v>38.19</v>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="J267" s="3" t="n">
+        <v>48.52</v>
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37894,26 +37894,26 @@
         </is>
       </c>
       <c r="E268" s="3" t="n">
-        <v>42.06</v>
+        <v>43.01</v>
       </c>
       <c r="F268" s="3" t="n">
-        <v>43.48</v>
+        <v>44.93</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>45.49</v>
+        <v>47.27</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>48.02</v>
+        <v>50.12</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>51.1</v>
+        <v>52.59</v>
       </c>
       <c r="J268" s="3" t="n">
-        <v>53.71</v>
+        <v>52.11</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L52" s="2" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L53" s="3" t="n"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L54" s="2" t="n"/>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L55" s="3" t="n"/>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L56" s="2" t="n"/>
@@ -28207,7 +28207,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L57" s="3" t="n"/>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L58" s="2" t="n"/>
@@ -28299,7 +28299,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L59" s="3" t="n"/>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L60" s="2" t="n"/>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L61" s="3" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L62" s="2" t="n"/>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L63" s="3" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L64" s="2" t="n"/>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L65" s="3" t="n"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L66" s="2" t="n"/>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L67" s="3" t="n"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L68" s="2" t="n"/>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L69" s="3" t="n"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L70" s="2" t="n"/>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L71" s="3" t="n"/>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L72" s="2" t="n"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L73" s="3" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L74" s="2" t="n"/>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L75" s="3" t="n"/>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L76" s="2" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L77" s="3" t="n"/>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L78" s="2" t="n"/>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L79" s="3" t="n"/>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L80" s="2" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L81" s="3" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L82" s="2" t="n"/>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L83" s="3" t="n"/>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L84" s="2" t="n"/>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L85" s="3" t="n"/>
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L86" s="2" t="n"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L87" s="3" t="n"/>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L88" s="2" t="n"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L89" s="3" t="n"/>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L90" s="2" t="n"/>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L91" s="3" t="n"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L92" s="2" t="n"/>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L93" s="3" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L94" s="2" t="n"/>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L95" s="3" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L96" s="2" t="n"/>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L97" s="3" t="n"/>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L98" s="2" t="n"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L99" s="3" t="n"/>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L100" s="2" t="n"/>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L101" s="3" t="n"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L102" s="2" t="n"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L103" s="3" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L104" s="2" t="n"/>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L105" s="3" t="n"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L106" s="2" t="n"/>
@@ -30507,7 +30507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L107" s="3" t="n"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L108" s="2" t="n"/>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L109" s="3" t="n"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L110" s="2" t="n"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L111" s="3" t="n"/>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L112" s="2" t="n"/>
@@ -30783,7 +30783,7 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L113" s="3" t="n"/>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L114" s="2" t="n"/>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L115" s="3" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L116" s="2" t="n"/>
@@ -30967,7 +30967,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L117" s="3" t="n"/>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L118" s="2" t="n"/>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L119" s="3" t="n"/>
@@ -31105,7 +31105,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L120" s="2" t="n"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L121" s="3" t="n"/>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L122" s="2" t="n"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L123" s="3" t="n"/>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L124" s="2" t="n"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L126" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L127" s="3" t="n"/>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L128" s="2" t="n"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L129" s="3" t="n"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L130" s="2" t="n"/>
@@ -31611,7 +31611,7 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L131" s="3" t="n"/>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L132" s="2" t="n"/>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L133" s="3" t="n"/>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L134" s="2" t="n"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L135" s="3" t="n"/>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L136" s="2" t="n"/>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L137" s="3" t="n"/>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L138" s="2" t="n"/>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L139" s="3" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L140" s="2" t="n"/>
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L141" s="3" t="n"/>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L142" s="2" t="n"/>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L143" s="3" t="n"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L144" s="2" t="n"/>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L145" s="3" t="n"/>
@@ -32301,7 +32301,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L146" s="2" t="n"/>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L147" s="3" t="n"/>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L148" s="2" t="n"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L149" s="3" t="n"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L150" s="2" t="n"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L151" s="3" t="n"/>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L152" s="2" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L153" s="3" t="n"/>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L154" s="2" t="n"/>
@@ -32715,7 +32715,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L155" s="3" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L156" s="2" t="n"/>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L157" s="3" t="n"/>
@@ -32853,7 +32853,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L158" s="2" t="n"/>
@@ -32899,7 +32899,7 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L159" s="3" t="n"/>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L160" s="2" t="n"/>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L161" s="3" t="n"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L162" s="2" t="n"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L163" s="3" t="n"/>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L164" s="2" t="n"/>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L165" s="3" t="n"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L166" s="2" t="n"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L167" s="3" t="n"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L168" s="2" t="n"/>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L169" s="3" t="n"/>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L171" s="3" t="n"/>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L172" s="2" t="n"/>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L173" s="3" t="n"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L174" s="2" t="n"/>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L175" s="3" t="n"/>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L176" s="2" t="n"/>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L177" s="3" t="n"/>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L178" s="2" t="n"/>
@@ -33819,7 +33819,7 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L179" s="3" t="n"/>
@@ -33865,7 +33865,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L180" s="2" t="n"/>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L181" s="3" t="n"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L182" s="2" t="n"/>
@@ -34003,7 +34003,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L183" s="3" t="n"/>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L184" s="2" t="n"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L185" s="3" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L186" s="2" t="n"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L187" s="3" t="n"/>
@@ -34233,7 +34233,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L188" s="2" t="n"/>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L189" s="3" t="n"/>
@@ -34325,7 +34325,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L190" s="2" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L191" s="3" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L192" s="2" t="n"/>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L193" s="3" t="n"/>
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L194" s="2" t="n"/>
@@ -34555,7 +34555,7 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L195" s="3" t="n"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L197" s="3" t="n"/>
@@ -34693,7 +34693,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L198" s="2" t="n"/>
@@ -34739,7 +34739,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L199" s="3" t="n"/>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L200" s="2" t="n"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L201" s="3" t="n"/>
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L202" s="2" t="n"/>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L204" s="2" t="n"/>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L206" s="2" t="n"/>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L208" s="2" t="n"/>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L209" s="3" t="n"/>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L210" s="2" t="n"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L211" s="3" t="n"/>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L212" s="2" t="n"/>
@@ -35383,7 +35383,7 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>
@@ -35429,7 +35429,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L214" s="2" t="n"/>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L215" s="3" t="n"/>
@@ -35521,7 +35521,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L216" s="2" t="n"/>
@@ -35567,7 +35567,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L217" s="3" t="n"/>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L218" s="2" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L219" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L220" s="2" t="n"/>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L221" s="3" t="n"/>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L222" s="2" t="n"/>
@@ -35843,7 +35843,7 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L223" s="3" t="n"/>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L224" s="2" t="n"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L225" s="3" t="n"/>
@@ -35981,7 +35981,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L226" s="2" t="n"/>
@@ -36027,7 +36027,7 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L227" s="3" t="n"/>
@@ -36073,7 +36073,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L228" s="2" t="n"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L229" s="3" t="n"/>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L230" s="2" t="n"/>
@@ -36211,7 +36211,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L231" s="3" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L232" s="2" t="n"/>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L233" s="3" t="n"/>
@@ -36349,7 +36349,7 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L234" s="2" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L235" s="3" t="n"/>
@@ -36441,7 +36441,7 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L236" s="2" t="n"/>
@@ -36487,7 +36487,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L237" s="3" t="n"/>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L238" s="2" t="n"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L239" s="3" t="n"/>
@@ -36625,7 +36625,7 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L240" s="2" t="n"/>
@@ -36671,7 +36671,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L241" s="3" t="n"/>
@@ -36717,7 +36717,7 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L242" s="2" t="n"/>
@@ -36763,7 +36763,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L243" s="3" t="n"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L244" s="2" t="n"/>
@@ -36855,7 +36855,7 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L245" s="3" t="n"/>
@@ -36901,7 +36901,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L246" s="2" t="n"/>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L247" s="3" t="n"/>
@@ -36993,7 +36993,7 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L248" s="2" t="n"/>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L249" s="3" t="n"/>
@@ -37085,7 +37085,7 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L250" s="2" t="n"/>
@@ -37131,7 +37131,7 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L251" s="3" t="n"/>
@@ -37177,7 +37177,7 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L252" s="2" t="n"/>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L253" s="3" t="n"/>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L255" s="3" t="n"/>
@@ -37361,7 +37361,7 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L257" s="3" t="n"/>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L258" s="2" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L259" s="3" t="n"/>
@@ -37545,7 +37545,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L260" s="2" t="n"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L261" s="3" t="n"/>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L262" s="2" t="n"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L263" s="3" t="n"/>
@@ -37729,7 +37729,7 @@
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L264" s="2" t="n"/>
@@ -37775,7 +37775,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L265" s="3" t="n"/>
@@ -37821,7 +37821,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L266" s="2" t="n"/>
@@ -37867,7 +37867,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L267" s="3" t="n"/>
@@ -37913,7 +37913,7 @@
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L268" s="2" t="n"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -12801,6 +12801,78 @@
           <val>
             <numRef>
               <f>'VHI_最近6周汇总'!$E$258:$J$258</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart258.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="E00000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="E00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="E00000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'VHI_最近6周汇总'!$E$259:$J$259</f>
             </numRef>
           </val>
         </ser>
@@ -24325,6 +24397,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>258</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2880000" cy="720000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="258" name="Chart 258"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId258"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -24617,7 +24711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L258"/>
+  <dimension ref="A1:L259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -24755,7 +24849,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -24764,22 +24858,22 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>62.22</v>
+        <v>60.38</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>62.55</v>
+        <v>61.21</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>61.85</v>
+        <v>61.16</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>60.08</v>
+        <v>58.1</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>57.89</v>
+        <v>53.92</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>56.75</v>
+        <v>47.58</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -24801,7 +24895,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -24810,22 +24904,22 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>60.38</v>
+        <v>70.14</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>61.21</v>
+        <v>70.31</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>61.16</v>
+        <v>71.75</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>58.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>53.92</v>
+        <v>69.52</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>47.58</v>
+        <v>65.88</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -24847,7 +24941,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -24856,22 +24950,22 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>70.14</v>
+        <v>49.68</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>70.31</v>
+        <v>49.28</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>71.75</v>
+        <v>50.45</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>51.07</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>69.52</v>
+        <v>50.95</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>65.88</v>
+        <v>47.39</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -24883,17 +24977,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>南里奥格兰德州</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -24902,22 +24996,22 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>49.68</v>
+        <v>56.74</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>49.28</v>
+        <v>57.84</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>50.45</v>
+        <v>59.81</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>51.07</v>
+        <v>61.94</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>50.95</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>47.39</v>
+        <v>64.11</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -24939,7 +25033,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>南里奥格兰德州</t>
+          <t>南马托格罗索州</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -24948,22 +25042,22 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>56.74</v>
+        <v>60.24</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>57.84</v>
+        <v>60.96</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>59.81</v>
+        <v>63.31</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>61.94</v>
+        <v>66.58</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>64.15000000000001</v>
+        <v>69.66</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>64.11</v>
+        <v>71.77</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -24985,7 +25079,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>南马托格罗索州</t>
+          <t>巴伊亚州</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -24994,22 +25088,22 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>60.24</v>
+        <v>42.79</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>60.96</v>
+        <v>43.92</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>63.31</v>
+        <v>45.42</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>66.58</v>
+        <v>47.22</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>69.66</v>
+        <v>49.17</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>71.77</v>
+        <v>52.38</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -25031,7 +25125,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>巴伊亚州</t>
+          <t>巴拉那州</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -25040,22 +25134,22 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>42.79</v>
+        <v>55.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>43.92</v>
+        <v>59.06</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45.42</v>
+        <v>61.22</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>47.22</v>
+        <v>63.15</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>49.17</v>
+        <v>65.41</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>52.38</v>
+        <v>67.37</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -25077,7 +25171,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>巴拉那州</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -25086,22 +25180,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>55.86</v>
+        <v>50.35</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>59.06</v>
+        <v>50.88</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>61.22</v>
+        <v>51.93</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>63.15</v>
+        <v>54.38</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>65.41</v>
+        <v>57.88</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>67.37</v>
+        <v>62.29</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -25123,7 +25217,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -25132,22 +25226,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>50.35</v>
+        <v>53.04</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>50.88</v>
+        <v>54.28</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>51.93</v>
+        <v>56.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>54.38</v>
+        <v>59.94</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>57.88</v>
+        <v>63.58</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>62.29</v>
+        <v>67.19</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -25169,7 +25263,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -25178,22 +25272,22 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>53.04</v>
+        <v>44.75</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>54.28</v>
+        <v>45.54</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>56.5</v>
+        <v>48.35</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>59.94</v>
+        <v>52.16</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>63.58</v>
+        <v>56.77</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>67.19</v>
+        <v>59.91</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -25205,17 +25299,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -25224,22 +25318,22 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>44.75</v>
+        <v>51.94</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>45.54</v>
+        <v>53.23</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>48.35</v>
+        <v>56.35</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>52.16</v>
+        <v>59.62</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>56.77</v>
+        <v>61.28</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>59.91</v>
+        <v>58.06</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -25261,7 +25355,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -25270,22 +25364,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>51.94</v>
+        <v>54.46</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>53.23</v>
+        <v>54.59</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>56.35</v>
+        <v>54.97</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>59.62</v>
+        <v>55.07</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>61.28</v>
+        <v>54.69</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>58.06</v>
+        <v>51.42</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -25307,7 +25401,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -25316,22 +25410,22 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>54.46</v>
+        <v>44.76</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>54.59</v>
+        <v>47.73</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>54.97</v>
+        <v>52.61</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>55.07</v>
+        <v>56.76</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>54.69</v>
+        <v>58.45</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>51.42</v>
+        <v>54.12</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -25353,7 +25447,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -25362,22 +25456,22 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>44.76</v>
+        <v>44.14</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>47.73</v>
+        <v>46.39</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>52.61</v>
+        <v>49.35</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>56.76</v>
+        <v>51.84</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>58.45</v>
+        <v>52.94</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>54.12</v>
+        <v>50.14</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -25399,7 +25493,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -25408,22 +25502,22 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>44.14</v>
+        <v>50.45</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46.39</v>
+        <v>54.06</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>49.35</v>
+        <v>58.19</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>51.84</v>
+        <v>62.03</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>52.94</v>
+        <v>65.3</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>50.14</v>
+        <v>66.34</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -25445,7 +25539,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -25453,23 +25547,23 @@
           <t>大豆</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>54.06</v>
+      <c r="E18" s="4" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>36.69</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>58.19</v>
+        <v>42.16</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>62.03</v>
+        <v>46.89</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>65.3</v>
+        <v>50.21</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>66.34</v>
+        <v>49.12</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -25491,7 +25585,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -25499,23 +25593,23 @@
           <t>大豆</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>31.97</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>36.69</v>
+      <c r="E19" s="3" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>42.82</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>42.16</v>
+        <v>44.96</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46.89</v>
+        <v>47.08</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>50.21</v>
+        <v>48.99</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>49.12</v>
+        <v>49.11</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -25537,7 +25631,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -25545,23 +25639,23 @@
           <t>大豆</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>42.82</v>
+      <c r="E20" s="4" t="n">
+        <v>37.47</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>39.94</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>44.96</v>
+        <v>42.87</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>47.08</v>
+        <v>45.09</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>48.99</v>
+        <v>46.88</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>49.11</v>
+        <v>46.47</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -25776,22 +25870,22 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>52.93</v>
+        <v>53.28</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>53.98</v>
+        <v>54.34</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>56.07</v>
+        <v>56.56</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>59.13</v>
+        <v>59.54</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>62.24</v>
+        <v>62.46</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>64.53</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -26006,22 +26100,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>55.78</v>
+        <v>54.59</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>56.43</v>
+        <v>55.11</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>56.52</v>
+        <v>55.26</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>56.29</v>
+        <v>55.22</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>55.53</v>
+        <v>54.71</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>53.92</v>
+        <v>53.29</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -26631,41 +26725,41 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>大麦</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>60.43</v>
+        <v>52.76</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>60.9</v>
+        <v>50.21</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>60.69</v>
+        <v>48.84</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>57.62</v>
+        <v>48.9</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>53.55</v>
+        <v>49.13</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>46.9</v>
+        <v>49.76</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -26687,7 +26781,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -26696,22 +26790,22 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>71.17</v>
+        <v>60.43</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>69.13</v>
+        <v>60.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>67.13</v>
+        <v>60.69</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>63.9</v>
+        <v>57.62</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>58.09</v>
+        <v>53.55</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>51.64</v>
+        <v>46.9</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -26733,7 +26827,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -26742,22 +26836,22 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>50.64</v>
+        <v>71.17</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>51.36</v>
+        <v>69.13</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>51.96</v>
+        <v>67.13</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>52.79</v>
+        <v>63.9</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>54.03</v>
+        <v>58.09</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>53.28</v>
+        <v>51.64</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -26779,7 +26873,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -26788,22 +26882,22 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>54.62</v>
+        <v>50.64</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>53.58</v>
+        <v>51.36</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>52.15</v>
+        <v>51.96</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>47.17</v>
+        <v>52.79</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>42.21</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>35.1</v>
+        <v>54.03</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>53.28</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -27064,22 +27158,22 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>68.14</v>
+        <v>67.12</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>69.02</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>68.36</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>67.23999999999999</v>
+        <v>66.14</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>68.70999999999999</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -27377,7 +27471,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>北方邦</t>
+          <t>中央邦</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -27386,22 +27480,22 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>73.69</v>
+        <v>61.09</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>62.11</v>
+        <v>49.9</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>49.02</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>41.81</v>
+        <v>44.74</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>35</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -27423,7 +27517,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>哈里亚纳邦</t>
+          <t>北方邦</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -27432,22 +27526,22 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>55.61</v>
+        <v>73.69</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>51.4</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>47.99</v>
+        <v>62.11</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>44.36</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>39.47</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>34.07</v>
+        <v>56.14</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>41.81</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -27469,7 +27563,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>拉贾斯坦邦</t>
+          <t>哈里亚纳邦</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -27478,22 +27572,22 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>64.33</v>
+        <v>55.61</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>62.03</v>
+        <v>51.4</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>60.71</v>
+        <v>47.99</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>57.94</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>53.87</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>49.97</v>
+        <v>44.36</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>34.07</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -27515,7 +27609,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>旁遮普邦</t>
+          <t>拉贾斯坦邦</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -27524,22 +27618,22 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>57.78</v>
+        <v>64.33</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>54.83</v>
+        <v>62.03</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>51.77</v>
+        <v>60.71</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>47.33</v>
+        <v>57.94</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>41.15</v>
-      </c>
-      <c r="J63" s="4" t="n">
-        <v>36.26</v>
+        <v>53.87</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>49.97</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -28297,7 +28391,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -28305,23 +28399,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E80" s="3" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>45.02</v>
+      <c r="E80" s="4" t="n">
+        <v>32.11</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>35.31</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>47.89</v>
+        <v>40.28</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>50.27</v>
+        <v>46.92</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>51.64</v>
+        <v>53.07</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>48.92</v>
+        <v>57.63</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -28343,7 +28437,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -28352,22 +28446,22 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>42.33</v>
+        <v>42.86</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>43.84</v>
+        <v>45.02</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>46.34</v>
+        <v>47.89</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>50.82</v>
+        <v>50.27</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>55.04</v>
+        <v>51.64</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>59.14</v>
+        <v>48.92</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -28389,7 +28483,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -28398,22 +28492,22 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>44.6</v>
+        <v>42.33</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>46.3</v>
+        <v>43.84</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>48.92</v>
+        <v>46.34</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>51.47</v>
+        <v>50.82</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>53.77</v>
+        <v>55.04</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>54.62</v>
+        <v>59.14</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -28435,7 +28529,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -28443,23 +28537,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E83" s="4" t="n">
-        <v>38.19</v>
+      <c r="E83" s="3" t="n">
+        <v>44.6</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>43</v>
+        <v>46.3</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>48.34</v>
+        <v>48.92</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>54.02</v>
+        <v>51.47</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>59.37</v>
+        <v>53.77</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>63.87</v>
+        <v>54.62</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -28481,7 +28575,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -28489,23 +28583,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E84" s="3" t="n">
-        <v>47.91</v>
+      <c r="E84" s="4" t="n">
+        <v>38.19</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>47.59</v>
+        <v>43</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>47.19</v>
+        <v>48.34</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>48</v>
+        <v>54.02</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>49.45</v>
+        <v>59.37</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>53.54</v>
+        <v>63.87</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -28517,17 +28611,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -28536,22 +28630,22 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>53.51</v>
+        <v>47.91</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>50.99</v>
+        <v>47.59</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>49.55</v>
+        <v>47.19</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>49.52</v>
+        <v>48</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>49.68</v>
+        <v>49.45</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>50.31</v>
+        <v>53.54</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -28573,7 +28667,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -28582,22 +28676,22 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>51.72</v>
+        <v>53.51</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>50.35</v>
+        <v>50.99</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>50.19</v>
+        <v>49.55</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>51.47</v>
+        <v>49.52</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>53.07</v>
+        <v>49.68</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>55.16</v>
+        <v>50.31</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -28619,7 +28713,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -28628,22 +28722,22 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>55.77</v>
+        <v>51.72</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>54.2</v>
+        <v>50.35</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>53.55</v>
+        <v>50.19</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>55.24</v>
+        <v>51.47</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>57.49</v>
+        <v>53.07</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>59.52</v>
+        <v>55.16</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -28655,41 +28749,41 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>棉花</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>52.92</v>
+        <v>55.77</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>55.04</v>
+        <v>54.2</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>57.01</v>
+        <v>53.55</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>58.77</v>
+        <v>55.24</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>60.73</v>
+        <v>57.49</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>59.8</v>
+        <v>59.52</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -28701,17 +28795,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>中央邦</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -28720,22 +28814,22 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>56.95</v>
+        <v>52.92</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>50.59</v>
+        <v>55.04</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>44.99</v>
+        <v>57.01</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>36.64</v>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v>34.26</v>
+        <v>58.77</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>59.8</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -28757,7 +28851,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>卡纳塔克邦</t>
+          <t>中央邦</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -28766,22 +28860,22 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>68.59</v>
+        <v>56.95</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>64.65000000000001</v>
+        <v>50.59</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>59.44</v>
+        <v>44.99</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>50.9</v>
+        <v>40.3</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>34.26</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -29115,17 +29209,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Queensland</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -29134,22 +29228,22 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>45.16</v>
+        <v>63.67</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>43.85</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>42.27</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>42.02</v>
+        <v>66.37</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>43.05</v>
+        <v>66.58</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>43.82</v>
+        <v>64.97</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -29171,7 +29265,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -29180,22 +29274,22 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>63.67</v>
+        <v>55.28</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>64.06999999999999</v>
+        <v>61.48</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>67.02</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>66.37</v>
+        <v>69.84</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>66.58</v>
+        <v>71.69</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>64.97</v>
+        <v>70.53</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -29217,7 +29311,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -29226,22 +29320,22 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>55.28</v>
+        <v>57.72</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>61.48</v>
+        <v>58.46</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>67.02</v>
+        <v>58.38</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>69.84</v>
+        <v>57.87</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>71.69</v>
+        <v>56.3</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>70.53</v>
+        <v>53.44</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -29263,7 +29357,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -29272,22 +29366,22 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>57.72</v>
+        <v>63.65</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>58.46</v>
+        <v>65.37</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>58.38</v>
+        <v>67.06</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>57.87</v>
+        <v>67.45</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>56.3</v>
+        <v>67.69</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>53.44</v>
+        <v>68.28</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -29309,7 +29403,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -29318,22 +29412,22 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>63.65</v>
+        <v>55.07</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>65.37</v>
+        <v>58.56</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>67.06</v>
+        <v>61.92</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>67.45</v>
+        <v>64.09</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>67.69</v>
+        <v>65.98</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>68.28</v>
+        <v>65.5</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -29355,7 +29449,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -29364,22 +29458,22 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>55.07</v>
+        <v>56.26</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>58.56</v>
+        <v>54.94</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>61.92</v>
+        <v>54.44</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>64.09</v>
+        <v>53.49</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>65.98</v>
+        <v>53.39</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>65.5</v>
+        <v>52.29</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -29401,7 +29495,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -29410,22 +29504,22 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>56.26</v>
+        <v>61.97</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>54.94</v>
+        <v>64.03</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>54.44</v>
+        <v>66.67</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>53.49</v>
+        <v>69</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>53.39</v>
+        <v>71.22</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>52.29</v>
+        <v>71.42</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -29447,7 +29541,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -29456,22 +29550,22 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>61.97</v>
+        <v>41.96</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>64.03</v>
+        <v>44.67</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>66.67</v>
+        <v>47.66</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>69</v>
+        <v>49.86</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>71.22</v>
+        <v>50.8</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>71.42</v>
+        <v>51.35</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -29483,41 +29577,41 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>东加里曼丹</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>棉花</t>
+          <t>棕榈油</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>41.96</v>
+        <v>48.58</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>44.67</v>
+        <v>49.82</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>47.66</v>
+        <v>50.11</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>49.86</v>
+        <v>49.4</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>50.8</v>
+        <v>48.85</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>51.35</v>
+        <v>48.06</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -29539,7 +29633,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>东加里曼丹</t>
+          <t>中加里曼丹</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -29548,22 +29642,22 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>48.58</v>
+        <v>45.92</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>49.82</v>
+        <v>46.66</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>50.11</v>
+        <v>46.8</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>49.4</v>
+        <v>46.22</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>48.85</v>
+        <v>46.34</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>48.06</v>
+        <v>46.44</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -29585,7 +29679,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>中加里曼丹</t>
+          <t>北苏门答腊</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -29594,22 +29688,22 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>45.92</v>
+        <v>46.37</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>46.66</v>
+        <v>48.74</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>46.8</v>
+        <v>52.66</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>46.22</v>
+        <v>56.03</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>46.34</v>
+        <v>58.09</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>46.44</v>
+        <v>57.77</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -29631,7 +29725,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>北苏门答腊</t>
+          <t>南苏门答腊</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -29640,22 +29734,22 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>46.37</v>
+        <v>40.97</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>48.74</v>
+        <v>41.26</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>52.66</v>
+        <v>42.12</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>56.03</v>
+        <v>43.68</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>58.09</v>
+        <v>45.92</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>57.77</v>
+        <v>47.64</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -29677,7 +29771,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>南苏门答腊</t>
+          <t>占碑</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -29685,23 +29779,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E110" s="3" t="n">
-        <v>40.97</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>41.26</v>
+      <c r="E110" s="4" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>39.56</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>42.12</v>
+        <v>41.41</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>43.68</v>
+        <v>43.27</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>45.92</v>
+        <v>46.12</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>47.64</v>
+        <v>47.46</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -29723,7 +29817,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>占碑</t>
+          <t>廖内</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -29731,23 +29825,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E111" s="4" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="F111" s="4" t="n">
-        <v>39.56</v>
+      <c r="E111" s="3" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>47.92</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>41.41</v>
+        <v>50.25</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>43.27</v>
+        <v>52.54</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>46.12</v>
+        <v>54.91</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>47.46</v>
+        <v>54.94</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
@@ -29769,7 +29863,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>廖内</t>
+          <t>西加里曼丹</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -29778,22 +29872,22 @@
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>44.79</v>
+        <v>49.19</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>47.92</v>
+        <v>49.75</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>50.25</v>
+        <v>50.02</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>52.54</v>
+        <v>49.92</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>54.91</v>
+        <v>51.1</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>54.94</v>
+        <v>53.26</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -29805,17 +29899,17 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>西加里曼丹</t>
+          <t>Johor</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -29824,22 +29918,22 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>49.19</v>
+        <v>47.4</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>49.75</v>
+        <v>47.77</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>50.02</v>
+        <v>48.14</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>49.92</v>
+        <v>48.8</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>51.1</v>
+        <v>49.78</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>53.26</v>
+        <v>49.11</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
@@ -29861,7 +29955,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Johor</t>
+          <t>Pahang</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -29870,22 +29964,22 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>47.4</v>
+        <v>54.49</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>47.77</v>
+        <v>55.37</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>48.14</v>
+        <v>56.09</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>48.8</v>
+        <v>56.57</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>49.78</v>
+        <v>56.86</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>49.11</v>
+        <v>56.46</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -29907,7 +30001,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Pahang</t>
+          <t>Perak</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -29916,22 +30010,22 @@
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>54.49</v>
+        <v>49.38</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>55.37</v>
+        <v>50.2</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>56.09</v>
+        <v>51.45</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>56.57</v>
+        <v>53.19</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>56.86</v>
+        <v>54.1</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>56.46</v>
+        <v>53.62</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
@@ -29953,7 +30047,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Perak</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -29962,22 +30056,22 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>49.38</v>
+        <v>47.78</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>50.2</v>
+        <v>47.88</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>51.45</v>
+        <v>48.48</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>53.19</v>
+        <v>48.93</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>54.1</v>
+        <v>49.27</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>53.62</v>
+        <v>49.39</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -29999,7 +30093,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Sarawak</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -30008,22 +30102,22 @@
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>47.78</v>
+        <v>48.42</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>47.88</v>
+        <v>49.7</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>48.48</v>
+        <v>50.22</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>48.93</v>
+        <v>50.1</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>49.27</v>
+        <v>50.38</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>49.39</v>
+        <v>51.9</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
@@ -30035,41 +30129,41 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Sarawak</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>棕榈油</t>
+          <t>玉米</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>48.42</v>
+        <v>60.86</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>49.7</v>
+        <v>59.55</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>50.22</v>
+        <v>57.48</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>50.1</v>
+        <v>54.45</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>50.38</v>
+        <v>51.23</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>51.9</v>
+        <v>49.02</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -30091,7 +30185,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -30100,22 +30194,22 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>60.86</v>
+        <v>61</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>59.55</v>
+        <v>62.62</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>57.48</v>
+        <v>63.99</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>54.45</v>
+        <v>64.89</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>51.23</v>
+        <v>64.95</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>49.02</v>
+        <v>62.47</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
@@ -30137,7 +30231,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -30146,22 +30240,22 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>61</v>
+        <v>54.92</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>62.62</v>
+        <v>58.25</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>63.99</v>
+        <v>61.37</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>64.89</v>
+        <v>61.58</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>64.95</v>
+        <v>60.11</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>62.47</v>
+        <v>55.63</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -30183,7 +30277,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -30192,22 +30286,22 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>54.92</v>
+        <v>61.76</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>58.25</v>
+        <v>61.99</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>61.37</v>
+        <v>61.22</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>61.58</v>
+        <v>59.34</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>60.11</v>
+        <v>57.1</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>55.63</v>
+        <v>55.92</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
@@ -30229,7 +30323,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -30238,22 +30332,22 @@
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>61.76</v>
+        <v>70.78</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>61.99</v>
+        <v>68.73</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>61.22</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>59.34</v>
+        <v>63.49</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>57.1</v>
+        <v>57.64</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>55.92</v>
+        <v>51.19</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -30275,7 +30369,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -30283,23 +30377,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E123" s="3" t="n">
-        <v>70.78</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>66.73999999999999</v>
-      </c>
-      <c r="H123" s="3" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="I123" s="3" t="n">
-        <v>57.64</v>
-      </c>
-      <c r="J123" s="3" t="n">
-        <v>51.19</v>
+      <c r="E123" s="5" t="n">
+        <v>83.44</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>85.62</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>86.37</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>84.79000000000001</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
@@ -30321,7 +30415,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -30329,23 +30423,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E124" s="5" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>85.62</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>86.37</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>86.06999999999999</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>84.79000000000001</v>
+      <c r="E124" s="3" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>53.72</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -30367,7 +30461,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -30375,23 +30469,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E125" s="3" t="n">
-        <v>50.67</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>51.52</v>
-      </c>
-      <c r="G125" s="3" t="n">
-        <v>52.22</v>
-      </c>
-      <c r="H125" s="3" t="n">
-        <v>53.12</v>
+      <c r="E125" s="5" t="n">
+        <v>84.54000000000001</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>81.34999999999999</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>54.41</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>53.72</v>
+        <v>73.53</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
@@ -30413,7 +30507,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -30421,23 +30515,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E126" s="5" t="n">
-        <v>84.54000000000001</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>83.87</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>81.34999999999999</v>
+      <c r="E126" s="3" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>71.48999999999999</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>77.18000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>73.53</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -30459,7 +30553,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -30468,22 +30562,22 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>70.09</v>
+        <v>70.27</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>70.17</v>
+        <v>71.94</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>71.62</v>
+        <v>72.66</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>71.48999999999999</v>
+        <v>72.14</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>70.22</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>66.23999999999999</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
@@ -30505,7 +30599,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -30514,22 +30608,22 @@
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>70.27</v>
+        <v>47.48</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>71.94</v>
+        <v>47.54</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>72.66</v>
+        <v>49.22</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>72.14</v>
+        <v>50.17</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>70.22</v>
+        <v>50.23</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -30541,17 +30635,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>Cherkaska</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -30560,22 +30654,22 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>47.48</v>
+        <v>42.55</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>47.54</v>
+        <v>43.93</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>49.22</v>
+        <v>46.4</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>50.17</v>
+        <v>50.05</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>50.23</v>
+        <v>53.45</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>46.57</v>
+        <v>54.04</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
@@ -30597,7 +30691,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Cherkaska</t>
+          <t>Chernihivska</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -30606,22 +30700,22 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>42.55</v>
+        <v>43.3</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>43.93</v>
+        <v>43.69</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>46.4</v>
+        <v>44.83</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>50.05</v>
+        <v>46.53</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>53.45</v>
+        <v>48.47</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>54.04</v>
+        <v>49.6</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -30643,7 +30737,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Chernihivska</t>
+          <t>Dnipropetrovska</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -30652,22 +30746,22 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>43.3</v>
+        <v>55.93</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>43.69</v>
+        <v>58.14</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>44.83</v>
+        <v>58.26</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>46.53</v>
+        <v>58.44</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>48.47</v>
+        <v>58.5</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>49.6</v>
+        <v>57.74</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
@@ -30689,7 +30783,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Dnipropetrovska</t>
+          <t>Donetsk</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -30698,22 +30792,22 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>55.93</v>
+        <v>62.34</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>58.14</v>
+        <v>62.34</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>58.26</v>
+        <v>61.06</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>58.44</v>
+        <v>60.76</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>58.5</v>
+        <v>60.95</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>57.74</v>
+        <v>61.44</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -30735,7 +30829,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Donetsk</t>
+          <t>Khersonska</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -30744,22 +30838,22 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>62.34</v>
+        <v>60.86</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>62.34</v>
+        <v>57.68</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>61.06</v>
+        <v>53.27</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>60.76</v>
+        <v>48.92</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>60.95</v>
+        <v>46.47</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>61.44</v>
+        <v>44.95</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
@@ -30781,7 +30875,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Khersonska</t>
+          <t>Khmelnitska</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -30790,22 +30884,22 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>60.86</v>
+        <v>44.8</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>57.68</v>
+        <v>45.02</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>53.27</v>
+        <v>45.32</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>48.92</v>
+        <v>46.29</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>46.47</v>
+        <v>47.43</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>44.95</v>
+        <v>47.24</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -30827,7 +30921,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Khmelnitska</t>
+          <t>Kirovohradska</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -30836,22 +30930,22 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>44.8</v>
+        <v>50.64</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>45.02</v>
+        <v>52.06</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>45.32</v>
+        <v>52.77</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>46.29</v>
+        <v>54.55</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>47.43</v>
+        <v>56.44</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>47.24</v>
+        <v>56.38</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
@@ -30873,7 +30967,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Kirovohradska</t>
+          <t>Kyivska</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -30882,22 +30976,22 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>50.64</v>
+        <v>44.36</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>52.06</v>
+        <v>45.59</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>52.77</v>
+        <v>47.19</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>54.55</v>
+        <v>49.7</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>56.44</v>
+        <v>51.8</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>56.38</v>
+        <v>51.71</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -30919,7 +31013,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Kyivska</t>
+          <t>Odeska</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -30928,22 +31022,22 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>44.36</v>
+        <v>75.62</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>45.59</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>47.19</v>
+        <v>77.88</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>49.7</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>51.8</v>
+        <v>73.88</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>51.71</v>
+        <v>70.58</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
@@ -30965,7 +31059,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Mykolaivska</t>
+          <t>Poltava</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -30974,22 +31068,22 @@
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>64.67</v>
+        <v>40.98</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>64.88</v>
+        <v>43.15</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>64.01000000000001</v>
+        <v>45.71</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>62.14</v>
+        <v>48.58</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>60.35</v>
+        <v>51.3</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>58.59</v>
+        <v>52.76</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -31011,7 +31105,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Odeska</t>
+          <t>Sumy</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -31020,22 +31114,22 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>75.62</v>
+        <v>50.26</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>77.18000000000001</v>
+        <v>51.65</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>77.88</v>
+        <v>53.49</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>76.45999999999999</v>
+        <v>55.67</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>73.88</v>
+        <v>58.91</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>70.58</v>
+        <v>61.34</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
@@ -31057,7 +31151,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Poltava</t>
+          <t>Vinnitsa</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -31066,22 +31160,22 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>40.98</v>
+        <v>51.03</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>43.15</v>
+        <v>51.98</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>45.71</v>
+        <v>53.56</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>48.58</v>
+        <v>55.8</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>51.3</v>
+        <v>57.71</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>52.76</v>
+        <v>57.68</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -31103,7 +31197,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Sumy</t>
+          <t>Zaporizka</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -31112,22 +31206,22 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>50.26</v>
+        <v>63.47</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>51.65</v>
+        <v>64.09</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>53.49</v>
+        <v>62.83</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>55.67</v>
+        <v>61.43</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>58.91</v>
+        <v>59.64</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>61.34</v>
+        <v>57.86</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -31149,7 +31243,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Vinnitsa</t>
+          <t>Zhytomyrska</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -31158,22 +31252,22 @@
         </is>
       </c>
       <c r="E142" s="3" t="n">
-        <v>51.03</v>
+        <v>45.7</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>51.98</v>
+        <v>46.64</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>53.56</v>
+        <v>47.15</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>55.8</v>
+        <v>47.2</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>57.71</v>
+        <v>47.69</v>
       </c>
       <c r="J142" s="3" t="n">
-        <v>57.68</v>
+        <v>46.92</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -31185,17 +31279,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Zaporizka</t>
+          <t>南马托格罗索州</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -31204,22 +31298,22 @@
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>63.47</v>
+        <v>60.13</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>64.09</v>
+        <v>60.87</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>62.83</v>
+        <v>63.28</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>61.43</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>59.64</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>57.86</v>
+        <v>71.92</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
@@ -31231,17 +31325,17 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Zhytomyrska</t>
+          <t>圣保罗州</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -31250,22 +31344,22 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>45.7</v>
+        <v>51.61</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>46.64</v>
+        <v>56.06</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>47.15</v>
+        <v>58.45</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>47.2</v>
+        <v>61.56</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>47.69</v>
+        <v>64.02</v>
       </c>
       <c r="J144" s="3" t="n">
-        <v>46.92</v>
+        <v>66.87</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -31287,7 +31381,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>南马托格罗索州</t>
+          <t>巴拉那州</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -31296,22 +31390,22 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>60.13</v>
+        <v>55.23</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>60.87</v>
+        <v>58.58</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>63.28</v>
+        <v>60.83</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>66.65000000000001</v>
+        <v>62.76</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>69.79000000000001</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>71.92</v>
+        <v>66.94</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
@@ -31333,7 +31427,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>圣保罗州</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -31342,22 +31436,22 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>51.61</v>
+        <v>49.68</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>56.06</v>
+        <v>50.2</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>58.45</v>
+        <v>51.24</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>61.56</v>
+        <v>53.73</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>64.02</v>
+        <v>57.25</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>66.87</v>
+        <v>61.78</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -31379,7 +31473,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>巴拉那州</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -31388,22 +31482,22 @@
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>55.23</v>
+        <v>52.69</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>58.58</v>
+        <v>54.44</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>60.83</v>
+        <v>56.69</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>62.76</v>
+        <v>59.26</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>64.98999999999999</v>
+        <v>61.94</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>66.94</v>
+        <v>64.67</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
@@ -31425,7 +31519,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -31434,22 +31528,22 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>49.68</v>
+        <v>44.35</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>50.2</v>
+        <v>45.17</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>51.24</v>
+        <v>47.96</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>53.73</v>
+        <v>51.78</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>57.25</v>
+        <v>56.47</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>61.78</v>
+        <v>59.69</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -31461,17 +31555,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -31480,22 +31574,22 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>52.69</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>54.44</v>
-      </c>
-      <c r="G149" s="3" t="n">
-        <v>56.69</v>
-      </c>
-      <c r="H149" s="3" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="I149" s="3" t="n">
-        <v>61.94</v>
-      </c>
-      <c r="J149" s="3" t="n">
-        <v>64.67</v>
+        <v>40.39</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="H149" s="4" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="I149" s="4" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="J149" s="4" t="n">
+        <v>36.77</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
@@ -31507,17 +31601,17 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -31526,22 +31620,22 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>44.35</v>
+        <v>64.44</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>45.17</v>
+        <v>65.25</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>47.96</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>51.78</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>56.47</v>
+        <v>66.14</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>59.69</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -31558,12 +31652,12 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -31572,22 +31666,22 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>64.44</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>65.25</v>
-      </c>
-      <c r="G151" s="3" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="H151" s="3" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I151" s="3" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="J151" s="3" t="n">
-        <v>66.81999999999999</v>
+        <v>42.04</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="I151" s="4" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="J151" s="4" t="n">
+        <v>29.4</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
@@ -31604,12 +31698,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -31618,22 +31712,22 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>42.04</v>
-      </c>
-      <c r="F152" s="4" t="n">
-        <v>37.61</v>
-      </c>
-      <c r="G152" s="4" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="H152" s="4" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="I152" s="4" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="J152" s="4" t="n">
-        <v>29.4</v>
+        <v>48.77</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>43</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -31650,12 +31744,12 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -31664,22 +31758,22 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>48.77</v>
+        <v>45.28</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="G153" s="3" t="n">
-        <v>45.89</v>
-      </c>
-      <c r="H153" s="3" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="I153" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="J153" s="3" t="n">
-        <v>43</v>
+        <v>42.43</v>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v>35.58</v>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>32.94</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
@@ -31696,12 +31790,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -31710,22 +31804,22 @@
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>45.28</v>
+        <v>50.47</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="G154" s="4" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="H154" s="4" t="n">
-        <v>35.58</v>
-      </c>
-      <c r="I154" s="4" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="J154" s="4" t="n">
-        <v>32.94</v>
+        <v>48.77</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>47.41</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -31742,12 +31836,12 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -31756,22 +31850,22 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>50.47</v>
+        <v>48.6</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>48.77</v>
+        <v>48.02</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>47.07</v>
+        <v>47.35</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>46.51</v>
+        <v>46.83</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>46.45</v>
+        <v>46.58</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>47.41</v>
+        <v>45.91</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
@@ -31788,12 +31882,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -31802,22 +31896,22 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>48.6</v>
+        <v>64.7</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>48.02</v>
+        <v>63.84</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>47.35</v>
+        <v>62.7</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>46.83</v>
+        <v>60.99</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>46.58</v>
+        <v>59.35</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>45.91</v>
+        <v>58.22</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -31834,12 +31928,12 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -31848,22 +31942,22 @@
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>64.7</v>
+        <v>45.11</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>63.84</v>
+        <v>43.32</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>62.7</v>
+        <v>42.48</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>60.99</v>
+        <v>42.88</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>59.35</v>
+        <v>44.32</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>58.22</v>
+        <v>48.75</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
@@ -31875,17 +31969,17 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -31894,22 +31988,22 @@
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>45.11</v>
+        <v>51.73</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>43.32</v>
+        <v>53.01</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>42.48</v>
+        <v>56.11</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>42.88</v>
+        <v>59.37</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>44.32</v>
+        <v>61.03</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>48.75</v>
+        <v>57.81</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -31931,7 +32025,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -31940,22 +32034,22 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>51.73</v>
+        <v>54.47</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>53.01</v>
+        <v>54.6</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>56.11</v>
+        <v>54.98</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>59.37</v>
+        <v>55.08</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>61.03</v>
+        <v>54.7</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>57.81</v>
+        <v>51.45</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
@@ -31977,7 +32071,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -31986,22 +32080,22 @@
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>54.47</v>
+        <v>44.76</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>54.6</v>
+        <v>47.73</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>54.98</v>
+        <v>52.61</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>55.08</v>
+        <v>56.76</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>54.7</v>
+        <v>58.45</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>51.45</v>
+        <v>54.12</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -32023,7 +32117,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -32031,23 +32125,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E161" s="3" t="n">
-        <v>44.76</v>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>47.73</v>
+      <c r="E161" s="4" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>35.56</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>52.61</v>
+        <v>40.36</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>56.76</v>
+        <v>46.88</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>58.45</v>
+        <v>52.9</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>54.12</v>
+        <v>57.39</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
@@ -32069,7 +32163,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -32077,23 +32171,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E162" s="4" t="n">
-        <v>32.44</v>
-      </c>
-      <c r="F162" s="4" t="n">
-        <v>35.56</v>
+      <c r="E162" s="3" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>46.66</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>40.36</v>
+        <v>49.63</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>46.88</v>
+        <v>52.13</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>52.9</v>
+        <v>53.19</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>57.39</v>
+        <v>50.33</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -32115,7 +32209,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -32123,23 +32217,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E163" s="3" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>46.66</v>
-      </c>
-      <c r="G163" s="3" t="n">
-        <v>49.63</v>
+      <c r="E163" s="4" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>38.46</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>52.13</v>
+        <v>43.24</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>53.19</v>
+        <v>46.77</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>50.33</v>
+        <v>46.52</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
@@ -32161,7 +32255,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -32170,22 +32264,22 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>28.87</v>
-      </c>
-      <c r="F164" s="4" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="G164" s="4" t="n">
-        <v>38.46</v>
+        <v>38.03</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>43.63</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>43.24</v>
+        <v>45.89</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>46.77</v>
+        <v>47.71</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>46.52</v>
+        <v>47.91</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -32207,7 +32301,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -32216,22 +32310,22 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>51.87</v>
+        <v>40.65</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>50.59</v>
+        <v>41.2</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>49.32</v>
+        <v>42.75</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>47.02</v>
+        <v>46.71</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>45.05</v>
+        <v>50.24</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>42.17</v>
+        <v>50.52</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
@@ -32243,17 +32337,17 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -32261,23 +32355,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E166" s="4" t="n">
-        <v>38.03</v>
+      <c r="E166" s="3" t="n">
+        <v>53.33</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>40.68</v>
+        <v>50.87</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>43.63</v>
+        <v>49.44</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>45.89</v>
+        <v>49.41</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>47.71</v>
+        <v>49.56</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>47.91</v>
+        <v>50.19</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -32289,17 +32383,17 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -32308,22 +32402,22 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>40.65</v>
+        <v>52.33</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>41.2</v>
+        <v>50.89</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>42.75</v>
+        <v>50.68</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>46.71</v>
+        <v>51.92</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>50.24</v>
+        <v>53.51</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>50.52</v>
+        <v>55.62</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
@@ -32345,7 +32439,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -32354,22 +32448,22 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>53.33</v>
+        <v>55.82</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>50.87</v>
+        <v>54.25</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>49.44</v>
+        <v>53.59</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>49.41</v>
+        <v>55.27</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>49.56</v>
+        <v>57.5</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>50.19</v>
+        <v>59.53</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -32391,7 +32485,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Santiago del Estero</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -32400,22 +32494,22 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>52.33</v>
+        <v>60.77</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>50.89</v>
+        <v>59.81</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>50.68</v>
+        <v>59.92</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>51.92</v>
+        <v>60.88</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>53.51</v>
+        <v>63.04</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>55.62</v>
+        <v>66.44</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
@@ -32427,41 +32521,41 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>甘蔗</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>55.82</v>
+        <v>59.49</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>54.25</v>
+        <v>58.29</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>53.59</v>
+        <v>56.22</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>55.27</v>
+        <v>53.23</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>57.5</v>
+        <v>49.98</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>59.53</v>
+        <v>47.76</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -32473,41 +32567,41 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>甘蔗</t>
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>60.77</v>
+        <v>49.25</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>59.81</v>
+        <v>48.23</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>59.92</v>
+        <v>47.49</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>60.88</v>
+        <v>48.06</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>63.04</v>
+        <v>49.71</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>66.44</v>
+        <v>51.68</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
@@ -32529,7 +32623,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -32538,22 +32632,22 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>59.49</v>
+        <v>60.85</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>58.29</v>
+        <v>61.31</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>56.22</v>
+        <v>60.68</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>53.23</v>
+        <v>59.71</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>49.98</v>
+        <v>57.9</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>47.76</v>
+        <v>56.69</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -32575,7 +32669,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -32584,22 +32678,22 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>49.25</v>
+        <v>67.48</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>48.23</v>
+        <v>67.37</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>47.49</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>48.06</v>
+        <v>63.51</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>49.71</v>
+        <v>59.61</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>51.68</v>
+        <v>57.14</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
@@ -32611,17 +32705,17 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北方邦</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -32630,22 +32724,22 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>60.85</v>
+        <v>73.64</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>61.31</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>60.68</v>
+        <v>62.11</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>59.71</v>
+        <v>56.23</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>57.9</v>
+        <v>49.23</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>56.69</v>
+        <v>42.05</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -32667,7 +32761,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>北方邦</t>
+          <t>卡纳塔克邦</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -32676,22 +32770,22 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>73.64</v>
+        <v>68.56</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>62.11</v>
+        <v>59.21</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>56.23</v>
+        <v>55.77</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>49.23</v>
+        <v>52.98</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>42.05</v>
+        <v>50.59</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
@@ -32713,7 +32807,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>卡纳塔克邦</t>
+          <t>古吉拉特邦</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -32722,22 +32816,22 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>68.56</v>
+        <v>58.37</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>64.5</v>
+        <v>53.4</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>59.21</v>
+        <v>48.24</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>55.77</v>
-      </c>
-      <c r="I176" s="3" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="J176" s="3" t="n">
-        <v>50.59</v>
+        <v>43.19</v>
+      </c>
+      <c r="I176" s="4" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="J176" s="4" t="n">
+        <v>35.81</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -32759,7 +32853,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>古吉拉特邦</t>
+          <t>安得拉邦</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -32768,22 +32862,22 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>58.37</v>
+        <v>54.84</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>48.24</v>
+        <v>48.09</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>43.19</v>
-      </c>
-      <c r="I177" s="4" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="J177" s="4" t="n">
-        <v>35.81</v>
+        <v>44.78</v>
+      </c>
+      <c r="I177" s="3" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="J177" s="3" t="n">
+        <v>40.39</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
@@ -32805,7 +32899,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>安得拉邦</t>
+          <t>泰米尔纳德邦</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -32814,22 +32908,22 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>54.84</v>
+        <v>69.55</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>51.4</v>
+        <v>68.08</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>48.09</v>
+        <v>64.37</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>44.78</v>
+        <v>62.05</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>42.48</v>
+        <v>60.31</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>40.39</v>
+        <v>57.86</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -32851,7 +32945,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>泰米尔纳德邦</t>
+          <t>马哈拉施特拉邦</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -32860,22 +32954,22 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>69.55</v>
+        <v>60.77</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>68.08</v>
+        <v>55.13</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>64.37</v>
+        <v>49.06</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>62.05</v>
+        <v>44.63</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="J179" s="3" t="n">
-        <v>57.86</v>
+        <v>41.72</v>
+      </c>
+      <c r="J179" s="4" t="n">
+        <v>39.59</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
@@ -34875,7 +34969,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Odeska</t>
+          <t>Luhanska</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -34884,22 +34978,22 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>75.62</v>
+        <v>57.9</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>77.18000000000001</v>
+        <v>56.31</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>77.88</v>
+        <v>55.8</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>76.45999999999999</v>
+        <v>57.05</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>73.88</v>
+        <v>57.4</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>70.58</v>
+        <v>58.8</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
@@ -34921,7 +35015,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Poltavska</t>
+          <t>Odeska</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -34930,22 +35024,22 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>40.98</v>
+        <v>75.62</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>43.15</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>45.71</v>
+        <v>77.88</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>48.58</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>51.3</v>
+        <v>73.88</v>
       </c>
       <c r="J224" s="3" t="n">
-        <v>52.76</v>
+        <v>70.58</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -34967,7 +35061,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Sumy</t>
+          <t>Poltavska</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -34976,22 +35070,22 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>50.26</v>
+        <v>40.98</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>51.65</v>
+        <v>43.15</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>53.49</v>
+        <v>45.71</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>55.67</v>
+        <v>48.58</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>58.91</v>
+        <v>51.3</v>
       </c>
       <c r="J225" s="3" t="n">
-        <v>61.34</v>
+        <v>52.76</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
@@ -35013,7 +35107,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Vinnitsa</t>
+          <t>Sumy</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -35022,22 +35116,22 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>51.03</v>
+        <v>50.26</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>51.98</v>
+        <v>51.65</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>53.56</v>
+        <v>53.49</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>55.8</v>
+        <v>55.67</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>57.71</v>
+        <v>58.91</v>
       </c>
       <c r="J226" s="3" t="n">
-        <v>57.68</v>
+        <v>61.34</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -35059,7 +35153,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Zaporizka</t>
+          <t>Vinnitsa</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -35068,22 +35162,22 @@
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>63.47</v>
+        <v>51.03</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>64.09</v>
+        <v>51.98</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>62.83</v>
+        <v>53.56</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>61.43</v>
+        <v>55.8</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>59.64</v>
+        <v>57.71</v>
       </c>
       <c r="J227" s="3" t="n">
-        <v>57.86</v>
+        <v>57.68</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
@@ -35095,17 +35189,17 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>中央</t>
+          <t>Zaporizka</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -35114,22 +35208,22 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>53.16</v>
+        <v>63.47</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>54.15</v>
+        <v>64.09</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>56.52</v>
+        <v>62.83</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>59.69</v>
+        <v>61.43</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>62.74</v>
+        <v>59.64</v>
       </c>
       <c r="J228" s="3" t="n">
-        <v>65.06</v>
+        <v>57.86</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -35151,7 +35245,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>伏尔加</t>
+          <t>中央</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -35160,22 +35254,22 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>59.86</v>
+        <v>53.68</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>63.02</v>
+        <v>54.48</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>67.11</v>
+        <v>56.73</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>70.42</v>
+        <v>59.75</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>72.54000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="J229" s="3" t="n">
-        <v>73.39</v>
+        <v>64.88</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
@@ -35197,7 +35291,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>北高加索</t>
+          <t>伏尔加</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -35206,22 +35300,22 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>71.8</v>
+        <v>60.23</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>72.03</v>
+        <v>63.64</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>70.81999999999999</v>
+        <v>67.81</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>69.15000000000001</v>
+        <v>71.23</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>68.27</v>
+        <v>73.19</v>
       </c>
       <c r="J230" s="3" t="n">
-        <v>70.58</v>
+        <v>73.91</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -35243,7 +35337,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北高加索</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -35252,22 +35346,22 @@
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>65.20999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>64.73</v>
+        <v>72.03</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>64.98</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>65.14</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="I231" s="3" t="n">
-        <v>65.62</v>
+        <v>68.27</v>
       </c>
       <c r="J231" s="3" t="n">
-        <v>67.25</v>
+        <v>70.58</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
@@ -35279,17 +35373,17 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>俄罗斯</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -35298,22 +35392,22 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>64.16</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>64.92</v>
+        <v>70.81</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>65.73</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>66.09</v>
+        <v>69.92</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>65.79000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="J232" s="3" t="n">
-        <v>66.48999999999999</v>
+        <v>69.59</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -35330,12 +35424,12 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -35344,22 +35438,22 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>64.56</v>
+        <v>64.16</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>63.73</v>
+        <v>64.92</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>62.59</v>
+        <v>65.73</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>60.9</v>
+        <v>66.09</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>59.27</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="J233" s="3" t="n">
-        <v>58.16</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
@@ -35376,12 +35470,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -35390,22 +35484,22 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>44.92</v>
-      </c>
-      <c r="F234" s="3" t="n">
-        <v>42.97</v>
-      </c>
-      <c r="G234" s="3" t="n">
-        <v>42.03</v>
-      </c>
-      <c r="H234" s="3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="I234" s="3" t="n">
-        <v>43.84</v>
-      </c>
-      <c r="J234" s="3" t="n">
-        <v>48.54</v>
+        <v>42.27</v>
+      </c>
+      <c r="F234" s="4" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="G234" s="4" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="H234" s="4" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="I234" s="4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J234" s="4" t="n">
+        <v>29.35</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -35417,17 +35511,17 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -35436,22 +35530,22 @@
         </is>
       </c>
       <c r="E235" s="3" t="n">
-        <v>53.5</v>
+        <v>45.27</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="G235" s="3" t="n">
-        <v>49.51</v>
-      </c>
-      <c r="H235" s="3" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="I235" s="3" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="J235" s="3" t="n">
-        <v>50.22</v>
+        <v>42.38</v>
+      </c>
+      <c r="G235" s="4" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="H235" s="4" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="I235" s="4" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="J235" s="4" t="n">
+        <v>32.76</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
@@ -35463,17 +35557,17 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -35482,22 +35576,22 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>49.21</v>
+        <v>64.56</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>47.96</v>
+        <v>63.73</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>48.33</v>
+        <v>62.59</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>49.53</v>
+        <v>60.9</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>51.3</v>
+        <v>59.27</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>51.79</v>
+        <v>58.16</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -35519,7 +35613,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -35528,22 +35622,22 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>56.02</v>
+        <v>53.5</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>54.4</v>
+        <v>50.98</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>53.71</v>
+        <v>49.51</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>55.39</v>
+        <v>49.46</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>57.65</v>
+        <v>49.6</v>
       </c>
       <c r="J237" s="3" t="n">
-        <v>59.7</v>
+        <v>50.22</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
@@ -35555,41 +35649,41 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>La Pampa</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>高粱</t>
+          <t>葵籽</t>
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>42.23</v>
+        <v>49.21</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>43.82</v>
+        <v>47.96</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>43.62</v>
+        <v>48.33</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="I238" s="4" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="J238" s="4" t="n">
-        <v>27.56</v>
+        <v>49.53</v>
+      </c>
+      <c r="I238" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="J238" s="3" t="n">
+        <v>51.79</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -35601,41 +35695,41 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Bauchi</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>高粱</t>
-        </is>
-      </c>
-      <c r="E239" s="4" t="n">
-        <v>33.47</v>
-      </c>
-      <c r="F239" s="4" t="n">
-        <v>36.12</v>
-      </c>
-      <c r="G239" s="4" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="H239" s="4" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="I239" s="4" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="J239" s="4" t="n">
-        <v>23.49</v>
+          <t>葵籽</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="G239" s="3" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="H239" s="3" t="n">
+        <v>55.39</v>
+      </c>
+      <c r="I239" s="3" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="J239" s="3" t="n">
+        <v>59.7</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
@@ -35657,7 +35751,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -35666,22 +35760,22 @@
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>52.07</v>
+        <v>42.23</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>56.9</v>
+        <v>43.82</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>61.46</v>
+        <v>43.62</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>63.02</v>
-      </c>
-      <c r="I240" s="3" t="n">
-        <v>61.49</v>
-      </c>
-      <c r="J240" s="3" t="n">
-        <v>56.35</v>
+        <v>40.29</v>
+      </c>
+      <c r="I240" s="4" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="J240" s="4" t="n">
+        <v>27.56</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -35703,7 +35797,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Gombe</t>
+          <t>Bauchi</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -35712,22 +35806,22 @@
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>39.24</v>
-      </c>
-      <c r="F241" s="3" t="n">
-        <v>40.05</v>
-      </c>
-      <c r="G241" s="3" t="n">
-        <v>40.47</v>
+        <v>33.47</v>
+      </c>
+      <c r="F241" s="4" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="G241" s="4" t="n">
+        <v>36.7</v>
       </c>
       <c r="H241" s="4" t="n">
-        <v>38.74</v>
+        <v>34.2</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>35.13</v>
+        <v>29.51</v>
       </c>
       <c r="J241" s="4" t="n">
-        <v>28.87</v>
+        <v>23.49</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
@@ -35749,7 +35843,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Jigawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -35758,22 +35852,22 @@
         </is>
       </c>
       <c r="E242" s="3" t="n">
-        <v>43.85</v>
+        <v>52.07</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>44.53</v>
+        <v>56.9</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>44.65</v>
+        <v>61.46</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>42.62</v>
-      </c>
-      <c r="I242" s="4" t="n">
-        <v>39.85</v>
-      </c>
-      <c r="J242" s="4" t="n">
-        <v>34.12</v>
+        <v>63.02</v>
+      </c>
+      <c r="I242" s="3" t="n">
+        <v>61.49</v>
+      </c>
+      <c r="J242" s="3" t="n">
+        <v>56.35</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -35795,7 +35889,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Kaduna</t>
+          <t>Gombe</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -35804,22 +35898,22 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="F243" s="4" t="n">
-        <v>33.79</v>
-      </c>
-      <c r="G243" s="4" t="n">
-        <v>32.36</v>
+        <v>39.24</v>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="G243" s="3" t="n">
+        <v>40.47</v>
       </c>
       <c r="H243" s="4" t="n">
-        <v>29.52</v>
+        <v>38.74</v>
       </c>
       <c r="I243" s="4" t="n">
-        <v>25.87</v>
+        <v>35.13</v>
       </c>
       <c r="J243" s="4" t="n">
-        <v>24.33</v>
+        <v>28.87</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
@@ -35841,7 +35935,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Kano</t>
+          <t>Jigawa</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -35849,23 +35943,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E244" s="4" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="F244" s="4" t="n">
-        <v>37.45</v>
-      </c>
-      <c r="G244" s="4" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="H244" s="4" t="n">
-        <v>36.55</v>
+      <c r="E244" s="3" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="G244" s="3" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>42.62</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>32.9</v>
+        <v>39.85</v>
       </c>
       <c r="J244" s="4" t="n">
-        <v>27.56</v>
+        <v>34.12</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -35887,7 +35981,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Kaduna</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -35895,23 +35989,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E245" s="3" t="n">
-        <v>46.14</v>
-      </c>
-      <c r="F245" s="3" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="G245" s="3" t="n">
-        <v>49.35</v>
-      </c>
-      <c r="H245" s="3" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="I245" s="3" t="n">
-        <v>45.98</v>
-      </c>
-      <c r="J245" s="3" t="n">
-        <v>41.99</v>
+      <c r="E245" s="4" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="F245" s="4" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="G245" s="4" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="H245" s="4" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="I245" s="4" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="J245" s="4" t="n">
+        <v>24.33</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
@@ -35933,7 +36027,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Kano</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -35942,22 +36036,22 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>35.33</v>
+        <v>35.9</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>37.1</v>
+        <v>37.45</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>37.48</v>
+        <v>38.16</v>
       </c>
       <c r="H246" s="4" t="n">
-        <v>35.83</v>
+        <v>36.55</v>
       </c>
       <c r="I246" s="4" t="n">
-        <v>32.72</v>
+        <v>32.9</v>
       </c>
       <c r="J246" s="4" t="n">
-        <v>27.93</v>
+        <v>27.56</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -35979,7 +36073,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -35987,23 +36081,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E247" s="4" t="n">
-        <v>26.26</v>
-      </c>
-      <c r="F247" s="4" t="n">
-        <v>29.18</v>
-      </c>
-      <c r="G247" s="4" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="H247" s="4" t="n">
-        <v>28.59</v>
-      </c>
-      <c r="I247" s="4" t="n">
-        <v>26.52</v>
-      </c>
-      <c r="J247" s="4" t="n">
-        <v>24.26</v>
+      <c r="E247" s="3" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="G247" s="3" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="I247" s="3" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="J247" s="3" t="n">
+        <v>41.99</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
@@ -36025,7 +36119,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Plateau</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -36033,23 +36127,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E248" s="3" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="F248" s="3" t="n">
-        <v>47.26</v>
-      </c>
-      <c r="G248" s="3" t="n">
-        <v>46.23</v>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>42.62</v>
+      <c r="E248" s="4" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="F248" s="4" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G248" s="4" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="H248" s="4" t="n">
+        <v>35.83</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>37.34</v>
+        <v>32.72</v>
       </c>
       <c r="J248" s="4" t="n">
-        <v>31.55</v>
+        <v>27.93</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -36071,7 +36165,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Sokoto</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -36079,23 +36173,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E249" s="3" t="n">
-        <v>50.97</v>
-      </c>
-      <c r="F249" s="3" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="G249" s="3" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="H249" s="3" t="n">
-        <v>54.21</v>
-      </c>
-      <c r="I249" s="3" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="J249" s="3" t="n">
-        <v>48.26</v>
+      <c r="E249" s="4" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="F249" s="4" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="G249" s="4" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="H249" s="4" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="I249" s="4" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="J249" s="4" t="n">
+        <v>24.26</v>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
@@ -36117,7 +36211,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Taraba</t>
+          <t>Plateau</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -36126,22 +36220,22 @@
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>48.2</v>
+        <v>45.62</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>49.06</v>
+        <v>47.26</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>47.27</v>
+        <v>46.23</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>43.21</v>
+        <v>42.62</v>
       </c>
       <c r="I250" s="4" t="n">
-        <v>37.95</v>
+        <v>37.34</v>
       </c>
       <c r="J250" s="4" t="n">
-        <v>34.11</v>
+        <v>31.55</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -36163,7 +36257,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Yobe</t>
+          <t>Sokoto</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -36172,22 +36266,22 @@
         </is>
       </c>
       <c r="E251" s="3" t="n">
-        <v>42.83</v>
+        <v>50.97</v>
       </c>
       <c r="F251" s="3" t="n">
-        <v>46.05</v>
+        <v>53.37</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>49.55</v>
+        <v>54.81</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>49.29</v>
+        <v>54.21</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>46.75</v>
+        <v>52.63</v>
       </c>
       <c r="J251" s="3" t="n">
-        <v>41.87</v>
+        <v>48.26</v>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
@@ -36209,7 +36303,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Taraba</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -36218,22 +36312,22 @@
         </is>
       </c>
       <c r="E252" s="3" t="n">
-        <v>44.26</v>
+        <v>48.2</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>48.78</v>
+        <v>49.06</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>51</v>
+        <v>47.27</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="I252" s="3" t="n">
-        <v>46.54</v>
-      </c>
-      <c r="J252" s="3" t="n">
-        <v>40.18</v>
+        <v>43.21</v>
+      </c>
+      <c r="I252" s="4" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="J252" s="4" t="n">
+        <v>34.11</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -36245,17 +36339,17 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>圣保罗州</t>
+          <t>Yobe</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -36264,22 +36358,22 @@
         </is>
       </c>
       <c r="E253" s="3" t="n">
-        <v>52.3</v>
+        <v>42.83</v>
       </c>
       <c r="F253" s="3" t="n">
-        <v>54.47</v>
+        <v>46.05</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>56.23</v>
+        <v>49.55</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>59.39</v>
+        <v>49.29</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>62.07</v>
+        <v>46.75</v>
       </c>
       <c r="J253" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>41.87</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
@@ -36291,17 +36385,17 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -36310,22 +36404,22 @@
         </is>
       </c>
       <c r="E254" s="3" t="n">
-        <v>51.73</v>
+        <v>44.26</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>52.2</v>
+        <v>48.78</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>53.21</v>
+        <v>51</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>55.67</v>
+        <v>50.6</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>59.13</v>
+        <v>46.54</v>
       </c>
       <c r="J254" s="3" t="n">
-        <v>63.48</v>
+        <v>40.18</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -36347,7 +36441,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>圣保罗州</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -36356,22 +36450,22 @@
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>53.46</v>
+        <v>52.3</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>54.66</v>
+        <v>54.47</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>56.41</v>
+        <v>56.23</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>59.07</v>
+        <v>59.39</v>
       </c>
       <c r="I255" s="3" t="n">
-        <v>61.89</v>
+        <v>62.07</v>
       </c>
       <c r="J255" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
@@ -36393,7 +36487,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -36402,22 +36496,22 @@
         </is>
       </c>
       <c r="E256" s="3" t="n">
-        <v>45.91</v>
+        <v>51.73</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>46.68</v>
+        <v>52.2</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>49.38</v>
+        <v>53.21</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>53.14</v>
+        <v>55.67</v>
       </c>
       <c r="I256" s="3" t="n">
-        <v>57.7</v>
+        <v>59.13</v>
       </c>
       <c r="J256" s="3" t="n">
-        <v>60.69</v>
+        <v>63.48</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -36429,17 +36523,17 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -36447,23 +36541,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E257" s="4" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="F257" s="4" t="n">
-        <v>34.35</v>
-      </c>
-      <c r="G257" s="4" t="n">
-        <v>39.29</v>
+      <c r="E257" s="3" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="G257" s="3" t="n">
+        <v>49.38</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>45.88</v>
+        <v>53.14</v>
       </c>
       <c r="I257" s="3" t="n">
-        <v>51.97</v>
+        <v>57.7</v>
       </c>
       <c r="J257" s="3" t="n">
-        <v>56.54</v>
+        <v>60.69</v>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
@@ -36485,38 +36579,84 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>高粱</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="F258" s="4" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="G258" s="4" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="H258" s="3" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="I258" s="3" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="J258" s="3" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
           <t>Texas</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="D259" s="3" t="inlineStr">
         <is>
           <t>高粱</t>
         </is>
       </c>
-      <c r="E258" s="3" t="n">
+      <c r="E259" s="3" t="n">
         <v>43.98</v>
       </c>
-      <c r="F258" s="3" t="n">
+      <c r="F259" s="3" t="n">
         <v>45.88</v>
       </c>
-      <c r="G258" s="3" t="n">
+      <c r="G259" s="3" t="n">
         <v>48.08</v>
       </c>
-      <c r="H258" s="3" t="n">
+      <c r="H259" s="3" t="n">
         <v>49.49</v>
       </c>
-      <c r="I258" s="3" t="n">
+      <c r="I259" s="3" t="n">
         <v>49.88</v>
       </c>
-      <c r="J258" s="3" t="n">
+      <c r="J259" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="K258" s="2" t="inlineStr">
+      <c r="K259" s="3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="L258" s="2" t="n"/>
+      <c r="L259" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -12657,78 +12657,6 @@
           <val>
             <numRef>
               <f>'VHI_最近6周汇总'!$E$256:$J$256</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="1"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="1"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart256.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln w="20000">
-              <a:solidFill>
-                <a:srgbClr val="E00000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="E00000"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="E00000"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <val>
-            <numRef>
-              <f>'VHI_最近6周汇总'!$E$257:$J$257</f>
             </numRef>
           </val>
         </ser>
@@ -24209,28 +24137,6 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>256</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2880000" cy="720000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="256" name="Chart 256"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId256"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -24523,7 +24429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L257"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -24937,7 +24843,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>巴伊亚州</t>
+          <t>巴拉那州</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -24946,22 +24852,22 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>42.79</v>
+        <v>55.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>43.92</v>
+        <v>59.06</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45.42</v>
+        <v>61.22</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>47.22</v>
+        <v>63.15</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>49.17</v>
+        <v>65.41</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>52.38</v>
+        <v>67.37</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -24983,7 +24889,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>巴拉那州</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -24992,22 +24898,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>55.86</v>
+        <v>50.35</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>59.06</v>
+        <v>50.88</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>61.22</v>
+        <v>51.93</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>63.15</v>
+        <v>54.38</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>65.41</v>
+        <v>57.88</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>67.37</v>
+        <v>62.29</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -25029,7 +24935,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -25038,22 +24944,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>50.35</v>
+        <v>53.04</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>50.88</v>
+        <v>54.28</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>51.93</v>
+        <v>56.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>54.38</v>
+        <v>59.94</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>57.88</v>
+        <v>63.58</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>62.29</v>
+        <v>67.19</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -25075,7 +24981,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -25084,22 +24990,22 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>53.04</v>
+        <v>44.75</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>54.28</v>
+        <v>45.54</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>56.5</v>
+        <v>48.35</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>59.94</v>
+        <v>52.16</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>63.58</v>
+        <v>56.77</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>67.19</v>
+        <v>59.91</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -25111,17 +25017,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -25130,22 +25036,22 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>44.75</v>
+        <v>51.94</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>45.54</v>
+        <v>53.23</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>48.35</v>
+        <v>56.35</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>52.16</v>
+        <v>59.62</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>56.77</v>
+        <v>61.28</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>59.91</v>
+        <v>58.06</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -25167,7 +25073,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -25176,22 +25082,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>51.94</v>
+        <v>54.46</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>53.23</v>
+        <v>54.59</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>56.35</v>
+        <v>54.97</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>59.62</v>
+        <v>55.07</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>61.28</v>
+        <v>54.69</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>58.06</v>
+        <v>51.42</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -25433,17 +25339,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -25451,23 +25357,23 @@
           <t>大豆</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>50.9</v>
+      <c r="E20" s="4" t="n">
+        <v>37.47</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>39.94</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>49.47</v>
+        <v>42.87</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>49.43</v>
+        <v>45.09</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>49.58</v>
+        <v>46.88</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>50.22</v>
+        <v>46.47</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -25489,7 +25395,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -25498,22 +25404,22 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>52.1</v>
+        <v>53.37</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>50.69</v>
+        <v>50.9</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>50.51</v>
+        <v>49.47</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>51.76</v>
+        <v>49.43</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>53.35</v>
+        <v>49.58</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>55.46</v>
+        <v>50.22</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -25535,7 +25441,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -25544,22 +25450,22 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>55.68</v>
+        <v>52.1</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>54.1</v>
+        <v>50.69</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>53.45</v>
+        <v>50.51</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>55.15</v>
+        <v>51.76</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>57.38</v>
+        <v>53.35</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>59.42</v>
+        <v>55.46</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -25581,7 +25487,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -25590,22 +25496,22 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>60.26</v>
+        <v>55.68</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>59.26</v>
+        <v>54.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59.33</v>
+        <v>53.45</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>60.28</v>
+        <v>55.15</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>62.33</v>
+        <v>57.38</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>65.56999999999999</v>
+        <v>59.42</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -25617,41 +25523,41 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>中央</t>
+          <t>Santiago del Estero</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>大麦</t>
+          <t>大豆</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>53.28</v>
+        <v>60.26</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>54.34</v>
+        <v>59.26</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>56.56</v>
+        <v>59.33</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>59.54</v>
+        <v>60.28</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>62.46</v>
+        <v>62.33</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -25673,7 +25579,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>乌拉尔</t>
+          <t>中央</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -25682,22 +25588,22 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>63.02</v>
+        <v>53.28</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>66.64</v>
+        <v>54.34</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>69.11</v>
+        <v>56.56</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>69.23</v>
+        <v>59.54</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>67.51000000000001</v>
+        <v>62.46</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>67.51000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -25719,7 +25625,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>伏尔加</t>
+          <t>乌拉尔</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -25728,22 +25634,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>60.29</v>
+        <v>63.02</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>63.53</v>
+        <v>66.64</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>67.64</v>
+        <v>69.11</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>71.03</v>
+        <v>69.23</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>72.98</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>73.89</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -25765,7 +25671,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>北高加索</t>
+          <t>伏尔加</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -25774,22 +25680,22 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>71.43000000000001</v>
+        <v>61.06</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>71.83</v>
+        <v>64.44</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>70.7</v>
+        <v>68.61</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>68.27</v>
+        <v>73.81</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>70.5</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -25811,7 +25717,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北高加索</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -25820,22 +25726,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>64.44</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>62.11</v>
+        <v>71.63</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>60.72</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>60.44</v>
+        <v>68.98</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>60.12</v>
+        <v>68.22</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>61.01</v>
+        <v>70.52</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -25857,7 +25763,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>西伯利亚</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -25866,22 +25772,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>55.78</v>
+        <v>64.44</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>56.43</v>
+        <v>62.11</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>56.52</v>
+        <v>60.72</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>56.29</v>
+        <v>60.44</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>55.53</v>
+        <v>60.12</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>53.92</v>
+        <v>61.01</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -25903,7 +25809,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>西北部</t>
+          <t>西伯利亚</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -25912,22 +25818,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>60.86</v>
+        <v>55.78</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>60.79</v>
+        <v>56.43</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>61.71</v>
+        <v>56.52</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>62.1</v>
+        <v>56.29</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>61.7</v>
+        <v>55.53</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>60.97</v>
+        <v>53.92</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -25939,17 +25845,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>俄罗斯</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>西北部</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -25958,22 +25864,22 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>54.82</v>
+        <v>60.86</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>56.23</v>
+        <v>60.79</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>54.76</v>
+        <v>61.71</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>53.02</v>
+        <v>62.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>52.16</v>
+        <v>61.7</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>52.39</v>
+        <v>60.97</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -25990,12 +25896,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -26004,22 +25910,22 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>38.79</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>35.39</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>32.59</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>30.58</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>30.35</v>
+        <v>54.82</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>53.02</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>52.39</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -26036,12 +25942,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -26050,22 +25956,22 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>46.78</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>44.37</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>43.63</v>
+        <v>42.86</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>30.35</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -26878,22 +26784,22 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>62.8</v>
+        <v>63.83</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>66.38</v>
+        <v>66.88</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>68.84999999999999</v>
+        <v>68.23</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>68.98</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>67.28</v>
+        <v>66.86</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>67.3</v>
+        <v>68.08</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -26924,22 +26830,22 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>60.2</v>
+        <v>60.08</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>63.42</v>
+        <v>63.43</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>70.87</v>
+        <v>71.17</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>72.81</v>
+        <v>73.09</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>73.73</v>
+        <v>73.98</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -28111,7 +28017,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Western Australia</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -28120,22 +28026,22 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>43.35</v>
+        <v>47.33</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>44.85</v>
+        <v>47.45</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>47.39</v>
+        <v>48.24</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>48.49</v>
+        <v>49.35</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>48</v>
+        <v>49.6</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>48.26</v>
+        <v>48.71</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -28147,17 +28053,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Western Australia</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -28166,22 +28072,22 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>44.12</v>
+        <v>43.35</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>43.12</v>
+        <v>44.85</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>42.66</v>
+        <v>47.39</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>43.86</v>
+        <v>48.49</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>46.11</v>
+        <v>48</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>51.46</v>
+        <v>48.26</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -28203,7 +28109,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -28211,23 +28117,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n">
-        <v>32.11</v>
-      </c>
-      <c r="F80" s="4" t="n">
-        <v>35.31</v>
+      <c r="E80" s="3" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>43.12</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>40.28</v>
+        <v>42.66</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>46.92</v>
+        <v>43.86</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>53.07</v>
+        <v>46.11</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>57.63</v>
+        <v>51.46</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -28249,7 +28155,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -28257,23 +28163,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E81" s="3" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>45.02</v>
+      <c r="E81" s="4" t="n">
+        <v>32.11</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>35.31</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>47.89</v>
+        <v>40.28</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>50.27</v>
+        <v>46.92</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>51.64</v>
+        <v>53.07</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>48.92</v>
+        <v>57.63</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -28295,7 +28201,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -28304,22 +28210,22 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>42.33</v>
+        <v>42.86</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.84</v>
+        <v>45.02</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>46.34</v>
+        <v>47.89</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>50.82</v>
+        <v>50.27</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>55.04</v>
+        <v>51.64</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>59.14</v>
+        <v>48.92</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -28341,7 +28247,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -28350,22 +28256,22 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>44.6</v>
+        <v>42.33</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>46.3</v>
+        <v>43.84</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>48.92</v>
+        <v>46.34</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>51.47</v>
+        <v>50.82</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>53.77</v>
+        <v>55.04</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>54.62</v>
+        <v>59.14</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -28387,7 +28293,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -28395,23 +28301,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E84" s="4" t="n">
-        <v>38.19</v>
+      <c r="E84" s="3" t="n">
+        <v>44.6</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>43</v>
+        <v>46.3</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>48.34</v>
+        <v>48.92</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>54.02</v>
+        <v>51.47</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>59.37</v>
+        <v>53.77</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>63.87</v>
+        <v>54.62</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -28433,7 +28339,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -28441,23 +28347,23 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="E85" s="3" t="n">
-        <v>47.91</v>
+      <c r="E85" s="4" t="n">
+        <v>38.19</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>47.59</v>
+        <v>43</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>47.19</v>
+        <v>48.34</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>48</v>
+        <v>54.02</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>49.45</v>
+        <v>59.37</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>53.54</v>
+        <v>63.87</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -28469,17 +28375,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -28488,22 +28394,22 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>53.51</v>
+        <v>47.91</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>50.99</v>
+        <v>47.59</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>49.55</v>
+        <v>47.19</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>49.52</v>
+        <v>48</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>49.68</v>
+        <v>49.45</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>50.31</v>
+        <v>53.54</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -28525,7 +28431,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -28534,22 +28440,22 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>51.72</v>
+        <v>53.51</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>50.35</v>
+        <v>50.99</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>50.19</v>
+        <v>49.55</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>51.47</v>
+        <v>49.52</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>53.07</v>
+        <v>49.68</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>55.16</v>
+        <v>50.31</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -28571,7 +28477,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -28580,22 +28486,22 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>55.77</v>
+        <v>51.72</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>54.2</v>
+        <v>50.35</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>53.55</v>
+        <v>50.19</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>55.24</v>
+        <v>51.47</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>57.49</v>
+        <v>53.07</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>59.52</v>
+        <v>55.16</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -28607,41 +28513,41 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>棉花</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>52.92</v>
+        <v>55.77</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>55.04</v>
+        <v>54.2</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>57.01</v>
+        <v>53.55</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>58.77</v>
+        <v>55.24</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>60.73</v>
+        <v>57.49</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>59.8</v>
+        <v>59.52</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -28653,17 +28559,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>中央邦</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -28672,22 +28578,22 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>56.95</v>
+        <v>52.92</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>50.59</v>
+        <v>55.04</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>44.99</v>
+        <v>57.01</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="I90" s="4" t="n">
-        <v>36.64</v>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>34.26</v>
+        <v>58.77</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>59.8</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -28939,7 +28845,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>巴伊亚州</t>
+          <t>南马托格罗索州</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -28948,22 +28854,22 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>43.67</v>
+        <v>61.98</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>43.53</v>
+        <v>63.18</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>44.08</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>44.85</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>46.15</v>
+        <v>71.86</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>49.01</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -28975,17 +28881,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>New South Wales</t>
+          <t>巴伊亚州</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -28993,23 +28899,23 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E97" s="4" t="n">
-        <v>39.61</v>
+      <c r="E97" s="3" t="n">
+        <v>43.67</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>41.61</v>
+        <v>43.53</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>43.94</v>
+        <v>44.08</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>46.41</v>
+        <v>44.85</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>47.86</v>
+        <v>46.15</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>46.69</v>
+        <v>49.01</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
@@ -29031,7 +28937,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Queensland</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -29039,23 +28945,23 @@
           <t>棉花</t>
         </is>
       </c>
-      <c r="E98" s="3" t="n">
-        <v>45.16</v>
+      <c r="E98" s="4" t="n">
+        <v>39.61</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>43.85</v>
+        <v>41.61</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>42.27</v>
+        <v>43.94</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>42.02</v>
+        <v>46.41</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>43.05</v>
+        <v>47.86</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>43.82</v>
+        <v>46.69</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -29067,17 +28973,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Queensland</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -29086,22 +28992,22 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>63.67</v>
+        <v>45.16</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>64.06999999999999</v>
+        <v>43.85</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>42.27</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>66.37</v>
+        <v>42.02</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>66.58</v>
+        <v>43.05</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>64.97</v>
+        <v>43.82</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -29123,7 +29029,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -29132,22 +29038,22 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>57.72</v>
+        <v>63.67</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>58.46</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>58.38</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>57.87</v>
+        <v>66.37</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>56.3</v>
+        <v>66.58</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>53.44</v>
+        <v>64.97</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -29169,7 +29075,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -29178,22 +29084,22 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>63.65</v>
+        <v>55.28</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>65.37</v>
+        <v>61.48</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>67.06</v>
+        <v>67.02</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>67.45</v>
+        <v>69.84</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>67.69</v>
+        <v>71.69</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>68.28</v>
+        <v>70.53</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -29215,7 +29121,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -29224,22 +29130,22 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>55.07</v>
+        <v>57.72</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>58.56</v>
+        <v>58.46</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>61.92</v>
+        <v>58.38</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>64.09</v>
+        <v>57.87</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>65.98</v>
+        <v>56.3</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>65.5</v>
+        <v>53.44</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -29261,7 +29167,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -29270,22 +29176,22 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>56.26</v>
+        <v>63.65</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>54.94</v>
+        <v>65.37</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>54.44</v>
+        <v>67.06</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>53.49</v>
+        <v>67.45</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>53.39</v>
+        <v>67.69</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>52.29</v>
+        <v>68.28</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -29307,7 +29213,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -29316,22 +29222,22 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>61.97</v>
+        <v>55.07</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>64.03</v>
+        <v>58.56</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>66.67</v>
+        <v>61.92</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>69</v>
+        <v>64.09</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>71.22</v>
+        <v>65.98</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>71.42</v>
+        <v>65.5</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -29353,7 +29259,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -29362,22 +29268,22 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>41.96</v>
+        <v>56.26</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>44.67</v>
+        <v>54.94</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>47.66</v>
+        <v>54.44</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>49.86</v>
+        <v>53.49</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>50.8</v>
+        <v>53.39</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>51.35</v>
+        <v>52.29</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -29389,41 +29295,41 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>东加里曼丹</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>棕榈油</t>
+          <t>棉花</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>48.58</v>
+        <v>61.97</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>49.82</v>
+        <v>64.03</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>50.11</v>
+        <v>66.67</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>49.4</v>
+        <v>69</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>48.85</v>
+        <v>71.22</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>48.06</v>
+        <v>71.42</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -29435,41 +29341,41 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>中加里曼丹</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>棕榈油</t>
+          <t>棉花</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>45.92</v>
+        <v>41.96</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>46.66</v>
+        <v>44.67</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>46.8</v>
+        <v>47.66</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>46.22</v>
+        <v>49.86</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>46.34</v>
+        <v>50.8</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>46.44</v>
+        <v>51.35</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -29491,7 +29397,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>北苏门答腊</t>
+          <t>东加里曼丹</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -29500,22 +29406,22 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>46.37</v>
+        <v>48.58</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>48.74</v>
+        <v>49.82</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>52.66</v>
+        <v>50.11</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>56.03</v>
+        <v>49.4</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>58.09</v>
+        <v>48.85</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>57.77</v>
+        <v>48.06</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -29537,7 +29443,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>南苏门答腊</t>
+          <t>中加里曼丹</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -29546,22 +29452,22 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>40.97</v>
+        <v>45.92</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>41.26</v>
+        <v>46.66</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>42.12</v>
+        <v>46.8</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>43.68</v>
+        <v>46.22</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>45.92</v>
+        <v>46.34</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>47.64</v>
+        <v>46.44</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -29583,7 +29489,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>占碑</t>
+          <t>北苏门答腊</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -29591,23 +29497,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E110" s="4" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="F110" s="4" t="n">
-        <v>39.56</v>
+      <c r="E110" s="3" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>48.74</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>41.41</v>
+        <v>52.66</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>43.27</v>
+        <v>56.03</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>46.12</v>
+        <v>58.09</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>47.46</v>
+        <v>57.77</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -29629,7 +29535,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>廖内</t>
+          <t>南苏门答腊</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -29638,22 +29544,22 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>44.79</v>
+        <v>40.97</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>47.92</v>
+        <v>41.26</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>50.25</v>
+        <v>42.12</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>52.54</v>
+        <v>43.68</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>54.91</v>
+        <v>45.92</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>54.94</v>
+        <v>47.64</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
@@ -29665,17 +29571,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Johor</t>
+          <t>占碑</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -29683,23 +29589,23 @@
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E112" s="3" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>47.77</v>
+      <c r="E112" s="4" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>39.56</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>48.14</v>
+        <v>41.41</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>48.8</v>
+        <v>43.27</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>49.78</v>
+        <v>46.12</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>49.11</v>
+        <v>47.46</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -29711,17 +29617,17 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Pahang</t>
+          <t>廖内</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -29730,22 +29636,22 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>54.49</v>
+        <v>44.79</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>55.37</v>
+        <v>47.92</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>56.09</v>
+        <v>50.25</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>56.57</v>
+        <v>52.54</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>56.86</v>
+        <v>54.91</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>56.46</v>
+        <v>54.94</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
@@ -29757,17 +29663,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Perak</t>
+          <t>西加里曼丹</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -29776,22 +29682,22 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>49.38</v>
+        <v>49.19</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>50.2</v>
+        <v>49.75</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>51.45</v>
+        <v>50.02</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>53.19</v>
+        <v>49.92</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>54.1</v>
+        <v>51.1</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>53.62</v>
+        <v>53.26</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -29813,7 +29719,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Johor</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -29822,22 +29728,22 @@
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>47.78</v>
+        <v>47.4</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>47.88</v>
+        <v>47.77</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>48.48</v>
+        <v>48.14</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>48.93</v>
+        <v>48.8</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>49.27</v>
+        <v>49.78</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>49.39</v>
+        <v>49.11</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
@@ -29859,7 +29765,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Sarawak</t>
+          <t>Pahang</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -29868,22 +29774,22 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>48.42</v>
+        <v>54.49</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>49.7</v>
+        <v>55.37</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>50.22</v>
+        <v>56.09</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>50.1</v>
+        <v>56.57</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>50.38</v>
+        <v>56.86</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>51.9</v>
+        <v>56.46</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -29895,41 +29801,41 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>Perak</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>棕榈油</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>60.86</v>
+        <v>49.38</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>59.55</v>
+        <v>50.2</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>57.48</v>
+        <v>51.45</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>54.45</v>
+        <v>53.19</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>51.23</v>
+        <v>54.1</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>49.02</v>
+        <v>53.62</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
@@ -29941,41 +29847,41 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>棕榈油</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>61</v>
+        <v>47.78</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>62.62</v>
+        <v>47.88</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>63.99</v>
+        <v>48.48</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>64.89</v>
+        <v>48.93</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>64.95</v>
+        <v>49.27</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>62.47</v>
+        <v>49.39</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -29987,41 +29893,41 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>Sarawak</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>棕榈油</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>54.92</v>
+        <v>48.42</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>58.25</v>
+        <v>49.7</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>61.37</v>
+        <v>50.22</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>61.58</v>
+        <v>50.1</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>60.11</v>
+        <v>50.38</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>55.63</v>
+        <v>51.9</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
@@ -30043,7 +29949,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -30052,22 +29958,22 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>61.76</v>
+        <v>60.86</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>61.99</v>
+        <v>59.55</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>61.22</v>
+        <v>57.48</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>59.34</v>
+        <v>54.45</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>57.1</v>
+        <v>51.23</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>55.92</v>
+        <v>49.02</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -30089,7 +29995,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -30098,22 +30004,22 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>70.78</v>
+        <v>61</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>68.73</v>
+        <v>62.62</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>66.73999999999999</v>
+        <v>63.99</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>63.49</v>
+        <v>64.89</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>57.64</v>
+        <v>64.95</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>51.19</v>
+        <v>62.47</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
@@ -30135,7 +30041,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -30143,23 +30049,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E122" s="5" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>85.62</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>86.37</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>86.06999999999999</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>84.79000000000001</v>
+      <c r="E122" s="3" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>55.63</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -30181,7 +30087,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -30190,22 +30096,22 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>50.67</v>
+        <v>61.76</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>51.52</v>
+        <v>61.99</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>52.22</v>
+        <v>61.22</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>53.12</v>
+        <v>59.34</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>54.41</v>
+        <v>57.1</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>53.72</v>
+        <v>55.92</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
@@ -30227,7 +30133,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -30236,22 +30142,22 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>84.54000000000001</v>
+        <v>83.44</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>85</v>
+        <v>85.62</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>83.87</v>
+        <v>86.3</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>81.34999999999999</v>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>77.18000000000001</v>
-      </c>
-      <c r="J124" s="3" t="n">
-        <v>73.53</v>
+        <v>86.37</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>84.79000000000001</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -30273,7 +30179,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -30282,22 +30188,22 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>70.09</v>
+        <v>50.67</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>70.17</v>
+        <v>51.52</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>71.62</v>
+        <v>52.22</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>71.48999999999999</v>
+        <v>53.12</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>54.41</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>66.23999999999999</v>
+        <v>53.72</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
@@ -30319,7 +30225,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -30327,23 +30233,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E126" s="3" t="n">
-        <v>70.27</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>71.94</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>72.66</v>
-      </c>
-      <c r="H126" s="3" t="n">
-        <v>72.14</v>
+      <c r="E126" s="5" t="n">
+        <v>84.54000000000001</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>81.34999999999999</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>70.22</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -30365,7 +30271,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -30374,22 +30280,22 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>47.48</v>
+        <v>70.09</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>47.54</v>
+        <v>70.17</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>49.22</v>
+        <v>71.62</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>50.17</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>50.23</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>46.57</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
@@ -30401,17 +30307,17 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Cherkaska</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -30420,22 +30326,22 @@
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>42.55</v>
+        <v>70.27</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>43.93</v>
+        <v>71.94</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>46.4</v>
+        <v>72.66</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>50.05</v>
+        <v>72.14</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>53.45</v>
+        <v>70.22</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>54.04</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -30447,17 +30353,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Chernihivska</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -30466,22 +30372,22 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>43.3</v>
+        <v>47.48</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>43.69</v>
+        <v>47.54</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>44.83</v>
+        <v>49.22</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>46.53</v>
+        <v>50.17</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>48.47</v>
+        <v>50.23</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>49.6</v>
+        <v>46.57</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
@@ -30503,7 +30409,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Dnipropetrovska</t>
+          <t>Cherkaska</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -30512,22 +30418,22 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>55.93</v>
+        <v>42.55</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>58.14</v>
+        <v>43.93</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>58.26</v>
+        <v>46.4</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>58.44</v>
+        <v>50.05</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>58.5</v>
+        <v>53.45</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>57.74</v>
+        <v>54.04</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -30549,7 +30455,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Khersonska</t>
+          <t>Chernihivska</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -30558,22 +30464,22 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>60.86</v>
+        <v>43.3</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>57.68</v>
+        <v>43.69</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>53.27</v>
+        <v>44.83</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>48.92</v>
+        <v>46.53</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>46.47</v>
+        <v>48.47</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>44.95</v>
+        <v>49.6</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
@@ -30595,7 +30501,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Kyivska</t>
+          <t>Dnipropetrovska</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -30604,22 +30510,22 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>44.36</v>
+        <v>55.93</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>45.59</v>
+        <v>58.14</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>47.19</v>
+        <v>58.26</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>49.7</v>
+        <v>58.44</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>51.8</v>
+        <v>58.5</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>51.71</v>
+        <v>57.74</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -30641,7 +30547,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Mykolaivska</t>
+          <t>Donetsk</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -30650,22 +30556,22 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>64.67</v>
+        <v>62.34</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>64.88</v>
+        <v>62.34</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>64.01000000000001</v>
+        <v>61.06</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>62.14</v>
+        <v>60.76</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>60.35</v>
+        <v>60.95</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>58.59</v>
+        <v>61.44</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
@@ -30687,7 +30593,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Odeska</t>
+          <t>Khersonska</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -30696,22 +30602,22 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>75.62</v>
+        <v>60.86</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>77.18000000000001</v>
+        <v>57.68</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>77.88</v>
+        <v>53.27</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>76.45999999999999</v>
+        <v>48.92</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>73.88</v>
+        <v>46.47</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>70.58</v>
+        <v>44.95</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -30733,7 +30639,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Poltava</t>
+          <t>Khmelnitska</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -30742,22 +30648,22 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>40.98</v>
+        <v>44.8</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>43.15</v>
+        <v>45.02</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>45.71</v>
+        <v>45.32</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>48.58</v>
+        <v>46.29</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>51.3</v>
+        <v>47.43</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>52.76</v>
+        <v>47.24</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
@@ -30779,7 +30685,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Sumy</t>
+          <t>Kirovohradska</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -30788,22 +30694,22 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>50.26</v>
+        <v>50.64</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>51.65</v>
+        <v>52.06</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>53.49</v>
+        <v>52.77</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>55.67</v>
+        <v>54.55</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>58.91</v>
+        <v>56.44</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>61.34</v>
+        <v>56.38</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -30825,7 +30731,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Vinnitsa</t>
+          <t>Kyivska</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -30834,22 +30740,22 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>51.03</v>
+        <v>44.36</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>51.98</v>
+        <v>45.59</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>53.56</v>
+        <v>47.19</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>55.8</v>
+        <v>49.7</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>57.71</v>
+        <v>51.8</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>57.68</v>
+        <v>51.71</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
@@ -30871,7 +30777,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Zaporizka</t>
+          <t>Mykolaivska</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -30880,22 +30786,22 @@
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>63.47</v>
+        <v>64.67</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>64.09</v>
+        <v>64.88</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>62.83</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>61.43</v>
+        <v>62.14</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>59.64</v>
+        <v>60.35</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>57.86</v>
+        <v>58.59</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -30917,7 +30823,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Zhytomyrska</t>
+          <t>Odeska</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -30926,22 +30832,22 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>45.7</v>
+        <v>75.62</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>46.64</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>47.15</v>
+        <v>77.88</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>47.2</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>47.69</v>
+        <v>73.88</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>46.92</v>
+        <v>70.58</v>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
@@ -30953,17 +30859,17 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>南马托格罗索州</t>
+          <t>Poltava</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -30972,22 +30878,22 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>60.13</v>
+        <v>40.98</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>60.87</v>
+        <v>43.15</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>63.28</v>
+        <v>45.71</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>66.65000000000001</v>
+        <v>48.58</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>69.79000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>71.92</v>
+        <v>52.76</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -30999,17 +30905,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>圣保罗州</t>
+          <t>Sumy</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -31018,22 +30924,22 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>51.61</v>
+        <v>50.26</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>56.06</v>
+        <v>51.65</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>58.45</v>
+        <v>53.49</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>61.56</v>
+        <v>55.67</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>64.02</v>
+        <v>58.91</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>66.87</v>
+        <v>61.34</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -31045,17 +30951,17 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>巴拉那州</t>
+          <t>Vinnitsa</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -31064,22 +30970,22 @@
         </is>
       </c>
       <c r="E142" s="3" t="n">
-        <v>55.23</v>
+        <v>51.03</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>58.58</v>
+        <v>51.98</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>60.83</v>
+        <v>53.56</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>62.76</v>
+        <v>55.8</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>64.98999999999999</v>
+        <v>57.71</v>
       </c>
       <c r="J142" s="3" t="n">
-        <v>66.94</v>
+        <v>57.68</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -31091,17 +30997,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>Zaporizka</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -31110,22 +31016,22 @@
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>49.68</v>
+        <v>63.47</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>50.2</v>
+        <v>64.09</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>51.24</v>
+        <v>62.83</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>53.73</v>
+        <v>61.43</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>57.25</v>
+        <v>59.64</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>61.78</v>
+        <v>57.86</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
@@ -31137,17 +31043,17 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>Zhytomyrska</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -31156,22 +31062,22 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>52.69</v>
+        <v>45.7</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>54.44</v>
+        <v>46.64</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>56.69</v>
+        <v>47.15</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>59.26</v>
+        <v>47.2</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>61.94</v>
+        <v>47.69</v>
       </c>
       <c r="J144" s="3" t="n">
-        <v>64.67</v>
+        <v>46.92</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -31193,7 +31099,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>南马托格罗索州</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -31202,22 +31108,22 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>44.35</v>
+        <v>60.13</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>45.17</v>
+        <v>60.87</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>47.96</v>
+        <v>63.28</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>51.78</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>56.47</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>59.69</v>
+        <v>71.92</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
@@ -31229,17 +31135,17 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>圣保罗州</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -31248,22 +31154,22 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="F146" s="4" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="G146" s="4" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="H146" s="4" t="n">
-        <v>36.23</v>
-      </c>
-      <c r="I146" s="4" t="n">
-        <v>36.23</v>
-      </c>
-      <c r="J146" s="4" t="n">
-        <v>36.77</v>
+        <v>51.61</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>56.06</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>66.87</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -31275,17 +31181,17 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>巴拉那州</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -31294,22 +31200,22 @@
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>64.44</v>
+        <v>55.23</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>65.25</v>
+        <v>58.58</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>60.83</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>66.45999999999999</v>
+        <v>62.76</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>66.14</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>66.81999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
@@ -31321,17 +31227,17 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -31340,22 +31246,22 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>42.04</v>
-      </c>
-      <c r="F148" s="4" t="n">
-        <v>37.61</v>
-      </c>
-      <c r="G148" s="4" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="H148" s="4" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="I148" s="4" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="J148" s="4" t="n">
-        <v>29.4</v>
+        <v>49.68</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="J148" s="3" t="n">
+        <v>61.78</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -31367,17 +31273,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -31386,22 +31292,22 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>48.77</v>
+        <v>52.69</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>47.73</v>
+        <v>54.44</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>45.89</v>
+        <v>56.69</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>44.6</v>
+        <v>59.26</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>43.7</v>
+        <v>61.94</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>43</v>
+        <v>64.67</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
@@ -31413,17 +31319,17 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -31432,22 +31338,22 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>45.28</v>
+        <v>44.35</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="G150" s="4" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="H150" s="4" t="n">
-        <v>35.58</v>
-      </c>
-      <c r="I150" s="4" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="J150" s="4" t="n">
-        <v>32.94</v>
+        <v>45.17</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>51.78</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="J150" s="3" t="n">
+        <v>59.69</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -31464,12 +31370,12 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -31478,22 +31384,22 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>50.47</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>48.77</v>
-      </c>
-      <c r="G151" s="3" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="H151" s="3" t="n">
-        <v>46.51</v>
-      </c>
-      <c r="I151" s="3" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="J151" s="3" t="n">
-        <v>47.41</v>
+        <v>40.39</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="I151" s="4" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="J151" s="4" t="n">
+        <v>36.77</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
@@ -31510,12 +31416,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -31524,22 +31430,22 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>48.6</v>
+        <v>64.44</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>48.02</v>
+        <v>65.25</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>47.35</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>46.83</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>46.58</v>
+        <v>66.14</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>45.91</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -31556,12 +31462,12 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -31570,22 +31476,22 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>63.84</v>
-      </c>
-      <c r="G153" s="3" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="H153" s="3" t="n">
-        <v>60.99</v>
-      </c>
-      <c r="I153" s="3" t="n">
-        <v>59.35</v>
-      </c>
-      <c r="J153" s="3" t="n">
-        <v>58.22</v>
+        <v>42.04</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>29.4</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
@@ -31602,12 +31508,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -31616,22 +31522,22 @@
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>45.11</v>
+        <v>48.77</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>43.32</v>
+        <v>47.73</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>42.48</v>
+        <v>45.89</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>42.88</v>
+        <v>44.6</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>44.32</v>
+        <v>43.7</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>48.75</v>
+        <v>43</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -31643,17 +31549,17 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -31662,22 +31568,22 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>51.73</v>
+        <v>45.28</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>53.01</v>
-      </c>
-      <c r="G155" s="3" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="H155" s="3" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="I155" s="3" t="n">
-        <v>61.03</v>
-      </c>
-      <c r="J155" s="3" t="n">
-        <v>57.81</v>
+        <v>42.43</v>
+      </c>
+      <c r="G155" s="4" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="H155" s="4" t="n">
+        <v>35.58</v>
+      </c>
+      <c r="I155" s="4" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="J155" s="4" t="n">
+        <v>32.94</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
@@ -31689,17 +31595,17 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -31708,22 +31614,22 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>54.47</v>
+        <v>50.47</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>54.6</v>
+        <v>48.77</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>54.98</v>
+        <v>47.07</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>55.08</v>
+        <v>46.51</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>54.7</v>
+        <v>46.45</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>51.45</v>
+        <v>47.41</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -31735,17 +31641,17 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -31754,22 +31660,22 @@
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>44.76</v>
+        <v>48.6</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>47.73</v>
+        <v>48.02</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>52.61</v>
+        <v>47.35</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>56.76</v>
+        <v>46.83</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>58.45</v>
+        <v>46.58</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>54.12</v>
+        <v>45.91</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
@@ -31781,17 +31687,17 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -31799,23 +31705,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E158" s="4" t="n">
-        <v>32.44</v>
-      </c>
-      <c r="F158" s="4" t="n">
-        <v>35.56</v>
+      <c r="E158" s="3" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>63.84</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>40.36</v>
+        <v>62.7</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>46.88</v>
+        <v>60.99</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>52.9</v>
+        <v>59.35</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>57.39</v>
+        <v>58.22</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -31827,17 +31733,17 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -31846,22 +31752,22 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>44.44</v>
+        <v>45.11</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>46.66</v>
+        <v>43.32</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>49.63</v>
+        <v>42.48</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>52.13</v>
+        <v>42.88</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>53.19</v>
+        <v>44.32</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>50.33</v>
+        <v>48.75</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
@@ -31883,7 +31789,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -31891,23 +31797,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E160" s="4" t="n">
-        <v>28.87</v>
-      </c>
-      <c r="F160" s="4" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="G160" s="4" t="n">
-        <v>38.46</v>
+      <c r="E160" s="3" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>56.11</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>43.24</v>
+        <v>59.37</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>46.77</v>
+        <v>61.03</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>46.52</v>
+        <v>57.81</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -31929,7 +31835,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -31938,22 +31844,22 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>51.87</v>
+        <v>54.47</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>50.59</v>
+        <v>54.6</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>49.32</v>
+        <v>54.98</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>47.02</v>
+        <v>55.08</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>45.05</v>
+        <v>54.7</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>42.17</v>
+        <v>51.45</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
@@ -31975,7 +31881,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -31983,23 +31889,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E162" s="4" t="n">
-        <v>38.03</v>
+      <c r="E162" s="3" t="n">
+        <v>44.76</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>40.68</v>
+        <v>47.73</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>43.63</v>
+        <v>52.61</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>45.89</v>
+        <v>56.76</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>47.71</v>
+        <v>58.45</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>47.91</v>
+        <v>54.12</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -32021,7 +31927,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -32029,23 +31935,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E163" s="3" t="n">
-        <v>40.65</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>41.2</v>
+      <c r="E163" s="4" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>35.56</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>42.75</v>
+        <v>40.36</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>46.71</v>
+        <v>46.88</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>50.24</v>
+        <v>52.9</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>50.52</v>
+        <v>57.39</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
@@ -32057,17 +31963,17 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -32076,22 +31982,22 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>53.33</v>
+        <v>44.44</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>50.87</v>
+        <v>46.66</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>49.44</v>
+        <v>49.63</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>49.41</v>
+        <v>52.13</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>49.56</v>
+        <v>53.19</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>50.19</v>
+        <v>50.33</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -32103,17 +32009,17 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -32122,22 +32028,22 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>52.33</v>
+        <v>51.87</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>50.89</v>
+        <v>50.59</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>50.68</v>
+        <v>49.32</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>51.92</v>
+        <v>47.02</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>53.51</v>
+        <v>45.05</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>55.62</v>
+        <v>42.17</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
@@ -32149,17 +32055,17 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -32167,23 +32073,23 @@
           <t>玉米</t>
         </is>
       </c>
-      <c r="E166" s="3" t="n">
-        <v>60.77</v>
+      <c r="E166" s="4" t="n">
+        <v>38.03</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>59.81</v>
+        <v>40.68</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>59.92</v>
+        <v>43.63</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>60.88</v>
+        <v>45.89</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>63.04</v>
+        <v>47.71</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>66.44</v>
+        <v>47.91</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -32195,41 +32101,41 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>甘蔗</t>
+          <t>玉米</t>
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>59.49</v>
+        <v>40.65</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>58.29</v>
+        <v>41.2</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>56.22</v>
+        <v>42.75</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>53.23</v>
+        <v>46.71</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>49.98</v>
+        <v>50.24</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>47.76</v>
+        <v>50.52</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
@@ -32241,41 +32147,41 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>甘蔗</t>
+          <t>玉米</t>
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>49.25</v>
+        <v>53.33</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>48.23</v>
+        <v>50.87</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>47.49</v>
+        <v>49.44</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>48.06</v>
+        <v>49.41</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>49.71</v>
+        <v>49.56</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>51.68</v>
+        <v>50.19</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -32287,41 +32193,41 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>甘蔗</t>
+          <t>玉米</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>60.85</v>
+        <v>52.33</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>61.31</v>
+        <v>50.89</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>60.68</v>
+        <v>50.68</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>59.71</v>
+        <v>51.92</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>57.9</v>
+        <v>53.51</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>56.69</v>
+        <v>55.62</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
@@ -32333,41 +32239,41 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>甘蔗</t>
+          <t>玉米</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>67.48</v>
+        <v>55.82</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>67.37</v>
+        <v>54.25</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>53.59</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>63.51</v>
+        <v>55.27</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>59.61</v>
+        <v>57.5</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>57.14</v>
+        <v>59.53</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -32379,41 +32285,41 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>北方邦</t>
+          <t>Santiago del Estero</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>甘蔗</t>
+          <t>玉米</t>
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>73.64</v>
+        <v>60.77</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>59.81</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>62.11</v>
+        <v>59.92</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>56.23</v>
+        <v>60.88</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>49.23</v>
+        <v>63.04</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>42.05</v>
+        <v>66.44</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
@@ -32425,17 +32331,17 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>卡纳塔克邦</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -32444,22 +32350,22 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>68.56</v>
+        <v>49.25</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>64.5</v>
+        <v>48.23</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>59.21</v>
+        <v>47.49</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>55.77</v>
+        <v>48.06</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>52.98</v>
+        <v>49.71</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>50.59</v>
+        <v>51.68</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -32471,17 +32377,17 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>安得拉邦</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -32490,22 +32396,22 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>54.84</v>
+        <v>60.85</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>51.4</v>
+        <v>61.31</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>48.09</v>
+        <v>60.68</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>44.78</v>
+        <v>59.71</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>42.48</v>
+        <v>57.9</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>40.39</v>
+        <v>56.69</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
@@ -32517,17 +32423,17 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>泰米尔纳德邦</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -32536,22 +32442,22 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>69.55</v>
+        <v>67.48</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>68.08</v>
+        <v>67.37</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>64.37</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>62.05</v>
+        <v>63.51</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>60.31</v>
+        <v>59.61</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>57.86</v>
+        <v>57.14</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -32573,7 +32479,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>马哈拉施特拉邦</t>
+          <t>北方邦</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -32582,22 +32488,22 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>60.77</v>
+        <v>73.64</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>55.13</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>49.06</v>
+        <v>62.11</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>44.63</v>
+        <v>56.23</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>41.72</v>
-      </c>
-      <c r="J175" s="4" t="n">
-        <v>39.59</v>
+        <v>49.23</v>
+      </c>
+      <c r="J175" s="3" t="n">
+        <v>42.05</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
@@ -32609,17 +32515,17 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>南马托格罗索州</t>
+          <t>卡纳塔克邦</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -32628,22 +32534,22 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>63.91</v>
+        <v>68.56</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>64.7</v>
+        <v>64.5</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>66.93000000000001</v>
+        <v>59.21</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>69.81</v>
+        <v>55.77</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>72.27</v>
+        <v>52.98</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>73.98999999999999</v>
+        <v>50.59</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -32655,17 +32561,17 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>圣保罗州</t>
+          <t>古吉拉特邦</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -32674,22 +32580,22 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>51.3</v>
+        <v>58.37</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>55.63</v>
+        <v>53.4</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>57.99</v>
+        <v>48.24</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="I177" s="3" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="J177" s="3" t="n">
-        <v>66.73</v>
+        <v>43.19</v>
+      </c>
+      <c r="I177" s="4" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="J177" s="4" t="n">
+        <v>35.81</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
@@ -32701,17 +32607,17 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>巴拉那州</t>
+          <t>安得拉邦</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -32720,22 +32626,22 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>57.4</v>
+        <v>54.84</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>60.53</v>
+        <v>51.4</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>62.57</v>
+        <v>48.09</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>64.68000000000001</v>
+        <v>44.78</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>67.05</v>
+        <v>42.48</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>68.8</v>
+        <v>40.39</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -32747,17 +32653,17 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>泰米尔纳德邦</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -32766,22 +32672,22 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>51.01</v>
+        <v>69.55</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>51.44</v>
+        <v>68.08</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>52.42</v>
+        <v>64.37</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>54.9</v>
+        <v>62.05</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>58.32</v>
+        <v>60.31</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>62.66</v>
+        <v>57.86</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
@@ -32793,17 +32699,17 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>马哈拉施特拉邦</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -32812,22 +32718,22 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>53.12</v>
+        <v>60.77</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>54.85</v>
+        <v>55.13</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>57.05</v>
+        <v>49.06</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>59.61</v>
+        <v>44.63</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>62.24</v>
-      </c>
-      <c r="J180" s="3" t="n">
-        <v>64.97</v>
+        <v>41.72</v>
+      </c>
+      <c r="J180" s="4" t="n">
+        <v>39.59</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -32849,7 +32755,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>南马托格罗索州</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -32858,22 +32764,22 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>47.67</v>
+        <v>63.91</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>48.87</v>
+        <v>64.7</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>51.62</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>55.5</v>
+        <v>69.81</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>60.13</v>
+        <v>72.27</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>63.47</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
@@ -32885,41 +32791,41 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>圣保罗州</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>菜籽</t>
+          <t>甘蔗</t>
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>61.61</v>
+        <v>51.3</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>60.29</v>
+        <v>55.63</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>58.03</v>
+        <v>57.99</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>54.87</v>
+        <v>61.21</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>51.47</v>
+        <v>63.78</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>49.05</v>
+        <v>66.73</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -32931,41 +32837,41 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>巴拉那州</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>菜籽</t>
+          <t>甘蔗</t>
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>61.54</v>
+        <v>57.4</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>61.72</v>
+        <v>60.53</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>60.89</v>
+        <v>62.57</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>59.1</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>56.97</v>
+        <v>67.05</v>
       </c>
       <c r="J183" s="3" t="n">
-        <v>55.96</v>
+        <v>68.8</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
@@ -32977,41 +32883,41 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>戈亚斯州</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>菜籽</t>
+          <t>甘蔗</t>
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>59</v>
+        <v>51.01</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>60.11</v>
+        <v>51.44</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>60.05</v>
+        <v>52.42</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>56.96</v>
+        <v>54.9</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>52.66</v>
+        <v>58.32</v>
       </c>
       <c r="J184" s="3" t="n">
-        <v>46.66</v>
+        <v>62.66</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -33023,41 +32929,41 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>菜籽</t>
+          <t>甘蔗</t>
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>51.02</v>
+        <v>53.12</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>49.91</v>
+        <v>54.85</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>48.12</v>
+        <v>57.05</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>42.76</v>
-      </c>
-      <c r="I185" s="4" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="J185" s="4" t="n">
-        <v>31.82</v>
+        <v>59.61</v>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>64.97</v>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
@@ -33069,41 +32975,41 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>菜籽</t>
+          <t>甘蔗</t>
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>61.46</v>
+        <v>47.67</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>60.57</v>
+        <v>48.87</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>59.15</v>
+        <v>51.62</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>57.84</v>
+        <v>55.5</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>56.06</v>
+        <v>60.13</v>
       </c>
       <c r="J186" s="3" t="n">
-        <v>55.13</v>
+        <v>63.47</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -33125,7 +33031,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -33134,22 +33040,22 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>63.82</v>
+        <v>61.61</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>62.07</v>
+        <v>60.29</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>60.73</v>
+        <v>58.03</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>58.84</v>
+        <v>54.87</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>56.9</v>
+        <v>51.47</v>
       </c>
       <c r="J187" s="3" t="n">
-        <v>54.05</v>
+        <v>49.05</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
@@ -33171,7 +33077,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -33180,22 +33086,22 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>60.6</v>
+        <v>61.54</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>61.21</v>
+        <v>61.72</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>60.53</v>
+        <v>60.89</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>59.54</v>
+        <v>59.1</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>56.48</v>
+        <v>56.97</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>55.16</v>
+        <v>55.96</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -33217,7 +33123,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -33226,22 +33132,22 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>59</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>64.59</v>
+        <v>60.11</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>63.29</v>
+        <v>60.05</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>60.94</v>
+        <v>56.96</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>57.18</v>
+        <v>52.66</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>54.87</v>
+        <v>46.66</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
@@ -33263,7 +33169,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -33272,22 +33178,22 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>62.95</v>
+        <v>51.02</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>63.62</v>
+        <v>49.91</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>63.9</v>
+        <v>48.12</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>62.82</v>
-      </c>
-      <c r="I190" s="3" t="n">
-        <v>60.83</v>
-      </c>
-      <c r="J190" s="3" t="n">
-        <v>59.7</v>
+        <v>42.76</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="J190" s="4" t="n">
+        <v>31.82</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -33299,17 +33205,17 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Alberta</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -33318,22 +33224,22 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>42.11</v>
+        <v>61.46</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>44.45</v>
+        <v>60.57</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>46.37</v>
+        <v>59.15</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>49.01</v>
+        <v>57.84</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>51.35</v>
+        <v>56.06</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>51.86</v>
+        <v>55.13</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
@@ -33345,17 +33251,17 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -33364,22 +33270,22 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>43.8</v>
+        <v>63.82</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>44.82</v>
+        <v>62.07</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>47.29</v>
+        <v>60.73</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>49.14</v>
+        <v>58.84</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>49.74</v>
+        <v>56.9</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>47.99</v>
+        <v>54.05</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -33391,17 +33297,17 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Saskatchewan</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -33410,22 +33316,22 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>47.66</v>
+        <v>60.6</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>48.86</v>
+        <v>61.21</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>50.98</v>
+        <v>60.53</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>53.95</v>
+        <v>59.54</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>55.87</v>
+        <v>56.48</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>56</v>
+        <v>55.16</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
@@ -33437,17 +33343,17 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -33456,22 +33362,22 @@
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>56.26</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>52.02</v>
+        <v>64.59</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>48.59</v>
+        <v>63.29</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>44.89</v>
-      </c>
-      <c r="I194" s="4" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="J194" s="4" t="n">
-        <v>34.39</v>
+        <v>60.94</v>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>54.87</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -33483,17 +33389,17 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -33502,22 +33408,22 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>62.45</v>
+        <v>62.95</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>56.63</v>
+        <v>63.62</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>51.81</v>
+        <v>63.9</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>46.57</v>
+        <v>62.82</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="J195" s="4" t="n">
-        <v>35.56</v>
+        <v>60.83</v>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>59.7</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
@@ -33529,17 +33435,17 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -33548,22 +33454,22 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>64.75</v>
+        <v>42.11</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>62.58</v>
+        <v>44.45</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>61.23</v>
+        <v>46.37</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>58.27</v>
+        <v>49.01</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>54.06</v>
+        <v>51.35</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>50.22</v>
+        <v>51.86</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -33575,17 +33481,17 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Manitoba</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -33594,22 +33500,22 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>73.48999999999999</v>
+        <v>43.8</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>67.48</v>
+        <v>44.82</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>61.73</v>
+        <v>47.29</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>55.63</v>
+        <v>49.14</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>48.4</v>
+        <v>49.74</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>41.16</v>
+        <v>47.99</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
@@ -33621,17 +33527,17 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Saskatchewan</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -33640,22 +33546,22 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>65.53</v>
+        <v>47.66</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>57.54</v>
+        <v>48.86</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>52.27</v>
+        <v>50.98</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>47.8</v>
+        <v>53.95</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>45.11</v>
+        <v>55.87</v>
       </c>
       <c r="J198" s="3" t="n">
-        <v>43.22</v>
+        <v>56</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -33667,17 +33573,17 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Czech</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -33686,22 +33592,22 @@
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>45.02</v>
+        <v>56.26</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>44.75</v>
+        <v>52.02</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>43.96</v>
+        <v>48.59</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>43.05</v>
-      </c>
-      <c r="I199" s="3" t="n">
-        <v>42.74</v>
-      </c>
-      <c r="J199" s="3" t="n">
-        <v>42.51</v>
+        <v>44.89</v>
+      </c>
+      <c r="I199" s="4" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="J199" s="4" t="n">
+        <v>34.39</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
@@ -33713,17 +33619,17 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -33732,22 +33638,22 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>54.82</v>
+        <v>62.45</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>56.22</v>
+        <v>56.63</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>54.75</v>
+        <v>51.81</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>53</v>
+        <v>46.57</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>52.14</v>
-      </c>
-      <c r="J200" s="3" t="n">
-        <v>52.37</v>
+        <v>40.89</v>
+      </c>
+      <c r="J200" s="4" t="n">
+        <v>35.56</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -33759,17 +33665,17 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -33778,22 +33684,22 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>42.82</v>
-      </c>
-      <c r="F201" s="4" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="G201" s="4" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="H201" s="4" t="n">
-        <v>32.52</v>
-      </c>
-      <c r="I201" s="4" t="n">
-        <v>30.51</v>
-      </c>
-      <c r="J201" s="4" t="n">
-        <v>30.28</v>
+        <v>64.75</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="J201" s="3" t="n">
+        <v>50.22</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
@@ -33805,17 +33711,17 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -33824,22 +33730,22 @@
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>50.09</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>48.81</v>
+        <v>67.48</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>46.75</v>
+        <v>61.73</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>45.31</v>
+        <v>55.63</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>44.34</v>
+        <v>48.4</v>
       </c>
       <c r="J202" s="3" t="n">
-        <v>43.59</v>
+        <v>41.16</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -33851,17 +33757,17 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -33870,22 +33776,22 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>45.57</v>
+        <v>65.53</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="G203" s="4" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="H203" s="4" t="n">
-        <v>35.74</v>
-      </c>
-      <c r="I203" s="4" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="J203" s="4" t="n">
-        <v>33</v>
+        <v>57.54</v>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>52.27</v>
+      </c>
+      <c r="H203" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I203" s="3" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="J203" s="3" t="n">
+        <v>43.22</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
@@ -33902,12 +33808,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -33916,22 +33822,22 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>56.26</v>
+        <v>54.82</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>56.45</v>
+        <v>56.22</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>57.98</v>
+        <v>54.75</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>58.92</v>
+        <v>53</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>59.05</v>
+        <v>52.14</v>
       </c>
       <c r="J204" s="3" t="n">
-        <v>58.31</v>
+        <v>52.37</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -33948,12 +33854,12 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -33962,22 +33868,22 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="F205" s="3" t="n">
-        <v>48.67</v>
-      </c>
-      <c r="G205" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H205" s="3" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I205" s="3" t="n">
-        <v>47.04</v>
-      </c>
-      <c r="J205" s="3" t="n">
-        <v>46.36</v>
+        <v>42.82</v>
+      </c>
+      <c r="F205" s="4" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="G205" s="4" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="H205" s="4" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="I205" s="4" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="J205" s="4" t="n">
+        <v>30.28</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
@@ -33994,12 +33900,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -34008,22 +33914,22 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>64.23999999999999</v>
+        <v>50.09</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>63.36</v>
+        <v>48.81</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>62.19</v>
+        <v>46.75</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>60.52</v>
+        <v>45.31</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>58.93</v>
+        <v>44.34</v>
       </c>
       <c r="J206" s="3" t="n">
-        <v>57.85</v>
+        <v>43.59</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -34035,17 +33941,17 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>New South Wales</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -34053,23 +33959,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E207" s="4" t="n">
-        <v>38.56</v>
+      <c r="E207" s="3" t="n">
+        <v>45.57</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>41.48</v>
-      </c>
-      <c r="G207" s="3" t="n">
-        <v>44.25</v>
-      </c>
-      <c r="H207" s="3" t="n">
-        <v>47.11</v>
-      </c>
-      <c r="I207" s="3" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="J207" s="3" t="n">
-        <v>48.11</v>
+        <v>42.66</v>
+      </c>
+      <c r="G207" s="4" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="H207" s="4" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="I207" s="4" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="J207" s="4" t="n">
+        <v>33</v>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
@@ -34081,17 +33987,17 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>South Australia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -34100,22 +34006,22 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>54.77</v>
+        <v>56.26</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>56.79</v>
+        <v>56.45</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>59.12</v>
+        <v>57.98</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>61.29</v>
+        <v>58.92</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>62.75</v>
+        <v>59.05</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>61.53</v>
+        <v>58.31</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -34127,17 +34033,17 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>澳洲</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -34146,22 +34052,22 @@
         </is>
       </c>
       <c r="E209" s="3" t="n">
-        <v>47.44</v>
+        <v>49.2</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>47.68</v>
+        <v>48.67</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>48.52</v>
+        <v>48</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>49.59</v>
+        <v>47.42</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>49.77</v>
+        <v>47.04</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>48.78</v>
+        <v>46.36</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
@@ -34183,7 +34089,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Western Australia</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -34191,23 +34097,23 @@
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E210" s="3" t="n">
-        <v>43.36</v>
+      <c r="E210" s="4" t="n">
+        <v>38.56</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>44.89</v>
+        <v>41.48</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>47.45</v>
+        <v>44.25</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>48.56</v>
+        <v>47.11</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>48.08</v>
+        <v>49.06</v>
       </c>
       <c r="J210" s="3" t="n">
-        <v>48.34</v>
+        <v>48.11</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -34219,41 +34125,41 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Cherkaska</t>
+          <t>South Australia</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>葵籽</t>
+          <t>菜籽</t>
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>42.55</v>
+        <v>54.77</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>43.93</v>
+        <v>56.79</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>46.4</v>
+        <v>59.12</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>50.05</v>
+        <v>61.29</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>53.45</v>
+        <v>62.75</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>54.04</v>
+        <v>61.53</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
@@ -34265,41 +34171,41 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Chivnivska</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>葵籽</t>
+          <t>菜籽</t>
         </is>
       </c>
       <c r="E212" s="3" t="n">
-        <v>51.52</v>
+        <v>47.44</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>51.77</v>
+        <v>47.68</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>51.2</v>
+        <v>48.52</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>49.87</v>
+        <v>49.59</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>48.11</v>
+        <v>49.77</v>
       </c>
       <c r="J212" s="3" t="n">
-        <v>46.16</v>
+        <v>48.78</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -34311,41 +34217,41 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>乌克兰</t>
+          <t>澳洲</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Dnipropetrovska</t>
+          <t>Western Australia</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>葵籽</t>
+          <t>菜籽</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>55.93</v>
+        <v>43.36</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>58.14</v>
+        <v>44.89</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>58.26</v>
+        <v>47.45</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>58.44</v>
+        <v>48.56</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>58.5</v>
+        <v>48.08</v>
       </c>
       <c r="J213" s="3" t="n">
-        <v>57.74</v>
+        <v>48.34</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
@@ -34367,7 +34273,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Donetsk</t>
+          <t>Cherkaska</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -34376,22 +34282,22 @@
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>62.34</v>
+        <v>42.55</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>62.34</v>
+        <v>43.93</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>61.06</v>
+        <v>46.4</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>60.76</v>
+        <v>50.05</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>60.95</v>
+        <v>53.45</v>
       </c>
       <c r="J214" s="3" t="n">
-        <v>61.44</v>
+        <v>54.04</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -34413,7 +34319,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Kharkivska</t>
+          <t>Chivnivska</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -34422,22 +34328,22 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>56.87</v>
+        <v>51.52</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>58.88</v>
+        <v>51.77</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>60.14</v>
+        <v>51.2</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>61.46</v>
+        <v>49.87</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>62.01</v>
+        <v>48.11</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>62.79</v>
+        <v>46.16</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
@@ -34459,7 +34365,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Khersonska</t>
+          <t>Dnipropetrovska</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -34468,22 +34374,22 @@
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>60.86</v>
+        <v>55.93</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>57.68</v>
+        <v>58.14</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>53.27</v>
+        <v>58.26</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>48.92</v>
+        <v>58.44</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>46.47</v>
+        <v>58.5</v>
       </c>
       <c r="J216" s="3" t="n">
-        <v>44.95</v>
+        <v>57.74</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -34505,7 +34411,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Kirovogradska</t>
+          <t>Donetsk</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -34514,22 +34420,22 @@
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>50.64</v>
+        <v>62.34</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>52.06</v>
+        <v>62.34</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>52.77</v>
+        <v>61.06</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>54.55</v>
+        <v>60.76</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>56.44</v>
+        <v>60.95</v>
       </c>
       <c r="J217" s="3" t="n">
-        <v>56.38</v>
+        <v>61.44</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
@@ -34551,7 +34457,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Kirovohradska</t>
+          <t>Kharkivska</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -34560,22 +34466,22 @@
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>50.64</v>
+        <v>56.87</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>52.06</v>
+        <v>58.88</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>52.77</v>
+        <v>60.14</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>54.55</v>
+        <v>61.46</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>56.44</v>
+        <v>62.01</v>
       </c>
       <c r="J218" s="3" t="n">
-        <v>56.38</v>
+        <v>62.79</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -34597,7 +34503,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Luhanska</t>
+          <t>Khersonska</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -34606,22 +34512,22 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>57.9</v>
+        <v>60.86</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>56.31</v>
+        <v>57.68</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>55.8</v>
+        <v>53.27</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>57.05</v>
+        <v>48.92</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>57.4</v>
+        <v>46.47</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>58.8</v>
+        <v>44.95</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
@@ -34643,7 +34549,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Odeska</t>
+          <t>Kirovogradska</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -34652,22 +34558,22 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>75.62</v>
+        <v>50.64</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>77.18000000000001</v>
+        <v>52.06</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>77.88</v>
+        <v>52.77</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>76.45999999999999</v>
+        <v>54.55</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>73.88</v>
+        <v>56.44</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>70.58</v>
+        <v>56.38</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -34689,7 +34595,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Poltavska</t>
+          <t>Luhanska</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -34698,22 +34604,22 @@
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>40.98</v>
+        <v>57.9</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>43.15</v>
+        <v>56.31</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>45.71</v>
+        <v>55.8</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>48.58</v>
+        <v>57.05</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>51.3</v>
+        <v>57.4</v>
       </c>
       <c r="J221" s="3" t="n">
-        <v>52.76</v>
+        <v>58.8</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
@@ -34735,7 +34641,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Sumy</t>
+          <t>Poltavska</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -34744,22 +34650,22 @@
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>50.26</v>
+        <v>40.98</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>51.65</v>
+        <v>43.15</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>53.49</v>
+        <v>45.71</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>55.67</v>
+        <v>48.58</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>58.91</v>
+        <v>51.3</v>
       </c>
       <c r="J222" s="3" t="n">
-        <v>61.34</v>
+        <v>52.76</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -34781,7 +34687,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Vinnitsa</t>
+          <t>Sumy</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -34790,22 +34696,22 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>51.03</v>
+        <v>50.26</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>51.98</v>
+        <v>51.65</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>53.56</v>
+        <v>53.49</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>55.8</v>
+        <v>55.67</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>57.71</v>
+        <v>58.91</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>57.68</v>
+        <v>61.34</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
@@ -34827,7 +34733,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Zaporizka</t>
+          <t>Vinnitsa</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -34836,22 +34742,22 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>63.47</v>
+        <v>51.03</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>64.09</v>
+        <v>51.98</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>62.83</v>
+        <v>53.56</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>61.43</v>
+        <v>55.8</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>59.64</v>
+        <v>57.71</v>
       </c>
       <c r="J224" s="3" t="n">
-        <v>57.86</v>
+        <v>57.68</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -34863,17 +34769,17 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>俄罗斯</t>
+          <t>乌克兰</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>中央</t>
+          <t>Zaporizka</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -34882,22 +34788,22 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>53.16</v>
+        <v>63.47</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>54.15</v>
+        <v>64.09</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>56.52</v>
+        <v>62.83</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>59.69</v>
+        <v>61.43</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>62.74</v>
+        <v>59.64</v>
       </c>
       <c r="J225" s="3" t="n">
-        <v>65.06</v>
+        <v>57.86</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
@@ -34919,7 +34825,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>伏尔加</t>
+          <t>中央</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -34928,22 +34834,22 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>60.23</v>
+        <v>53.11</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>63.64</v>
+        <v>54.01</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>67.81</v>
+        <v>56.48</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>71.23</v>
+        <v>59.76</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>73.19</v>
+        <v>62.9</v>
       </c>
       <c r="J226" s="3" t="n">
-        <v>73.91</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -34965,7 +34871,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>北高加索</t>
+          <t>伏尔加</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -34974,22 +34880,22 @@
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>71.8</v>
+        <v>59.12</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>72.03</v>
+        <v>62.12</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>70.81999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>69.15000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>68.27</v>
+        <v>72</v>
       </c>
       <c r="J227" s="3" t="n">
-        <v>70.58</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
@@ -35011,7 +34917,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>南部</t>
+          <t>北高加索</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -35020,22 +34926,22 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>65.20999999999999</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>64.73</v>
+        <v>71.08</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>64.98</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>65.14</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>65.62</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="J228" s="3" t="n">
-        <v>67.25</v>
+        <v>69.97</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -35047,17 +34953,17 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>欧盟</t>
+          <t>俄罗斯</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>南部</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -35066,22 +34972,22 @@
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>64.16</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>64.92</v>
+        <v>64.73</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>65.73</v>
+        <v>64.98</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>66.09</v>
+        <v>65.14</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>65.79000000000001</v>
+        <v>65.62</v>
       </c>
       <c r="J229" s="3" t="n">
-        <v>66.48999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
@@ -35098,12 +35004,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -35112,22 +35018,22 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>42.27</v>
-      </c>
-      <c r="F230" s="4" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="G230" s="4" t="n">
-        <v>34.36</v>
-      </c>
-      <c r="H230" s="4" t="n">
-        <v>31.53</v>
-      </c>
-      <c r="I230" s="4" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="J230" s="4" t="n">
-        <v>29.35</v>
+        <v>64.16</v>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>65.73</v>
+      </c>
+      <c r="H230" s="3" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="I230" s="3" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="J230" s="3" t="n">
+        <v>66.48999999999999</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -35144,12 +35050,12 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -35158,22 +35064,22 @@
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>45.27</v>
-      </c>
-      <c r="F231" s="3" t="n">
-        <v>42.38</v>
+        <v>42.27</v>
+      </c>
+      <c r="F231" s="4" t="n">
+        <v>37.86</v>
       </c>
       <c r="G231" s="4" t="n">
-        <v>38.95</v>
+        <v>34.36</v>
       </c>
       <c r="H231" s="4" t="n">
-        <v>35.45</v>
+        <v>31.53</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>33.63</v>
+        <v>29.5</v>
       </c>
       <c r="J231" s="4" t="n">
-        <v>32.76</v>
+        <v>29.35</v>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
@@ -35190,12 +35096,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -35204,22 +35110,22 @@
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>64.56</v>
+        <v>45.27</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="G232" s="3" t="n">
-        <v>62.59</v>
-      </c>
-      <c r="H232" s="3" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="I232" s="3" t="n">
-        <v>59.27</v>
-      </c>
-      <c r="J232" s="3" t="n">
-        <v>58.16</v>
+        <v>42.38</v>
+      </c>
+      <c r="G232" s="4" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="H232" s="4" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="I232" s="4" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="J232" s="4" t="n">
+        <v>32.76</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -35236,12 +35142,12 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -35250,22 +35156,22 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>44.92</v>
+        <v>64.56</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>42.97</v>
+        <v>63.73</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>42.03</v>
+        <v>62.59</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>42.4</v>
+        <v>60.9</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>43.84</v>
+        <v>59.27</v>
       </c>
       <c r="J233" s="3" t="n">
-        <v>48.54</v>
+        <v>58.16</v>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
@@ -35277,17 +35183,17 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>欧盟</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -35296,22 +35202,22 @@
         </is>
       </c>
       <c r="E234" s="3" t="n">
-        <v>53.5</v>
+        <v>44.92</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>50.98</v>
+        <v>42.97</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>49.51</v>
+        <v>42.03</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>49.46</v>
+        <v>42.4</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>49.6</v>
+        <v>43.84</v>
       </c>
       <c r="J234" s="3" t="n">
-        <v>50.22</v>
+        <v>48.54</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -35333,7 +35239,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -35342,22 +35248,22 @@
         </is>
       </c>
       <c r="E235" s="3" t="n">
-        <v>49.21</v>
+        <v>53.5</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>47.96</v>
+        <v>50.98</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>48.33</v>
+        <v>49.51</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>49.53</v>
+        <v>49.46</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>51.3</v>
+        <v>49.6</v>
       </c>
       <c r="J235" s="3" t="n">
-        <v>51.79</v>
+        <v>50.22</v>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
@@ -35379,7 +35285,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>La Pampa</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -35388,22 +35294,22 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>56.02</v>
+        <v>49.21</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>54.4</v>
+        <v>47.96</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>53.71</v>
+        <v>48.33</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>55.39</v>
+        <v>49.53</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>57.65</v>
+        <v>51.3</v>
       </c>
       <c r="J236" s="3" t="n">
-        <v>59.7</v>
+        <v>51.79</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -35415,41 +35321,41 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>高粱</t>
+          <t>葵籽</t>
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>42.23</v>
+        <v>56.02</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>43.82</v>
+        <v>54.4</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>43.62</v>
+        <v>53.71</v>
       </c>
       <c r="H237" s="3" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="I237" s="4" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="J237" s="4" t="n">
-        <v>27.56</v>
+        <v>55.39</v>
+      </c>
+      <c r="I237" s="3" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="J237" s="3" t="n">
+        <v>59.7</v>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
@@ -35471,7 +35377,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Bauchi</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -35479,23 +35385,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E238" s="4" t="n">
-        <v>33.47</v>
-      </c>
-      <c r="F238" s="4" t="n">
-        <v>36.12</v>
-      </c>
-      <c r="G238" s="4" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="H238" s="4" t="n">
-        <v>34.2</v>
+      <c r="E238" s="3" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="G238" s="3" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>40.29</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>29.51</v>
+        <v>34.37</v>
       </c>
       <c r="J238" s="4" t="n">
-        <v>23.49</v>
+        <v>27.56</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -35517,7 +35423,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Bauchi</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -35525,23 +35431,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E239" s="3" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="F239" s="3" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="G239" s="3" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="H239" s="3" t="n">
-        <v>63.02</v>
-      </c>
-      <c r="I239" s="3" t="n">
-        <v>61.49</v>
-      </c>
-      <c r="J239" s="3" t="n">
-        <v>56.35</v>
+      <c r="E239" s="4" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="F239" s="4" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="G239" s="4" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="H239" s="4" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I239" s="4" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="J239" s="4" t="n">
+        <v>23.49</v>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
@@ -35563,7 +35469,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Gombe</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -35571,23 +35477,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E240" s="4" t="n">
-        <v>39.24</v>
+      <c r="E240" s="3" t="n">
+        <v>52.07</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>40.05</v>
+        <v>56.9</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>40.47</v>
-      </c>
-      <c r="H240" s="4" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="I240" s="4" t="n">
-        <v>35.13</v>
-      </c>
-      <c r="J240" s="4" t="n">
-        <v>28.87</v>
+        <v>61.46</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>63.02</v>
+      </c>
+      <c r="I240" s="3" t="n">
+        <v>61.49</v>
+      </c>
+      <c r="J240" s="3" t="n">
+        <v>56.35</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -35609,7 +35515,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Jigawa</t>
+          <t>Gombe</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -35617,23 +35523,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E241" s="3" t="n">
-        <v>43.85</v>
+      <c r="E241" s="4" t="n">
+        <v>39.24</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>44.53</v>
+        <v>40.05</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>44.65</v>
-      </c>
-      <c r="H241" s="3" t="n">
-        <v>42.62</v>
+        <v>40.47</v>
+      </c>
+      <c r="H241" s="4" t="n">
+        <v>38.74</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>39.85</v>
+        <v>35.13</v>
       </c>
       <c r="J241" s="4" t="n">
-        <v>34.12</v>
+        <v>28.87</v>
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
@@ -35655,7 +35561,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Kaduna</t>
+          <t>Jigawa</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -35663,23 +35569,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E242" s="4" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="F242" s="4" t="n">
-        <v>33.79</v>
-      </c>
-      <c r="G242" s="4" t="n">
-        <v>32.36</v>
-      </c>
-      <c r="H242" s="4" t="n">
-        <v>29.52</v>
+      <c r="E242" s="3" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>42.62</v>
       </c>
       <c r="I242" s="4" t="n">
-        <v>25.87</v>
+        <v>39.85</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>24.33</v>
+        <v>34.12</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -35701,7 +35607,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Kano</t>
+          <t>Kaduna</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -35710,22 +35616,22 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>35.9</v>
+        <v>33.45</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>37.45</v>
+        <v>33.79</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>38.16</v>
+        <v>32.36</v>
       </c>
       <c r="H243" s="4" t="n">
-        <v>36.55</v>
+        <v>29.52</v>
       </c>
       <c r="I243" s="4" t="n">
-        <v>32.9</v>
+        <v>25.87</v>
       </c>
       <c r="J243" s="4" t="n">
-        <v>27.56</v>
+        <v>24.33</v>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
@@ -35747,7 +35653,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Kano</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -35755,23 +35661,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E244" s="3" t="n">
-        <v>46.14</v>
-      </c>
-      <c r="F244" s="3" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="G244" s="3" t="n">
-        <v>49.35</v>
-      </c>
-      <c r="H244" s="3" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="I244" s="3" t="n">
-        <v>45.98</v>
-      </c>
-      <c r="J244" s="3" t="n">
-        <v>41.99</v>
+      <c r="E244" s="4" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="F244" s="4" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="G244" s="4" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="H244" s="4" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="I244" s="4" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="J244" s="4" t="n">
+        <v>27.56</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -35793,7 +35699,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Kebbi</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -35801,23 +35707,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E245" s="4" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="F245" s="4" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="G245" s="4" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="H245" s="4" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="I245" s="4" t="n">
-        <v>32.72</v>
-      </c>
-      <c r="J245" s="4" t="n">
-        <v>27.93</v>
+      <c r="E245" s="3" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="G245" s="3" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="H245" s="3" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="I245" s="3" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="J245" s="3" t="n">
+        <v>41.99</v>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
@@ -35839,7 +35745,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Kebbi</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -35848,22 +35754,22 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>26.26</v>
+        <v>35.33</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>29.18</v>
+        <v>37.1</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>29.86</v>
+        <v>37.48</v>
       </c>
       <c r="H246" s="4" t="n">
-        <v>28.59</v>
+        <v>35.83</v>
       </c>
       <c r="I246" s="4" t="n">
-        <v>26.52</v>
+        <v>32.72</v>
       </c>
       <c r="J246" s="4" t="n">
-        <v>24.26</v>
+        <v>27.93</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -35885,7 +35791,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Plateau</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -35893,23 +35799,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E247" s="3" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="F247" s="3" t="n">
-        <v>47.26</v>
-      </c>
-      <c r="G247" s="3" t="n">
-        <v>46.23</v>
-      </c>
-      <c r="H247" s="3" t="n">
-        <v>42.62</v>
+      <c r="E247" s="4" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="F247" s="4" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="G247" s="4" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="H247" s="4" t="n">
+        <v>28.59</v>
       </c>
       <c r="I247" s="4" t="n">
-        <v>37.34</v>
+        <v>26.52</v>
       </c>
       <c r="J247" s="4" t="n">
-        <v>31.55</v>
+        <v>24.26</v>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
@@ -36161,7 +36067,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>戈亚斯州</t>
+          <t>米纳斯吉拉斯州</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -36170,22 +36076,22 @@
         </is>
       </c>
       <c r="E253" s="3" t="n">
-        <v>51.73</v>
+        <v>53.46</v>
       </c>
       <c r="F253" s="3" t="n">
-        <v>52.2</v>
+        <v>54.66</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>53.21</v>
+        <v>56.41</v>
       </c>
       <c r="H253" s="3" t="n">
-        <v>55.67</v>
+        <v>59.07</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>59.13</v>
+        <v>61.89</v>
       </c>
       <c r="J253" s="3" t="n">
-        <v>63.48</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
@@ -36207,7 +36113,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>米纳斯吉拉斯州</t>
+          <t>马托格罗索州</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -36216,22 +36122,22 @@
         </is>
       </c>
       <c r="E254" s="3" t="n">
-        <v>53.46</v>
+        <v>45.91</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>54.66</v>
+        <v>46.68</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>56.41</v>
+        <v>49.38</v>
       </c>
       <c r="H254" s="3" t="n">
-        <v>59.07</v>
+        <v>53.14</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>61.89</v>
+        <v>57.7</v>
       </c>
       <c r="J254" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>60.69</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -36243,17 +36149,17 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>马托格罗索州</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -36261,23 +36167,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E255" s="3" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="F255" s="3" t="n">
-        <v>46.68</v>
-      </c>
-      <c r="G255" s="3" t="n">
-        <v>49.38</v>
+      <c r="E255" s="4" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="F255" s="4" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="G255" s="4" t="n">
+        <v>39.29</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>53.14</v>
+        <v>45.88</v>
       </c>
       <c r="I255" s="3" t="n">
-        <v>57.7</v>
+        <v>51.97</v>
       </c>
       <c r="J255" s="3" t="n">
-        <v>60.69</v>
+        <v>56.54</v>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
@@ -36299,7 +36205,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -36307,23 +36213,23 @@
           <t>高粱</t>
         </is>
       </c>
-      <c r="E256" s="4" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="F256" s="4" t="n">
-        <v>34.35</v>
-      </c>
-      <c r="G256" s="4" t="n">
-        <v>39.29</v>
+      <c r="E256" s="3" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="G256" s="3" t="n">
+        <v>48.08</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>45.88</v>
+        <v>49.49</v>
       </c>
       <c r="I256" s="3" t="n">
-        <v>51.97</v>
+        <v>49.88</v>
       </c>
       <c r="J256" s="3" t="n">
-        <v>56.54</v>
+        <v>50</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -36331,52 +36237,6 @@
         </is>
       </c>
       <c r="L256" s="2" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="3" t="inlineStr">
-        <is>
-          <t>美国</t>
-        </is>
-      </c>
-      <c r="B257" s="3" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C257" s="3" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="D257" s="3" t="inlineStr">
-        <is>
-          <t>高粱</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="n">
-        <v>43.98</v>
-      </c>
-      <c r="F257" s="3" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="G257" s="3" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="H257" s="3" t="n">
-        <v>49.49</v>
-      </c>
-      <c r="I257" s="3" t="n">
-        <v>49.88</v>
-      </c>
-      <c r="J257" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="K257" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="L257" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VHI_Data/VHI_最近6周汇总.xlsx
+++ b/VHI_Data/VHI_最近6周汇总.xlsx
@@ -25677,7 +25677,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L2" s="2" t="n"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L5" s="3" t="n"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L7" s="3" t="n"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L8" s="2" t="n"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L12" s="2" t="n"/>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L14" s="2" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L16" s="2" t="n"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L18" s="2" t="n"/>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L22" s="2" t="n"/>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L23" s="3" t="n"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L24" s="2" t="n"/>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L25" s="3" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L26" s="2" t="n"/>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L27" s="3" t="n"/>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L28" s="2" t="n"/>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L29" s="3" t="n"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L30" s="2" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L31" s="3" t="n"/>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L32" s="2" t="n"/>
@@ -27103,7 +27103,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L33" s="3" t="n"/>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L34" s="2" t="n"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L35" s="3" t="n"/>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L36" s="2" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L37" s="3" t="n"/>
@@ -27333,7 +27333,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L38" s="2" t="n"/>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L39" s="3" t="n"/>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L40" s="2" t="n"/>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L41" s="3" t="n"/>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L42" s="2" t="n"/>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L43" s="3" t="n"/>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -27701,7 +27701,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L46" s="2" t="n"/>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L47" s="3" t="n"/>
@@ -27793,7 +27793,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L48" s="2" t="n"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L49" s="3" t="n"/>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L50" s="2" t="n"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="L51" s="3" t="n"/>
@@ -27977,7 +27977,7 @@
       </c>
     